--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -28214,13 +28214,13 @@
         <v>9</v>
       </c>
       <c r="D1265" t="n">
-        <v>5.65</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="E1265" t="n">
-        <v>6.64</v>
+        <v>7.22</v>
       </c>
       <c r="F1265" t="n">
-        <v>211.32</v>
+        <v>214.88</v>
       </c>
     </row>
     <row r="1266">
@@ -42116,13 +42116,13 @@
         <v>42.52</v>
       </c>
       <c r="J23" t="n">
-        <v>5.65</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>117.66</v>
+        <v>121.14</v>
       </c>
     </row>
   </sheetData>
@@ -43148,13 +43148,13 @@
         <v>17.04</v>
       </c>
       <c r="J23" t="n">
-        <v>6.64</v>
+        <v>7.22</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>155.88</v>
+        <v>156.46</v>
       </c>
     </row>
   </sheetData>
@@ -44112,7 +44112,7 @@
         <v>207.24</v>
       </c>
       <c r="J23" t="n">
-        <v>211.32</v>
+        <v>214.88</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -8308,10 +8308,10 @@
         <v>9</v>
       </c>
       <c r="D358" t="n">
-        <v>1.37</v>
+        <v>1.492</v>
       </c>
       <c r="E358" t="n">
-        <v>2.826</v>
+        <v>2.864</v>
       </c>
       <c r="F358" t="n">
         <v>47.132</v>
@@ -13858,13 +13858,13 @@
         <v>9</v>
       </c>
       <c r="D611" t="n">
-        <v>3.533</v>
+        <v>3.831</v>
       </c>
       <c r="E611" t="n">
-        <v>3.19</v>
+        <v>3.575</v>
       </c>
       <c r="F611" t="n">
-        <v>24.211</v>
+        <v>24.634</v>
       </c>
     </row>
     <row r="612">
@@ -22504,13 +22504,13 @@
         <v>9</v>
       </c>
       <c r="D1004" t="n">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="E1004" t="n">
-        <v>7.67</v>
+        <v>8.25</v>
       </c>
       <c r="F1004" t="n">
-        <v>80.70999999999999</v>
+        <v>80.56</v>
       </c>
     </row>
     <row r="1005">
@@ -36004,13 +36004,13 @@
         <v>9</v>
       </c>
       <c r="D1658" t="n">
-        <v>6.563</v>
+        <v>7.063</v>
       </c>
       <c r="E1658" t="n">
-        <v>13.686</v>
+        <v>14.689</v>
       </c>
       <c r="F1658" t="n">
-        <v>152.053</v>
+        <v>152.326</v>
       </c>
     </row>
   </sheetData>
@@ -37435,7 +37435,7 @@
         <v>84.2</v>
       </c>
       <c r="J34" t="n">
-        <v>80.70999999999999</v>
+        <v>80.56</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
@@ -38676,13 +38676,13 @@
         <v>16.109</v>
       </c>
       <c r="J34" t="n">
-        <v>6.563</v>
+        <v>7.063</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>189.6</v>
+        <v>190.1</v>
       </c>
     </row>
   </sheetData>
@@ -39928,13 +39928,13 @@
         <v>36.758</v>
       </c>
       <c r="J34" t="n">
-        <v>13.686</v>
+        <v>14.689</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>328.951</v>
+        <v>329.954</v>
       </c>
     </row>
   </sheetData>
@@ -41071,7 +41071,7 @@
         <v>155.567</v>
       </c>
       <c r="J34" t="n">
-        <v>152.053</v>
+        <v>152.326</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
@@ -45509,13 +45509,13 @@
         <v>3.782</v>
       </c>
       <c r="J31" t="n">
-        <v>1.37</v>
+        <v>1.492</v>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>44.498</v>
+        <v>44.62</v>
       </c>
     </row>
   </sheetData>
@@ -46909,13 +46909,13 @@
         <v>4.822</v>
       </c>
       <c r="J31" t="n">
-        <v>2.826</v>
+        <v>2.864</v>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>61.924</v>
+        <v>61.962</v>
       </c>
     </row>
   </sheetData>
@@ -49238,13 +49238,13 @@
         <v>5.597</v>
       </c>
       <c r="J23" t="n">
-        <v>3.533</v>
+        <v>3.831</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>79.992</v>
+        <v>80.29000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -50270,13 +50270,13 @@
         <v>13.826</v>
       </c>
       <c r="J23" t="n">
-        <v>3.19</v>
+        <v>3.575</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>108.757</v>
+        <v>109.142</v>
       </c>
     </row>
   </sheetData>
@@ -51226,7 +51226,7 @@
         <v>22.876</v>
       </c>
       <c r="J23" t="n">
-        <v>24.211</v>
+        <v>24.634</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
@@ -52755,13 +52755,13 @@
         <v>6.73</v>
       </c>
       <c r="J34" t="n">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>65.11</v>
+        <v>65.19</v>
       </c>
     </row>
   </sheetData>
@@ -54287,13 +54287,13 @@
         <v>18.11</v>
       </c>
       <c r="J34" t="n">
-        <v>7.67</v>
+        <v>8.25</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>158.27</v>
+        <v>158.85</v>
       </c>
     </row>
   </sheetData>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -28214,13 +28214,13 @@
         <v>9</v>
       </c>
       <c r="D1265" t="n">
-        <v>9.130000000000001</v>
+        <v>11.22</v>
       </c>
       <c r="E1265" t="n">
-        <v>7.22</v>
+        <v>7.8</v>
       </c>
       <c r="F1265" t="n">
-        <v>214.88</v>
+        <v>217.04</v>
       </c>
     </row>
     <row r="1266">
@@ -42116,13 +42116,13 @@
         <v>42.52</v>
       </c>
       <c r="J23" t="n">
-        <v>9.130000000000001</v>
+        <v>11.22</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>121.14</v>
+        <v>123.23</v>
       </c>
     </row>
   </sheetData>
@@ -43148,13 +43148,13 @@
         <v>17.04</v>
       </c>
       <c r="J23" t="n">
-        <v>7.22</v>
+        <v>7.8</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>156.46</v>
+        <v>157.04</v>
       </c>
     </row>
   </sheetData>
@@ -44112,7 +44112,7 @@
         <v>207.24</v>
       </c>
       <c r="J23" t="n">
-        <v>214.88</v>
+        <v>217.04</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -8308,10 +8308,10 @@
         <v>9</v>
       </c>
       <c r="D358" t="n">
-        <v>1.492</v>
+        <v>1.665</v>
       </c>
       <c r="E358" t="n">
-        <v>2.864</v>
+        <v>3.037</v>
       </c>
       <c r="F358" t="n">
         <v>47.132</v>
@@ -13858,13 +13858,13 @@
         <v>9</v>
       </c>
       <c r="D611" t="n">
-        <v>3.831</v>
+        <v>4.107</v>
       </c>
       <c r="E611" t="n">
-        <v>3.575</v>
+        <v>3.963</v>
       </c>
       <c r="F611" t="n">
-        <v>24.634</v>
+        <v>24.719</v>
       </c>
     </row>
     <row r="612">
@@ -22504,13 +22504,13 @@
         <v>9</v>
       </c>
       <c r="D1004" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="E1004" t="n">
-        <v>8.25</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="F1004" t="n">
-        <v>80.56</v>
+        <v>80.41</v>
       </c>
     </row>
     <row r="1005">
@@ -36004,13 +36004,13 @@
         <v>9</v>
       </c>
       <c r="D1658" t="n">
-        <v>7.063</v>
+        <v>7.552</v>
       </c>
       <c r="E1658" t="n">
-        <v>14.689</v>
+        <v>15.79</v>
       </c>
       <c r="F1658" t="n">
-        <v>152.326</v>
+        <v>152.261</v>
       </c>
     </row>
   </sheetData>
@@ -37435,7 +37435,7 @@
         <v>84.2</v>
       </c>
       <c r="J34" t="n">
-        <v>80.56</v>
+        <v>80.41</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
@@ -38676,13 +38676,13 @@
         <v>16.109</v>
       </c>
       <c r="J34" t="n">
-        <v>7.063</v>
+        <v>7.552</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>190.1</v>
+        <v>190.589</v>
       </c>
     </row>
   </sheetData>
@@ -39928,13 +39928,13 @@
         <v>36.758</v>
       </c>
       <c r="J34" t="n">
-        <v>14.689</v>
+        <v>15.79</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>329.954</v>
+        <v>331.055</v>
       </c>
     </row>
   </sheetData>
@@ -41071,7 +41071,7 @@
         <v>155.567</v>
       </c>
       <c r="J34" t="n">
-        <v>152.326</v>
+        <v>152.261</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
@@ -45509,13 +45509,13 @@
         <v>3.782</v>
       </c>
       <c r="J31" t="n">
-        <v>1.492</v>
+        <v>1.665</v>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>44.62</v>
+        <v>44.793</v>
       </c>
     </row>
   </sheetData>
@@ -46909,13 +46909,13 @@
         <v>4.822</v>
       </c>
       <c r="J31" t="n">
-        <v>2.864</v>
+        <v>3.037</v>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>61.962</v>
+        <v>62.135</v>
       </c>
     </row>
   </sheetData>
@@ -49238,13 +49238,13 @@
         <v>5.597</v>
       </c>
       <c r="J23" t="n">
-        <v>3.831</v>
+        <v>4.107</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>80.29000000000001</v>
+        <v>80.566</v>
       </c>
     </row>
   </sheetData>
@@ -50270,13 +50270,13 @@
         <v>13.826</v>
       </c>
       <c r="J23" t="n">
-        <v>3.575</v>
+        <v>3.963</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>109.142</v>
+        <v>109.53</v>
       </c>
     </row>
   </sheetData>
@@ -51226,7 +51226,7 @@
         <v>22.876</v>
       </c>
       <c r="J23" t="n">
-        <v>24.634</v>
+        <v>24.719</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
@@ -52755,13 +52755,13 @@
         <v>6.73</v>
       </c>
       <c r="J34" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>65.19</v>
+        <v>65.22999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -54287,13 +54287,13 @@
         <v>18.11</v>
       </c>
       <c r="J34" t="n">
-        <v>8.25</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>158.85</v>
+        <v>159.39</v>
       </c>
     </row>
   </sheetData>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -28214,13 +28214,13 @@
         <v>9</v>
       </c>
       <c r="D1265" t="n">
-        <v>11.22</v>
+        <v>12.29</v>
       </c>
       <c r="E1265" t="n">
-        <v>7.8</v>
+        <v>8.35</v>
       </c>
       <c r="F1265" t="n">
-        <v>217.04</v>
+        <v>218.12</v>
       </c>
     </row>
     <row r="1266">
@@ -42116,13 +42116,13 @@
         <v>42.52</v>
       </c>
       <c r="J23" t="n">
-        <v>11.22</v>
+        <v>12.29</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>123.23</v>
+        <v>124.3</v>
       </c>
     </row>
   </sheetData>
@@ -43148,13 +43148,13 @@
         <v>17.04</v>
       </c>
       <c r="J23" t="n">
-        <v>7.8</v>
+        <v>8.35</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>157.04</v>
+        <v>157.59</v>
       </c>
     </row>
   </sheetData>
@@ -44112,7 +44112,7 @@
         <v>207.24</v>
       </c>
       <c r="J23" t="n">
-        <v>217.04</v>
+        <v>218.12</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -8308,10 +8308,10 @@
         <v>9</v>
       </c>
       <c r="D358" t="n">
-        <v>1.665</v>
+        <v>1.838</v>
       </c>
       <c r="E358" t="n">
-        <v>3.037</v>
+        <v>3.21</v>
       </c>
       <c r="F358" t="n">
         <v>47.132</v>
@@ -13858,10 +13858,10 @@
         <v>9</v>
       </c>
       <c r="D611" t="n">
-        <v>4.107</v>
+        <v>4.383</v>
       </c>
       <c r="E611" t="n">
-        <v>3.963</v>
+        <v>4.351</v>
       </c>
       <c r="F611" t="n">
         <v>24.719</v>
@@ -22507,10 +22507,10 @@
         <v>1.78</v>
       </c>
       <c r="E1004" t="n">
-        <v>8.789999999999999</v>
+        <v>9.32</v>
       </c>
       <c r="F1004" t="n">
-        <v>80.41</v>
+        <v>80.11</v>
       </c>
     </row>
     <row r="1005">
@@ -36004,13 +36004,13 @@
         <v>9</v>
       </c>
       <c r="D1658" t="n">
-        <v>7.552</v>
+        <v>8.000999999999999</v>
       </c>
       <c r="E1658" t="n">
-        <v>15.79</v>
+        <v>16.881</v>
       </c>
       <c r="F1658" t="n">
-        <v>152.261</v>
+        <v>151.961</v>
       </c>
     </row>
   </sheetData>
@@ -37435,7 +37435,7 @@
         <v>84.2</v>
       </c>
       <c r="J34" t="n">
-        <v>80.41</v>
+        <v>80.11</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
@@ -38676,13 +38676,13 @@
         <v>16.109</v>
       </c>
       <c r="J34" t="n">
-        <v>7.552</v>
+        <v>8.000999999999999</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>190.589</v>
+        <v>191.038</v>
       </c>
     </row>
   </sheetData>
@@ -39928,13 +39928,13 @@
         <v>36.758</v>
       </c>
       <c r="J34" t="n">
-        <v>15.79</v>
+        <v>16.881</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>331.055</v>
+        <v>332.146</v>
       </c>
     </row>
   </sheetData>
@@ -41071,7 +41071,7 @@
         <v>155.567</v>
       </c>
       <c r="J34" t="n">
-        <v>152.261</v>
+        <v>151.961</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
@@ -45509,13 +45509,13 @@
         <v>3.782</v>
       </c>
       <c r="J31" t="n">
-        <v>1.665</v>
+        <v>1.838</v>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>44.793</v>
+        <v>44.966</v>
       </c>
     </row>
   </sheetData>
@@ -46909,13 +46909,13 @@
         <v>4.822</v>
       </c>
       <c r="J31" t="n">
-        <v>3.037</v>
+        <v>3.21</v>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>62.135</v>
+        <v>62.308</v>
       </c>
     </row>
   </sheetData>
@@ -49238,13 +49238,13 @@
         <v>5.597</v>
       </c>
       <c r="J23" t="n">
-        <v>4.107</v>
+        <v>4.383</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>80.566</v>
+        <v>80.842</v>
       </c>
     </row>
   </sheetData>
@@ -50270,13 +50270,13 @@
         <v>13.826</v>
       </c>
       <c r="J23" t="n">
-        <v>3.963</v>
+        <v>4.351</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>109.53</v>
+        <v>109.918</v>
       </c>
     </row>
   </sheetData>
@@ -54287,13 +54287,13 @@
         <v>18.11</v>
       </c>
       <c r="J34" t="n">
-        <v>8.789999999999999</v>
+        <v>9.32</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>159.39</v>
+        <v>159.92</v>
       </c>
     </row>
   </sheetData>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -28214,13 +28214,13 @@
         <v>9</v>
       </c>
       <c r="D1265" t="n">
-        <v>12.29</v>
+        <v>14.18</v>
       </c>
       <c r="E1265" t="n">
-        <v>8.35</v>
+        <v>8.91</v>
       </c>
       <c r="F1265" t="n">
-        <v>218.12</v>
+        <v>219.92</v>
       </c>
     </row>
     <row r="1266">
@@ -42116,13 +42116,13 @@
         <v>42.52</v>
       </c>
       <c r="J23" t="n">
-        <v>12.29</v>
+        <v>14.18</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>124.3</v>
+        <v>126.19</v>
       </c>
     </row>
   </sheetData>
@@ -43148,13 +43148,13 @@
         <v>17.04</v>
       </c>
       <c r="J23" t="n">
-        <v>8.35</v>
+        <v>8.91</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>157.59</v>
+        <v>158.15</v>
       </c>
     </row>
   </sheetData>
@@ -44112,7 +44112,7 @@
         <v>207.24</v>
       </c>
       <c r="J23" t="n">
-        <v>218.12</v>
+        <v>219.92</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -8308,13 +8308,13 @@
         <v>9</v>
       </c>
       <c r="D358" t="n">
-        <v>1.838</v>
+        <v>2.01</v>
       </c>
       <c r="E358" t="n">
-        <v>3.21</v>
+        <v>3.382</v>
       </c>
       <c r="F358" t="n">
-        <v>47.132</v>
+        <v>46.964</v>
       </c>
     </row>
     <row r="359">
@@ -13858,10 +13858,10 @@
         <v>9</v>
       </c>
       <c r="D611" t="n">
-        <v>4.383</v>
+        <v>4.601</v>
       </c>
       <c r="E611" t="n">
-        <v>4.351</v>
+        <v>4.744</v>
       </c>
       <c r="F611" t="n">
         <v>24.719</v>
@@ -22504,13 +22504,13 @@
         <v>9</v>
       </c>
       <c r="D1004" t="n">
-        <v>1.78</v>
+        <v>2.15</v>
       </c>
       <c r="E1004" t="n">
-        <v>9.32</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="F1004" t="n">
-        <v>80.11</v>
+        <v>80.26000000000001</v>
       </c>
     </row>
     <row r="1005">
@@ -36004,13 +36004,13 @@
         <v>9</v>
       </c>
       <c r="D1658" t="n">
-        <v>8.000999999999999</v>
+        <v>8.760999999999999</v>
       </c>
       <c r="E1658" t="n">
-        <v>16.881</v>
+        <v>18.016</v>
       </c>
       <c r="F1658" t="n">
-        <v>151.961</v>
+        <v>151.943</v>
       </c>
     </row>
   </sheetData>
@@ -37435,7 +37435,7 @@
         <v>84.2</v>
       </c>
       <c r="J34" t="n">
-        <v>80.11</v>
+        <v>80.26000000000001</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
@@ -38676,13 +38676,13 @@
         <v>16.109</v>
       </c>
       <c r="J34" t="n">
-        <v>8.000999999999999</v>
+        <v>8.760999999999999</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>191.038</v>
+        <v>191.798</v>
       </c>
     </row>
   </sheetData>
@@ -39928,13 +39928,13 @@
         <v>36.758</v>
       </c>
       <c r="J34" t="n">
-        <v>16.881</v>
+        <v>18.016</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>332.146</v>
+        <v>333.281</v>
       </c>
     </row>
   </sheetData>
@@ -41071,7 +41071,7 @@
         <v>155.567</v>
       </c>
       <c r="J34" t="n">
-        <v>151.961</v>
+        <v>151.943</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
@@ -45509,13 +45509,13 @@
         <v>3.782</v>
       </c>
       <c r="J31" t="n">
-        <v>1.838</v>
+        <v>2.01</v>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>44.966</v>
+        <v>45.138</v>
       </c>
     </row>
   </sheetData>
@@ -46909,13 +46909,13 @@
         <v>4.822</v>
       </c>
       <c r="J31" t="n">
-        <v>3.21</v>
+        <v>3.382</v>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>62.308</v>
+        <v>62.48</v>
       </c>
     </row>
   </sheetData>
@@ -48217,7 +48217,7 @@
         <v>48.491</v>
       </c>
       <c r="J31" t="n">
-        <v>47.132</v>
+        <v>46.964</v>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
@@ -49238,13 +49238,13 @@
         <v>5.597</v>
       </c>
       <c r="J23" t="n">
-        <v>4.383</v>
+        <v>4.601</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>80.842</v>
+        <v>81.06</v>
       </c>
     </row>
   </sheetData>
@@ -50270,13 +50270,13 @@
         <v>13.826</v>
       </c>
       <c r="J23" t="n">
-        <v>4.351</v>
+        <v>4.744</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>109.918</v>
+        <v>110.311</v>
       </c>
     </row>
   </sheetData>
@@ -52755,13 +52755,13 @@
         <v>6.73</v>
       </c>
       <c r="J34" t="n">
-        <v>1.78</v>
+        <v>2.15</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>65.22999999999999</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -54287,13 +54287,13 @@
         <v>18.11</v>
       </c>
       <c r="J34" t="n">
-        <v>9.32</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>159.92</v>
+        <v>160.49</v>
       </c>
     </row>
   </sheetData>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -28214,13 +28214,13 @@
         <v>9</v>
       </c>
       <c r="D1265" t="n">
-        <v>14.18</v>
+        <v>15.24</v>
       </c>
       <c r="E1265" t="n">
-        <v>8.91</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="F1265" t="n">
-        <v>219.92</v>
+        <v>221</v>
       </c>
     </row>
     <row r="1266">
@@ -42116,13 +42116,13 @@
         <v>42.52</v>
       </c>
       <c r="J23" t="n">
-        <v>14.18</v>
+        <v>15.24</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>126.19</v>
+        <v>127.25</v>
       </c>
     </row>
   </sheetData>
@@ -43148,13 +43148,13 @@
         <v>17.04</v>
       </c>
       <c r="J23" t="n">
-        <v>8.91</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>158.15</v>
+        <v>158.7</v>
       </c>
     </row>
   </sheetData>
@@ -44112,7 +44112,7 @@
         <v>207.24</v>
       </c>
       <c r="J23" t="n">
-        <v>219.92</v>
+        <v>221</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -8308,13 +8308,13 @@
         <v>9</v>
       </c>
       <c r="D358" t="n">
-        <v>2.01</v>
+        <v>2.857</v>
       </c>
       <c r="E358" t="n">
-        <v>3.382</v>
+        <v>3.554</v>
       </c>
       <c r="F358" t="n">
-        <v>46.964</v>
+        <v>47.639</v>
       </c>
     </row>
     <row r="359">
@@ -13858,13 +13858,13 @@
         <v>9</v>
       </c>
       <c r="D611" t="n">
-        <v>4.601</v>
+        <v>5.088</v>
       </c>
       <c r="E611" t="n">
-        <v>4.744</v>
+        <v>5.152</v>
       </c>
       <c r="F611" t="n">
-        <v>24.719</v>
+        <v>24.974</v>
       </c>
     </row>
     <row r="612">
@@ -22504,13 +22504,13 @@
         <v>9</v>
       </c>
       <c r="D1004" t="n">
-        <v>2.15</v>
+        <v>2.91</v>
       </c>
       <c r="E1004" t="n">
-        <v>9.890000000000001</v>
+        <v>10.41</v>
       </c>
       <c r="F1004" t="n">
-        <v>80.26000000000001</v>
+        <v>80.87</v>
       </c>
     </row>
     <row r="1005">
@@ -36004,13 +36004,13 @@
         <v>9</v>
       </c>
       <c r="D1658" t="n">
-        <v>8.760999999999999</v>
+        <v>10.855</v>
       </c>
       <c r="E1658" t="n">
-        <v>18.016</v>
+        <v>19.116</v>
       </c>
       <c r="F1658" t="n">
-        <v>151.943</v>
+        <v>153.483</v>
       </c>
     </row>
   </sheetData>
@@ -37435,7 +37435,7 @@
         <v>84.2</v>
       </c>
       <c r="J34" t="n">
-        <v>80.26000000000001</v>
+        <v>80.87</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
@@ -38676,13 +38676,13 @@
         <v>16.109</v>
       </c>
       <c r="J34" t="n">
-        <v>8.760999999999999</v>
+        <v>10.855</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>191.798</v>
+        <v>193.892</v>
       </c>
     </row>
   </sheetData>
@@ -39928,13 +39928,13 @@
         <v>36.758</v>
       </c>
       <c r="J34" t="n">
-        <v>18.016</v>
+        <v>19.116</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>333.281</v>
+        <v>334.381</v>
       </c>
     </row>
   </sheetData>
@@ -41071,7 +41071,7 @@
         <v>155.567</v>
       </c>
       <c r="J34" t="n">
-        <v>151.943</v>
+        <v>153.483</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
@@ -45509,13 +45509,13 @@
         <v>3.782</v>
       </c>
       <c r="J31" t="n">
-        <v>2.01</v>
+        <v>2.857</v>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>45.138</v>
+        <v>45.985</v>
       </c>
     </row>
   </sheetData>
@@ -46909,13 +46909,13 @@
         <v>4.822</v>
       </c>
       <c r="J31" t="n">
-        <v>3.382</v>
+        <v>3.554</v>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>62.48</v>
+        <v>62.652</v>
       </c>
     </row>
   </sheetData>
@@ -48217,7 +48217,7 @@
         <v>48.491</v>
       </c>
       <c r="J31" t="n">
-        <v>46.964</v>
+        <v>47.639</v>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
@@ -49238,13 +49238,13 @@
         <v>5.597</v>
       </c>
       <c r="J23" t="n">
-        <v>4.601</v>
+        <v>5.088</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>81.06</v>
+        <v>81.547</v>
       </c>
     </row>
   </sheetData>
@@ -50270,13 +50270,13 @@
         <v>13.826</v>
       </c>
       <c r="J23" t="n">
-        <v>4.744</v>
+        <v>5.152</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>110.311</v>
+        <v>110.719</v>
       </c>
     </row>
   </sheetData>
@@ -51226,7 +51226,7 @@
         <v>22.876</v>
       </c>
       <c r="J23" t="n">
-        <v>24.719</v>
+        <v>24.974</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
@@ -52755,13 +52755,13 @@
         <v>6.73</v>
       </c>
       <c r="J34" t="n">
-        <v>2.15</v>
+        <v>2.91</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>65.59999999999999</v>
+        <v>66.36</v>
       </c>
     </row>
   </sheetData>
@@ -54287,13 +54287,13 @@
         <v>18.11</v>
       </c>
       <c r="J34" t="n">
-        <v>9.890000000000001</v>
+        <v>10.41</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>160.49</v>
+        <v>161.01</v>
       </c>
     </row>
   </sheetData>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -28214,13 +28214,13 @@
         <v>9</v>
       </c>
       <c r="D1265" t="n">
-        <v>15.24</v>
+        <v>16.17</v>
       </c>
       <c r="E1265" t="n">
-        <v>9.460000000000001</v>
+        <v>10.02</v>
       </c>
       <c r="F1265" t="n">
-        <v>221</v>
+        <v>221.72</v>
       </c>
     </row>
     <row r="1266">
@@ -42116,13 +42116,13 @@
         <v>42.52</v>
       </c>
       <c r="J23" t="n">
-        <v>15.24</v>
+        <v>16.17</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>127.25</v>
+        <v>128.18</v>
       </c>
     </row>
   </sheetData>
@@ -43148,13 +43148,13 @@
         <v>17.04</v>
       </c>
       <c r="J23" t="n">
-        <v>9.460000000000001</v>
+        <v>10.02</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>158.7</v>
+        <v>159.26</v>
       </c>
     </row>
   </sheetData>
@@ -44112,7 +44112,7 @@
         <v>207.24</v>
       </c>
       <c r="J23" t="n">
-        <v>221</v>
+        <v>221.72</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -8308,13 +8308,13 @@
         <v>9</v>
       </c>
       <c r="D358" t="n">
-        <v>2.857</v>
+        <v>3.115</v>
       </c>
       <c r="E358" t="n">
-        <v>3.554</v>
+        <v>3.727</v>
       </c>
       <c r="F358" t="n">
-        <v>47.639</v>
+        <v>47.723</v>
       </c>
     </row>
     <row r="359">
@@ -13858,13 +13858,13 @@
         <v>9</v>
       </c>
       <c r="D611" t="n">
-        <v>5.088</v>
+        <v>5.231</v>
       </c>
       <c r="E611" t="n">
-        <v>5.152</v>
+        <v>5.556</v>
       </c>
       <c r="F611" t="n">
-        <v>24.974</v>
+        <v>24.889</v>
       </c>
     </row>
     <row r="612">
@@ -22507,10 +22507,10 @@
         <v>2.91</v>
       </c>
       <c r="E1004" t="n">
-        <v>10.41</v>
+        <v>10.93</v>
       </c>
       <c r="F1004" t="n">
-        <v>80.87</v>
+        <v>80.70999999999999</v>
       </c>
     </row>
     <row r="1005">
@@ -28214,7 +28214,7 @@
         <v>9</v>
       </c>
       <c r="D1265" t="n">
-        <v>16.17</v>
+        <v>15.87</v>
       </c>
       <c r="E1265" t="n">
         <v>10.02</v>
@@ -36004,13 +36004,13 @@
         <v>9</v>
       </c>
       <c r="D1658" t="n">
-        <v>10.855</v>
+        <v>11.256</v>
       </c>
       <c r="E1658" t="n">
-        <v>19.116</v>
+        <v>20.213</v>
       </c>
       <c r="F1658" t="n">
-        <v>153.483</v>
+        <v>153.322</v>
       </c>
     </row>
   </sheetData>
@@ -37435,7 +37435,7 @@
         <v>84.2</v>
       </c>
       <c r="J34" t="n">
-        <v>80.87</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
@@ -38676,13 +38676,13 @@
         <v>16.109</v>
       </c>
       <c r="J34" t="n">
-        <v>10.855</v>
+        <v>11.256</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>193.892</v>
+        <v>194.293</v>
       </c>
     </row>
   </sheetData>
@@ -39928,13 +39928,13 @@
         <v>36.758</v>
       </c>
       <c r="J34" t="n">
-        <v>19.116</v>
+        <v>20.213</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>334.381</v>
+        <v>335.478</v>
       </c>
     </row>
   </sheetData>
@@ -41071,7 +41071,7 @@
         <v>155.567</v>
       </c>
       <c r="J34" t="n">
-        <v>153.483</v>
+        <v>153.322</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
@@ -42116,13 +42116,13 @@
         <v>42.52</v>
       </c>
       <c r="J23" t="n">
-        <v>16.17</v>
+        <v>15.87</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>128.18</v>
+        <v>127.88</v>
       </c>
     </row>
   </sheetData>
@@ -45509,13 +45509,13 @@
         <v>3.782</v>
       </c>
       <c r="J31" t="n">
-        <v>2.857</v>
+        <v>3.115</v>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>45.985</v>
+        <v>46.243</v>
       </c>
     </row>
   </sheetData>
@@ -46909,13 +46909,13 @@
         <v>4.822</v>
       </c>
       <c r="J31" t="n">
-        <v>3.554</v>
+        <v>3.727</v>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>62.652</v>
+        <v>62.825</v>
       </c>
     </row>
   </sheetData>
@@ -48217,7 +48217,7 @@
         <v>48.491</v>
       </c>
       <c r="J31" t="n">
-        <v>47.639</v>
+        <v>47.723</v>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
@@ -49238,13 +49238,13 @@
         <v>5.597</v>
       </c>
       <c r="J23" t="n">
-        <v>5.088</v>
+        <v>5.231</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>81.547</v>
+        <v>81.69</v>
       </c>
     </row>
   </sheetData>
@@ -50270,13 +50270,13 @@
         <v>13.826</v>
       </c>
       <c r="J23" t="n">
-        <v>5.152</v>
+        <v>5.556</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>110.719</v>
+        <v>111.123</v>
       </c>
     </row>
   </sheetData>
@@ -51226,7 +51226,7 @@
         <v>22.876</v>
       </c>
       <c r="J23" t="n">
-        <v>24.974</v>
+        <v>24.889</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
@@ -54287,13 +54287,13 @@
         <v>18.11</v>
       </c>
       <c r="J34" t="n">
-        <v>10.41</v>
+        <v>10.93</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>161.01</v>
+        <v>161.53</v>
       </c>
     </row>
   </sheetData>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -22504,13 +22504,13 @@
         <v>9</v>
       </c>
       <c r="D1004" t="n">
-        <v>2.91</v>
+        <v>3.48</v>
       </c>
       <c r="E1004" t="n">
-        <v>10.93</v>
+        <v>11.43</v>
       </c>
       <c r="F1004" t="n">
-        <v>80.70999999999999</v>
+        <v>81.17</v>
       </c>
     </row>
     <row r="1005">
@@ -28214,13 +28214,13 @@
         <v>9</v>
       </c>
       <c r="D1265" t="n">
-        <v>15.87</v>
+        <v>21.21</v>
       </c>
       <c r="E1265" t="n">
-        <v>10.02</v>
+        <v>10.57</v>
       </c>
       <c r="F1265" t="n">
-        <v>221.72</v>
+        <v>227.12</v>
       </c>
     </row>
     <row r="1266">
@@ -36004,13 +36004,13 @@
         <v>9</v>
       </c>
       <c r="D1658" t="n">
-        <v>11.256</v>
+        <v>11.826</v>
       </c>
       <c r="E1658" t="n">
-        <v>20.213</v>
+        <v>20.713</v>
       </c>
       <c r="F1658" t="n">
-        <v>153.322</v>
+        <v>153.782</v>
       </c>
     </row>
   </sheetData>
@@ -37435,7 +37435,7 @@
         <v>84.2</v>
       </c>
       <c r="J34" t="n">
-        <v>80.70999999999999</v>
+        <v>81.17</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
@@ -38676,13 +38676,13 @@
         <v>16.109</v>
       </c>
       <c r="J34" t="n">
-        <v>11.256</v>
+        <v>11.826</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>194.293</v>
+        <v>194.863</v>
       </c>
     </row>
   </sheetData>
@@ -39928,13 +39928,13 @@
         <v>36.758</v>
       </c>
       <c r="J34" t="n">
-        <v>20.213</v>
+        <v>20.713</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>335.478</v>
+        <v>335.978</v>
       </c>
     </row>
   </sheetData>
@@ -41071,7 +41071,7 @@
         <v>155.567</v>
       </c>
       <c r="J34" t="n">
-        <v>153.322</v>
+        <v>153.782</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
@@ -42116,13 +42116,13 @@
         <v>42.52</v>
       </c>
       <c r="J23" t="n">
-        <v>15.87</v>
+        <v>21.21</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>127.88</v>
+        <v>133.22</v>
       </c>
     </row>
   </sheetData>
@@ -43148,13 +43148,13 @@
         <v>17.04</v>
       </c>
       <c r="J23" t="n">
-        <v>10.02</v>
+        <v>10.57</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>159.26</v>
+        <v>159.81</v>
       </c>
     </row>
   </sheetData>
@@ -44112,7 +44112,7 @@
         <v>207.24</v>
       </c>
       <c r="J23" t="n">
-        <v>221.72</v>
+        <v>227.12</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
@@ -52755,13 +52755,13 @@
         <v>6.73</v>
       </c>
       <c r="J34" t="n">
-        <v>2.91</v>
+        <v>3.48</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>66.36</v>
+        <v>66.92999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -54287,13 +54287,13 @@
         <v>18.11</v>
       </c>
       <c r="J34" t="n">
-        <v>10.93</v>
+        <v>11.43</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>161.53</v>
+        <v>162.03</v>
       </c>
     </row>
   </sheetData>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -8308,13 +8308,13 @@
         <v>9</v>
       </c>
       <c r="D358" t="n">
-        <v>3.115</v>
+        <v>4.048</v>
       </c>
       <c r="E358" t="n">
-        <v>3.727</v>
+        <v>3.978</v>
       </c>
       <c r="F358" t="n">
-        <v>47.723</v>
+        <v>48.405</v>
       </c>
     </row>
     <row r="359">
@@ -13858,13 +13858,13 @@
         <v>9</v>
       </c>
       <c r="D611" t="n">
-        <v>5.231</v>
+        <v>5.989</v>
       </c>
       <c r="E611" t="n">
-        <v>5.556</v>
+        <v>5.976</v>
       </c>
       <c r="F611" t="n">
-        <v>24.889</v>
+        <v>25.401</v>
       </c>
     </row>
     <row r="612">
@@ -36004,13 +36004,13 @@
         <v>9</v>
       </c>
       <c r="D1658" t="n">
-        <v>11.826</v>
+        <v>13.517</v>
       </c>
       <c r="E1658" t="n">
-        <v>20.713</v>
+        <v>21.384</v>
       </c>
       <c r="F1658" t="n">
-        <v>153.782</v>
+        <v>154.976</v>
       </c>
     </row>
   </sheetData>
@@ -38676,13 +38676,13 @@
         <v>16.109</v>
       </c>
       <c r="J34" t="n">
-        <v>11.826</v>
+        <v>13.517</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>194.863</v>
+        <v>196.554</v>
       </c>
     </row>
   </sheetData>
@@ -39928,13 +39928,13 @@
         <v>36.758</v>
       </c>
       <c r="J34" t="n">
-        <v>20.713</v>
+        <v>21.384</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>335.978</v>
+        <v>336.649</v>
       </c>
     </row>
   </sheetData>
@@ -41071,7 +41071,7 @@
         <v>155.567</v>
       </c>
       <c r="J34" t="n">
-        <v>153.782</v>
+        <v>154.976</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
@@ -45509,13 +45509,13 @@
         <v>3.782</v>
       </c>
       <c r="J31" t="n">
-        <v>3.115</v>
+        <v>4.048</v>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>46.243</v>
+        <v>47.176</v>
       </c>
     </row>
   </sheetData>
@@ -46909,13 +46909,13 @@
         <v>4.822</v>
       </c>
       <c r="J31" t="n">
-        <v>3.727</v>
+        <v>3.978</v>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>62.825</v>
+        <v>63.076</v>
       </c>
     </row>
   </sheetData>
@@ -48217,7 +48217,7 @@
         <v>48.491</v>
       </c>
       <c r="J31" t="n">
-        <v>47.723</v>
+        <v>48.405</v>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
@@ -49238,13 +49238,13 @@
         <v>5.597</v>
       </c>
       <c r="J23" t="n">
-        <v>5.231</v>
+        <v>5.989</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>81.69</v>
+        <v>82.44800000000001</v>
       </c>
     </row>
   </sheetData>
@@ -50270,13 +50270,13 @@
         <v>13.826</v>
       </c>
       <c r="J23" t="n">
-        <v>5.556</v>
+        <v>5.976</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>111.123</v>
+        <v>111.543</v>
       </c>
     </row>
   </sheetData>
@@ -51226,7 +51226,7 @@
         <v>22.876</v>
       </c>
       <c r="J23" t="n">
-        <v>24.889</v>
+        <v>25.401</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -28214,13 +28214,13 @@
         <v>9</v>
       </c>
       <c r="D1265" t="n">
-        <v>21.21</v>
+        <v>22.57</v>
       </c>
       <c r="E1265" t="n">
-        <v>10.57</v>
+        <v>11.12</v>
       </c>
       <c r="F1265" t="n">
-        <v>227.12</v>
+        <v>228.56</v>
       </c>
     </row>
     <row r="1266">
@@ -42116,13 +42116,13 @@
         <v>42.52</v>
       </c>
       <c r="J23" t="n">
-        <v>21.21</v>
+        <v>22.57</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>133.22</v>
+        <v>134.58</v>
       </c>
     </row>
   </sheetData>
@@ -43148,13 +43148,13 @@
         <v>17.04</v>
       </c>
       <c r="J23" t="n">
-        <v>10.57</v>
+        <v>11.12</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>159.81</v>
+        <v>160.36</v>
       </c>
     </row>
   </sheetData>
@@ -44112,7 +44112,7 @@
         <v>207.24</v>
       </c>
       <c r="J23" t="n">
-        <v>227.12</v>
+        <v>228.56</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -8308,10 +8308,10 @@
         <v>9</v>
       </c>
       <c r="D358" t="n">
-        <v>4.048</v>
+        <v>4.299</v>
       </c>
       <c r="E358" t="n">
-        <v>3.978</v>
+        <v>4.229</v>
       </c>
       <c r="F358" t="n">
         <v>48.405</v>
@@ -13858,10 +13858,10 @@
         <v>9</v>
       </c>
       <c r="D611" t="n">
-        <v>5.989</v>
+        <v>6.409</v>
       </c>
       <c r="E611" t="n">
-        <v>5.976</v>
+        <v>6.396</v>
       </c>
       <c r="F611" t="n">
         <v>25.401</v>
@@ -22504,13 +22504,13 @@
         <v>9</v>
       </c>
       <c r="D1004" t="n">
-        <v>3.48</v>
+        <v>3.86</v>
       </c>
       <c r="E1004" t="n">
-        <v>11.43</v>
+        <v>11.88</v>
       </c>
       <c r="F1004" t="n">
-        <v>81.17</v>
+        <v>81.47</v>
       </c>
     </row>
     <row r="1005">
@@ -36004,13 +36004,13 @@
         <v>9</v>
       </c>
       <c r="D1658" t="n">
-        <v>13.517</v>
+        <v>14.568</v>
       </c>
       <c r="E1658" t="n">
-        <v>21.384</v>
+        <v>22.505</v>
       </c>
       <c r="F1658" t="n">
-        <v>154.976</v>
+        <v>155.276</v>
       </c>
     </row>
   </sheetData>
@@ -37435,7 +37435,7 @@
         <v>84.2</v>
       </c>
       <c r="J34" t="n">
-        <v>81.17</v>
+        <v>81.47</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
@@ -38676,13 +38676,13 @@
         <v>16.109</v>
       </c>
       <c r="J34" t="n">
-        <v>13.517</v>
+        <v>14.568</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>196.554</v>
+        <v>197.605</v>
       </c>
     </row>
   </sheetData>
@@ -39928,13 +39928,13 @@
         <v>36.758</v>
       </c>
       <c r="J34" t="n">
-        <v>21.384</v>
+        <v>22.505</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>336.649</v>
+        <v>337.77</v>
       </c>
     </row>
   </sheetData>
@@ -41071,7 +41071,7 @@
         <v>155.567</v>
       </c>
       <c r="J34" t="n">
-        <v>154.976</v>
+        <v>155.276</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
@@ -45509,13 +45509,13 @@
         <v>3.782</v>
       </c>
       <c r="J31" t="n">
-        <v>4.048</v>
+        <v>4.299</v>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>47.176</v>
+        <v>47.427</v>
       </c>
     </row>
   </sheetData>
@@ -46909,13 +46909,13 @@
         <v>4.822</v>
       </c>
       <c r="J31" t="n">
-        <v>3.978</v>
+        <v>4.229</v>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>63.076</v>
+        <v>63.327</v>
       </c>
     </row>
   </sheetData>
@@ -49238,13 +49238,13 @@
         <v>5.597</v>
       </c>
       <c r="J23" t="n">
-        <v>5.989</v>
+        <v>6.409</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>82.44800000000001</v>
+        <v>82.86800000000001</v>
       </c>
     </row>
   </sheetData>
@@ -50270,13 +50270,13 @@
         <v>13.826</v>
       </c>
       <c r="J23" t="n">
-        <v>5.976</v>
+        <v>6.396</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>111.543</v>
+        <v>111.963</v>
       </c>
     </row>
   </sheetData>
@@ -52755,13 +52755,13 @@
         <v>6.73</v>
       </c>
       <c r="J34" t="n">
-        <v>3.48</v>
+        <v>3.86</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>66.92999999999999</v>
+        <v>67.31</v>
       </c>
     </row>
   </sheetData>
@@ -54287,13 +54287,13 @@
         <v>18.11</v>
       </c>
       <c r="J34" t="n">
-        <v>11.43</v>
+        <v>11.88</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>162.03</v>
+        <v>162.48</v>
       </c>
     </row>
   </sheetData>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -28214,13 +28214,13 @@
         <v>9</v>
       </c>
       <c r="D1265" t="n">
-        <v>22.57</v>
+        <v>27.13</v>
       </c>
       <c r="E1265" t="n">
-        <v>11.12</v>
+        <v>11.65</v>
       </c>
       <c r="F1265" t="n">
-        <v>228.56</v>
+        <v>233.24</v>
       </c>
     </row>
     <row r="1266">
@@ -42116,13 +42116,13 @@
         <v>42.52</v>
       </c>
       <c r="J23" t="n">
-        <v>22.57</v>
+        <v>27.13</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>134.58</v>
+        <v>139.14</v>
       </c>
     </row>
   </sheetData>
@@ -43148,13 +43148,13 @@
         <v>17.04</v>
       </c>
       <c r="J23" t="n">
-        <v>11.12</v>
+        <v>11.65</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>160.36</v>
+        <v>160.89</v>
       </c>
     </row>
   </sheetData>
@@ -44112,7 +44112,7 @@
         <v>207.24</v>
       </c>
       <c r="J23" t="n">
-        <v>228.56</v>
+        <v>233.24</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -8308,13 +8308,13 @@
         <v>9</v>
       </c>
       <c r="D358" t="n">
-        <v>4.299</v>
+        <v>4.603</v>
       </c>
       <c r="E358" t="n">
-        <v>4.229</v>
+        <v>4.275</v>
       </c>
       <c r="F358" t="n">
-        <v>48.405</v>
+        <v>48.835</v>
       </c>
     </row>
     <row r="359">
@@ -13858,13 +13858,13 @@
         <v>9</v>
       </c>
       <c r="D611" t="n">
-        <v>6.409</v>
+        <v>8.721</v>
       </c>
       <c r="E611" t="n">
-        <v>6.396</v>
+        <v>6.884</v>
       </c>
       <c r="F611" t="n">
-        <v>25.401</v>
+        <v>27.314</v>
       </c>
     </row>
     <row r="612">
@@ -22504,13 +22504,13 @@
         <v>9</v>
       </c>
       <c r="D1004" t="n">
-        <v>3.86</v>
+        <v>4.5</v>
       </c>
       <c r="E1004" t="n">
-        <v>11.88</v>
+        <v>12.36</v>
       </c>
       <c r="F1004" t="n">
-        <v>81.47</v>
+        <v>82.08</v>
       </c>
     </row>
     <row r="1005">
@@ -36004,13 +36004,13 @@
         <v>9</v>
       </c>
       <c r="D1658" t="n">
-        <v>14.568</v>
+        <v>17.824</v>
       </c>
       <c r="E1658" t="n">
-        <v>22.505</v>
+        <v>23.519</v>
       </c>
       <c r="F1658" t="n">
-        <v>155.276</v>
+        <v>158.229</v>
       </c>
     </row>
   </sheetData>
@@ -37435,7 +37435,7 @@
         <v>84.2</v>
       </c>
       <c r="J34" t="n">
-        <v>81.47</v>
+        <v>82.08</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
@@ -38676,13 +38676,13 @@
         <v>16.109</v>
       </c>
       <c r="J34" t="n">
-        <v>14.568</v>
+        <v>17.824</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>197.605</v>
+        <v>200.861</v>
       </c>
     </row>
   </sheetData>
@@ -39928,13 +39928,13 @@
         <v>36.758</v>
       </c>
       <c r="J34" t="n">
-        <v>22.505</v>
+        <v>23.519</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>337.77</v>
+        <v>338.784</v>
       </c>
     </row>
   </sheetData>
@@ -41071,7 +41071,7 @@
         <v>155.567</v>
       </c>
       <c r="J34" t="n">
-        <v>155.276</v>
+        <v>158.229</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
@@ -45509,13 +45509,13 @@
         <v>3.782</v>
       </c>
       <c r="J31" t="n">
-        <v>4.299</v>
+        <v>4.603</v>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>47.427</v>
+        <v>47.731</v>
       </c>
     </row>
   </sheetData>
@@ -46909,13 +46909,13 @@
         <v>4.822</v>
       </c>
       <c r="J31" t="n">
-        <v>4.229</v>
+        <v>4.275</v>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>63.327</v>
+        <v>63.373</v>
       </c>
     </row>
   </sheetData>
@@ -48217,7 +48217,7 @@
         <v>48.491</v>
       </c>
       <c r="J31" t="n">
-        <v>48.405</v>
+        <v>48.835</v>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
@@ -49238,13 +49238,13 @@
         <v>5.597</v>
       </c>
       <c r="J23" t="n">
-        <v>6.409</v>
+        <v>8.721</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>82.86800000000001</v>
+        <v>85.18000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -50270,13 +50270,13 @@
         <v>13.826</v>
       </c>
       <c r="J23" t="n">
-        <v>6.396</v>
+        <v>6.884</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>111.963</v>
+        <v>112.451</v>
       </c>
     </row>
   </sheetData>
@@ -51226,7 +51226,7 @@
         <v>22.876</v>
       </c>
       <c r="J23" t="n">
-        <v>25.401</v>
+        <v>27.314</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
@@ -52755,13 +52755,13 @@
         <v>6.73</v>
       </c>
       <c r="J34" t="n">
-        <v>3.86</v>
+        <v>4.5</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>67.31</v>
+        <v>67.94999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -54287,13 +54287,13 @@
         <v>18.11</v>
       </c>
       <c r="J34" t="n">
-        <v>11.88</v>
+        <v>12.36</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>162.48</v>
+        <v>162.96</v>
       </c>
     </row>
   </sheetData>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -8308,13 +8308,13 @@
         <v>9</v>
       </c>
       <c r="D358" t="n">
-        <v>4.603</v>
+        <v>4.864</v>
       </c>
       <c r="E358" t="n">
-        <v>4.275</v>
+        <v>4.45</v>
       </c>
       <c r="F358" t="n">
-        <v>48.835</v>
+        <v>48.921</v>
       </c>
     </row>
     <row r="359">
@@ -13858,13 +13858,13 @@
         <v>9</v>
       </c>
       <c r="D611" t="n">
-        <v>8.721</v>
+        <v>9.563000000000001</v>
       </c>
       <c r="E611" t="n">
-        <v>6.884</v>
+        <v>7.354</v>
       </c>
       <c r="F611" t="n">
-        <v>27.314</v>
+        <v>27.845</v>
       </c>
     </row>
     <row r="612">
@@ -22504,13 +22504,13 @@
         <v>9</v>
       </c>
       <c r="D1004" t="n">
-        <v>4.5</v>
+        <v>5.01</v>
       </c>
       <c r="E1004" t="n">
-        <v>12.36</v>
+        <v>12.85</v>
       </c>
       <c r="F1004" t="n">
-        <v>82.08</v>
+        <v>82.53</v>
       </c>
     </row>
     <row r="1005">
@@ -28214,13 +28214,13 @@
         <v>9</v>
       </c>
       <c r="D1265" t="n">
-        <v>27.13</v>
+        <v>36.03</v>
       </c>
       <c r="E1265" t="n">
-        <v>11.65</v>
+        <v>12.2</v>
       </c>
       <c r="F1265" t="n">
-        <v>233.24</v>
+        <v>242.24</v>
       </c>
     </row>
     <row r="1266">
@@ -36004,13 +36004,13 @@
         <v>9</v>
       </c>
       <c r="D1658" t="n">
-        <v>17.824</v>
+        <v>19.437</v>
       </c>
       <c r="E1658" t="n">
-        <v>23.519</v>
+        <v>24.654</v>
       </c>
       <c r="F1658" t="n">
-        <v>158.229</v>
+        <v>159.296</v>
       </c>
     </row>
   </sheetData>
@@ -37435,7 +37435,7 @@
         <v>84.2</v>
       </c>
       <c r="J34" t="n">
-        <v>82.08</v>
+        <v>82.53</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
@@ -38676,13 +38676,13 @@
         <v>16.109</v>
       </c>
       <c r="J34" t="n">
-        <v>17.824</v>
+        <v>19.437</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>200.861</v>
+        <v>202.474</v>
       </c>
     </row>
   </sheetData>
@@ -39928,13 +39928,13 @@
         <v>36.758</v>
       </c>
       <c r="J34" t="n">
-        <v>23.519</v>
+        <v>24.654</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>338.784</v>
+        <v>339.919</v>
       </c>
     </row>
   </sheetData>
@@ -41071,7 +41071,7 @@
         <v>155.567</v>
       </c>
       <c r="J34" t="n">
-        <v>158.229</v>
+        <v>159.296</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
@@ -42116,13 +42116,13 @@
         <v>42.52</v>
       </c>
       <c r="J23" t="n">
-        <v>27.13</v>
+        <v>36.03</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>139.14</v>
+        <v>148.04</v>
       </c>
     </row>
   </sheetData>
@@ -43148,13 +43148,13 @@
         <v>17.04</v>
       </c>
       <c r="J23" t="n">
-        <v>11.65</v>
+        <v>12.2</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>160.89</v>
+        <v>161.44</v>
       </c>
     </row>
   </sheetData>
@@ -44112,7 +44112,7 @@
         <v>207.24</v>
       </c>
       <c r="J23" t="n">
-        <v>233.24</v>
+        <v>242.24</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
@@ -45509,13 +45509,13 @@
         <v>3.782</v>
       </c>
       <c r="J31" t="n">
-        <v>4.603</v>
+        <v>4.864</v>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>47.731</v>
+        <v>47.992</v>
       </c>
     </row>
   </sheetData>
@@ -46909,13 +46909,13 @@
         <v>4.822</v>
       </c>
       <c r="J31" t="n">
-        <v>4.275</v>
+        <v>4.45</v>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>63.373</v>
+        <v>63.548</v>
       </c>
     </row>
   </sheetData>
@@ -48217,7 +48217,7 @@
         <v>48.491</v>
       </c>
       <c r="J31" t="n">
-        <v>48.835</v>
+        <v>48.921</v>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
@@ -49238,13 +49238,13 @@
         <v>5.597</v>
       </c>
       <c r="J23" t="n">
-        <v>8.721</v>
+        <v>9.563000000000001</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>85.18000000000001</v>
+        <v>86.02200000000001</v>
       </c>
     </row>
   </sheetData>
@@ -50270,13 +50270,13 @@
         <v>13.826</v>
       </c>
       <c r="J23" t="n">
-        <v>6.884</v>
+        <v>7.354</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>112.451</v>
+        <v>112.921</v>
       </c>
     </row>
   </sheetData>
@@ -51226,7 +51226,7 @@
         <v>22.876</v>
       </c>
       <c r="J23" t="n">
-        <v>27.314</v>
+        <v>27.845</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
@@ -52755,13 +52755,13 @@
         <v>6.73</v>
       </c>
       <c r="J34" t="n">
-        <v>4.5</v>
+        <v>5.01</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>67.94999999999999</v>
+        <v>68.45999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -54287,13 +54287,13 @@
         <v>18.11</v>
       </c>
       <c r="J34" t="n">
-        <v>12.36</v>
+        <v>12.85</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>162.96</v>
+        <v>163.45</v>
       </c>
     </row>
   </sheetData>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -28214,13 +28214,13 @@
         <v>9</v>
       </c>
       <c r="D1265" t="n">
-        <v>36.03</v>
+        <v>18.04</v>
       </c>
       <c r="E1265" t="n">
-        <v>12.2</v>
+        <v>12.47</v>
       </c>
       <c r="F1265" t="n">
-        <v>242.24</v>
+        <v>224.96</v>
       </c>
     </row>
     <row r="1266">
@@ -42116,13 +42116,13 @@
         <v>42.52</v>
       </c>
       <c r="J23" t="n">
-        <v>36.03</v>
+        <v>18.04</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>148.04</v>
+        <v>130.05</v>
       </c>
     </row>
   </sheetData>
@@ -43148,13 +43148,13 @@
         <v>17.04</v>
       </c>
       <c r="J23" t="n">
-        <v>12.2</v>
+        <v>12.47</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>161.44</v>
+        <v>161.71</v>
       </c>
     </row>
   </sheetData>
@@ -44112,7 +44112,7 @@
         <v>207.24</v>
       </c>
       <c r="J23" t="n">
-        <v>242.24</v>
+        <v>224.96</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -8308,13 +8308,13 @@
         <v>9</v>
       </c>
       <c r="D358" t="n">
-        <v>4.864</v>
+        <v>5.771</v>
       </c>
       <c r="E358" t="n">
-        <v>4.45</v>
+        <v>4.489</v>
       </c>
       <c r="F358" t="n">
-        <v>48.921</v>
+        <v>49.789</v>
       </c>
     </row>
     <row r="359">
@@ -13858,13 +13858,13 @@
         <v>9</v>
       </c>
       <c r="D611" t="n">
-        <v>9.563000000000001</v>
+        <v>11.098</v>
       </c>
       <c r="E611" t="n">
-        <v>7.354</v>
+        <v>7.808</v>
       </c>
       <c r="F611" t="n">
-        <v>27.845</v>
+        <v>29.098</v>
       </c>
     </row>
     <row r="612">
@@ -36004,13 +36004,13 @@
         <v>9</v>
       </c>
       <c r="D1658" t="n">
-        <v>19.437</v>
+        <v>21.879</v>
       </c>
       <c r="E1658" t="n">
-        <v>24.654</v>
+        <v>25.147</v>
       </c>
       <c r="F1658" t="n">
-        <v>159.296</v>
+        <v>161.417</v>
       </c>
     </row>
   </sheetData>
@@ -38676,13 +38676,13 @@
         <v>16.109</v>
       </c>
       <c r="J34" t="n">
-        <v>19.437</v>
+        <v>21.879</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>202.474</v>
+        <v>204.916</v>
       </c>
     </row>
   </sheetData>
@@ -39928,13 +39928,13 @@
         <v>36.758</v>
       </c>
       <c r="J34" t="n">
-        <v>24.654</v>
+        <v>25.147</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>339.919</v>
+        <v>340.412</v>
       </c>
     </row>
   </sheetData>
@@ -41071,7 +41071,7 @@
         <v>155.567</v>
       </c>
       <c r="J34" t="n">
-        <v>159.296</v>
+        <v>161.417</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
@@ -45509,13 +45509,13 @@
         <v>3.782</v>
       </c>
       <c r="J31" t="n">
-        <v>4.864</v>
+        <v>5.771</v>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>47.992</v>
+        <v>48.899</v>
       </c>
     </row>
   </sheetData>
@@ -46909,13 +46909,13 @@
         <v>4.822</v>
       </c>
       <c r="J31" t="n">
-        <v>4.45</v>
+        <v>4.489</v>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>63.548</v>
+        <v>63.587</v>
       </c>
     </row>
   </sheetData>
@@ -48217,7 +48217,7 @@
         <v>48.491</v>
       </c>
       <c r="J31" t="n">
-        <v>48.921</v>
+        <v>49.789</v>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
@@ -49238,13 +49238,13 @@
         <v>5.597</v>
       </c>
       <c r="J23" t="n">
-        <v>9.563000000000001</v>
+        <v>11.098</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>86.02200000000001</v>
+        <v>87.557</v>
       </c>
     </row>
   </sheetData>
@@ -50270,13 +50270,13 @@
         <v>13.826</v>
       </c>
       <c r="J23" t="n">
-        <v>7.354</v>
+        <v>7.808</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>112.921</v>
+        <v>113.375</v>
       </c>
     </row>
   </sheetData>
@@ -51226,7 +51226,7 @@
         <v>22.876</v>
       </c>
       <c r="J23" t="n">
-        <v>27.845</v>
+        <v>29.098</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -22504,13 +22504,13 @@
         <v>9</v>
       </c>
       <c r="D1004" t="n">
-        <v>5.01</v>
+        <v>6.76</v>
       </c>
       <c r="E1004" t="n">
-        <v>12.85</v>
+        <v>13.34</v>
       </c>
       <c r="F1004" t="n">
-        <v>82.53</v>
+        <v>84.2</v>
       </c>
     </row>
     <row r="1005">
@@ -28217,7 +28217,7 @@
         <v>18.04</v>
       </c>
       <c r="E1265" t="n">
-        <v>12.47</v>
+        <v>12.28</v>
       </c>
       <c r="F1265" t="n">
         <v>224.96</v>
@@ -36004,13 +36004,13 @@
         <v>9</v>
       </c>
       <c r="D1658" t="n">
-        <v>21.879</v>
+        <v>23.629</v>
       </c>
       <c r="E1658" t="n">
-        <v>25.147</v>
+        <v>25.637</v>
       </c>
       <c r="F1658" t="n">
-        <v>161.417</v>
+        <v>163.087</v>
       </c>
     </row>
   </sheetData>
@@ -37435,7 +37435,7 @@
         <v>84.2</v>
       </c>
       <c r="J34" t="n">
-        <v>82.53</v>
+        <v>84.2</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
@@ -38676,13 +38676,13 @@
         <v>16.109</v>
       </c>
       <c r="J34" t="n">
-        <v>21.879</v>
+        <v>23.629</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>204.916</v>
+        <v>206.666</v>
       </c>
     </row>
   </sheetData>
@@ -39928,13 +39928,13 @@
         <v>36.758</v>
       </c>
       <c r="J34" t="n">
-        <v>25.147</v>
+        <v>25.637</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>340.412</v>
+        <v>340.902</v>
       </c>
     </row>
   </sheetData>
@@ -41071,7 +41071,7 @@
         <v>155.567</v>
       </c>
       <c r="J34" t="n">
-        <v>161.417</v>
+        <v>163.087</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
@@ -43148,13 +43148,13 @@
         <v>17.04</v>
       </c>
       <c r="J23" t="n">
-        <v>12.47</v>
+        <v>12.28</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>161.71</v>
+        <v>161.52</v>
       </c>
     </row>
   </sheetData>
@@ -52755,13 +52755,13 @@
         <v>6.73</v>
       </c>
       <c r="J34" t="n">
-        <v>5.01</v>
+        <v>6.76</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>68.45999999999999</v>
+        <v>70.20999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -54287,13 +54287,13 @@
         <v>18.11</v>
       </c>
       <c r="J34" t="n">
-        <v>12.85</v>
+        <v>13.34</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>163.45</v>
+        <v>163.94</v>
       </c>
     </row>
   </sheetData>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -28214,13 +28214,13 @@
         <v>9</v>
       </c>
       <c r="D1265" t="n">
-        <v>18.04</v>
+        <v>18.23</v>
       </c>
       <c r="E1265" t="n">
-        <v>12.28</v>
+        <v>12.77</v>
       </c>
       <c r="F1265" t="n">
-        <v>224.96</v>
+        <v>225.32</v>
       </c>
     </row>
     <row r="1266">
@@ -42116,13 +42116,13 @@
         <v>42.52</v>
       </c>
       <c r="J23" t="n">
-        <v>18.04</v>
+        <v>18.23</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>130.05</v>
+        <v>130.24</v>
       </c>
     </row>
   </sheetData>
@@ -43148,13 +43148,13 @@
         <v>17.04</v>
       </c>
       <c r="J23" t="n">
-        <v>12.28</v>
+        <v>12.77</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>161.52</v>
+        <v>162.01</v>
       </c>
     </row>
   </sheetData>
@@ -44112,7 +44112,7 @@
         <v>207.24</v>
       </c>
       <c r="J23" t="n">
-        <v>224.96</v>
+        <v>225.32</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -8308,13 +8308,13 @@
         <v>9</v>
       </c>
       <c r="D358" t="n">
-        <v>5.771</v>
+        <v>7.667</v>
       </c>
       <c r="E358" t="n">
-        <v>4.489</v>
+        <v>4.528</v>
       </c>
       <c r="F358" t="n">
-        <v>49.789</v>
+        <v>51.645</v>
       </c>
     </row>
     <row r="359">
@@ -13858,13 +13858,13 @@
         <v>9</v>
       </c>
       <c r="D611" t="n">
-        <v>11.098</v>
+        <v>12.12</v>
       </c>
       <c r="E611" t="n">
-        <v>7.808</v>
+        <v>8.263</v>
       </c>
       <c r="F611" t="n">
-        <v>29.098</v>
+        <v>29.823</v>
       </c>
     </row>
     <row r="612">
@@ -22504,13 +22504,13 @@
         <v>9</v>
       </c>
       <c r="D1004" t="n">
-        <v>6.76</v>
+        <v>8.34</v>
       </c>
       <c r="E1004" t="n">
-        <v>13.34</v>
+        <v>13.81</v>
       </c>
       <c r="F1004" t="n">
-        <v>84.2</v>
+        <v>85.72</v>
       </c>
     </row>
     <row r="1005">
@@ -36004,13 +36004,13 @@
         <v>9</v>
       </c>
       <c r="D1658" t="n">
-        <v>23.629</v>
+        <v>28.127</v>
       </c>
       <c r="E1658" t="n">
-        <v>25.637</v>
+        <v>26.601</v>
       </c>
       <c r="F1658" t="n">
-        <v>163.087</v>
+        <v>167.188</v>
       </c>
     </row>
   </sheetData>
@@ -37435,7 +37435,7 @@
         <v>84.2</v>
       </c>
       <c r="J34" t="n">
-        <v>84.2</v>
+        <v>85.72</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
@@ -38676,13 +38676,13 @@
         <v>16.109</v>
       </c>
       <c r="J34" t="n">
-        <v>23.629</v>
+        <v>28.127</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>206.666</v>
+        <v>211.164</v>
       </c>
     </row>
   </sheetData>
@@ -39928,13 +39928,13 @@
         <v>36.758</v>
       </c>
       <c r="J34" t="n">
-        <v>25.637</v>
+        <v>26.601</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>340.902</v>
+        <v>341.866</v>
       </c>
     </row>
   </sheetData>
@@ -41071,7 +41071,7 @@
         <v>155.567</v>
       </c>
       <c r="J34" t="n">
-        <v>163.087</v>
+        <v>167.188</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
@@ -45509,13 +45509,13 @@
         <v>3.782</v>
       </c>
       <c r="J31" t="n">
-        <v>5.771</v>
+        <v>7.667</v>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>48.899</v>
+        <v>50.795</v>
       </c>
     </row>
   </sheetData>
@@ -46909,13 +46909,13 @@
         <v>4.822</v>
       </c>
       <c r="J31" t="n">
-        <v>4.489</v>
+        <v>4.528</v>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>63.587</v>
+        <v>63.626</v>
       </c>
     </row>
   </sheetData>
@@ -48217,7 +48217,7 @@
         <v>48.491</v>
       </c>
       <c r="J31" t="n">
-        <v>49.789</v>
+        <v>51.645</v>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
@@ -49238,13 +49238,13 @@
         <v>5.597</v>
       </c>
       <c r="J23" t="n">
-        <v>11.098</v>
+        <v>12.12</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>87.557</v>
+        <v>88.57900000000001</v>
       </c>
     </row>
   </sheetData>
@@ -50270,13 +50270,13 @@
         <v>13.826</v>
       </c>
       <c r="J23" t="n">
-        <v>7.808</v>
+        <v>8.263</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>113.375</v>
+        <v>113.83</v>
       </c>
     </row>
   </sheetData>
@@ -51226,7 +51226,7 @@
         <v>22.876</v>
       </c>
       <c r="J23" t="n">
-        <v>29.098</v>
+        <v>29.823</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
@@ -52755,13 +52755,13 @@
         <v>6.73</v>
       </c>
       <c r="J34" t="n">
-        <v>6.76</v>
+        <v>8.34</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>70.20999999999999</v>
+        <v>71.78999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -54287,13 +54287,13 @@
         <v>18.11</v>
       </c>
       <c r="J34" t="n">
-        <v>13.34</v>
+        <v>13.81</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>163.94</v>
+        <v>164.41</v>
       </c>
     </row>
   </sheetData>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -28214,13 +28214,13 @@
         <v>9</v>
       </c>
       <c r="D1265" t="n">
-        <v>18.23</v>
+        <v>24.22</v>
       </c>
       <c r="E1265" t="n">
-        <v>12.77</v>
+        <v>13.32</v>
       </c>
       <c r="F1265" t="n">
-        <v>225.32</v>
+        <v>231.44</v>
       </c>
     </row>
     <row r="1266">
@@ -42116,13 +42116,13 @@
         <v>42.52</v>
       </c>
       <c r="J23" t="n">
-        <v>18.23</v>
+        <v>24.22</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>130.24</v>
+        <v>136.23</v>
       </c>
     </row>
   </sheetData>
@@ -43148,13 +43148,13 @@
         <v>17.04</v>
       </c>
       <c r="J23" t="n">
-        <v>12.77</v>
+        <v>13.32</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>162.01</v>
+        <v>162.56</v>
       </c>
     </row>
   </sheetData>
@@ -44112,7 +44112,7 @@
         <v>207.24</v>
       </c>
       <c r="J23" t="n">
-        <v>225.32</v>
+        <v>231.44</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -8308,13 +8308,13 @@
         <v>9</v>
       </c>
       <c r="D358" t="n">
-        <v>7.667</v>
+        <v>14.808</v>
       </c>
       <c r="E358" t="n">
-        <v>4.528</v>
+        <v>4.568</v>
       </c>
       <c r="F358" t="n">
-        <v>51.645</v>
+        <v>58.746</v>
       </c>
     </row>
     <row r="359">
@@ -13858,13 +13858,13 @@
         <v>9</v>
       </c>
       <c r="D611" t="n">
-        <v>12.12</v>
+        <v>13.403</v>
       </c>
       <c r="E611" t="n">
-        <v>8.263</v>
+        <v>8.718</v>
       </c>
       <c r="F611" t="n">
-        <v>29.823</v>
+        <v>30.822</v>
       </c>
     </row>
     <row r="612">
@@ -22504,13 +22504,13 @@
         <v>9</v>
       </c>
       <c r="D1004" t="n">
-        <v>8.34</v>
+        <v>12.53</v>
       </c>
       <c r="E1004" t="n">
-        <v>13.81</v>
+        <v>14.26</v>
       </c>
       <c r="F1004" t="n">
-        <v>85.72</v>
+        <v>89.88</v>
       </c>
     </row>
     <row r="1005">
@@ -36004,13 +36004,13 @@
         <v>9</v>
       </c>
       <c r="D1658" t="n">
-        <v>28.127</v>
+        <v>40.741</v>
       </c>
       <c r="E1658" t="n">
-        <v>26.601</v>
+        <v>27.546</v>
       </c>
       <c r="F1658" t="n">
-        <v>167.188</v>
+        <v>179.448</v>
       </c>
     </row>
   </sheetData>
@@ -37435,7 +37435,7 @@
         <v>84.2</v>
       </c>
       <c r="J34" t="n">
-        <v>85.72</v>
+        <v>89.88</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
@@ -38676,13 +38676,13 @@
         <v>16.109</v>
       </c>
       <c r="J34" t="n">
-        <v>28.127</v>
+        <v>40.741</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>211.164</v>
+        <v>223.778</v>
       </c>
     </row>
   </sheetData>
@@ -39928,13 +39928,13 @@
         <v>36.758</v>
       </c>
       <c r="J34" t="n">
-        <v>26.601</v>
+        <v>27.546</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>341.866</v>
+        <v>342.811</v>
       </c>
     </row>
   </sheetData>
@@ -41071,7 +41071,7 @@
         <v>155.567</v>
       </c>
       <c r="J34" t="n">
-        <v>167.188</v>
+        <v>179.448</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
@@ -45509,13 +45509,13 @@
         <v>3.782</v>
       </c>
       <c r="J31" t="n">
-        <v>7.667</v>
+        <v>14.808</v>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>50.795</v>
+        <v>57.936</v>
       </c>
     </row>
   </sheetData>
@@ -46909,13 +46909,13 @@
         <v>4.822</v>
       </c>
       <c r="J31" t="n">
-        <v>4.528</v>
+        <v>4.568</v>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>63.626</v>
+        <v>63.666</v>
       </c>
     </row>
   </sheetData>
@@ -48217,7 +48217,7 @@
         <v>48.491</v>
       </c>
       <c r="J31" t="n">
-        <v>51.645</v>
+        <v>58.746</v>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
@@ -49238,13 +49238,13 @@
         <v>5.597</v>
       </c>
       <c r="J23" t="n">
-        <v>12.12</v>
+        <v>13.403</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>88.57900000000001</v>
+        <v>89.86200000000001</v>
       </c>
     </row>
   </sheetData>
@@ -50270,13 +50270,13 @@
         <v>13.826</v>
       </c>
       <c r="J23" t="n">
-        <v>8.263</v>
+        <v>8.718</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>113.83</v>
+        <v>114.285</v>
       </c>
     </row>
   </sheetData>
@@ -51226,7 +51226,7 @@
         <v>22.876</v>
       </c>
       <c r="J23" t="n">
-        <v>29.823</v>
+        <v>30.822</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
@@ -52755,13 +52755,13 @@
         <v>6.73</v>
       </c>
       <c r="J34" t="n">
-        <v>8.34</v>
+        <v>12.53</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>71.78999999999999</v>
+        <v>75.97999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -54287,13 +54287,13 @@
         <v>18.11</v>
       </c>
       <c r="J34" t="n">
-        <v>13.81</v>
+        <v>14.26</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>164.41</v>
+        <v>164.86</v>
       </c>
     </row>
   </sheetData>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -28214,13 +28214,13 @@
         <v>9</v>
       </c>
       <c r="D1265" t="n">
-        <v>24.22</v>
+        <v>49.86</v>
       </c>
       <c r="E1265" t="n">
-        <v>13.32</v>
+        <v>13.75</v>
       </c>
       <c r="F1265" t="n">
-        <v>231.44</v>
+        <v>257.24</v>
       </c>
     </row>
     <row r="1266">
@@ -42116,13 +42116,13 @@
         <v>42.52</v>
       </c>
       <c r="J23" t="n">
-        <v>24.22</v>
+        <v>49.86</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>136.23</v>
+        <v>161.87</v>
       </c>
     </row>
   </sheetData>
@@ -43148,13 +43148,13 @@
         <v>17.04</v>
       </c>
       <c r="J23" t="n">
-        <v>13.32</v>
+        <v>13.75</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>162.56</v>
+        <v>162.99</v>
       </c>
     </row>
   </sheetData>
@@ -44112,7 +44112,7 @@
         <v>207.24</v>
       </c>
       <c r="J23" t="n">
-        <v>231.44</v>
+        <v>257.24</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -8308,13 +8308,13 @@
         <v>9</v>
       </c>
       <c r="D358" t="n">
-        <v>14.808</v>
+        <v>24.894</v>
       </c>
       <c r="E358" t="n">
-        <v>4.568</v>
+        <v>4.612</v>
       </c>
       <c r="F358" t="n">
-        <v>58.746</v>
+        <v>68.789</v>
       </c>
     </row>
     <row r="359">
@@ -13858,13 +13858,13 @@
         <v>9</v>
       </c>
       <c r="D611" t="n">
-        <v>13.403</v>
+        <v>24.303</v>
       </c>
       <c r="E611" t="n">
-        <v>8.718</v>
+        <v>9.455</v>
       </c>
       <c r="F611" t="n">
-        <v>30.822</v>
+        <v>41.155</v>
       </c>
     </row>
     <row r="612">
@@ -22504,13 +22504,13 @@
         <v>9</v>
       </c>
       <c r="D1004" t="n">
-        <v>12.53</v>
+        <v>28.12</v>
       </c>
       <c r="E1004" t="n">
-        <v>14.26</v>
+        <v>14.69</v>
       </c>
       <c r="F1004" t="n">
-        <v>89.88</v>
+        <v>105.73</v>
       </c>
     </row>
     <row r="1005">
@@ -36004,13 +36004,13 @@
         <v>9</v>
       </c>
       <c r="D1658" t="n">
-        <v>40.741</v>
+        <v>77.31699999999999</v>
       </c>
       <c r="E1658" t="n">
-        <v>27.546</v>
+        <v>28.757</v>
       </c>
       <c r="F1658" t="n">
-        <v>179.448</v>
+        <v>215.674</v>
       </c>
     </row>
   </sheetData>
@@ -37435,7 +37435,7 @@
         <v>84.2</v>
       </c>
       <c r="J34" t="n">
-        <v>89.88</v>
+        <v>105.73</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
@@ -38676,13 +38676,13 @@
         <v>16.109</v>
       </c>
       <c r="J34" t="n">
-        <v>40.741</v>
+        <v>77.31699999999999</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>223.778</v>
+        <v>260.354</v>
       </c>
     </row>
   </sheetData>
@@ -39928,13 +39928,13 @@
         <v>36.758</v>
       </c>
       <c r="J34" t="n">
-        <v>27.546</v>
+        <v>28.757</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>342.811</v>
+        <v>344.022</v>
       </c>
     </row>
   </sheetData>
@@ -41071,7 +41071,7 @@
         <v>155.567</v>
       </c>
       <c r="J34" t="n">
-        <v>179.448</v>
+        <v>215.674</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
@@ -45509,13 +45509,13 @@
         <v>3.782</v>
       </c>
       <c r="J31" t="n">
-        <v>14.808</v>
+        <v>24.894</v>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>57.936</v>
+        <v>68.02199999999999</v>
       </c>
     </row>
   </sheetData>
@@ -46909,13 +46909,13 @@
         <v>4.822</v>
       </c>
       <c r="J31" t="n">
-        <v>4.568</v>
+        <v>4.612</v>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>63.666</v>
+        <v>63.71</v>
       </c>
     </row>
   </sheetData>
@@ -48217,7 +48217,7 @@
         <v>48.491</v>
       </c>
       <c r="J31" t="n">
-        <v>58.746</v>
+        <v>68.789</v>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
@@ -49238,13 +49238,13 @@
         <v>5.597</v>
       </c>
       <c r="J23" t="n">
-        <v>13.403</v>
+        <v>24.303</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>89.86200000000001</v>
+        <v>100.762</v>
       </c>
     </row>
   </sheetData>
@@ -50270,13 +50270,13 @@
         <v>13.826</v>
       </c>
       <c r="J23" t="n">
-        <v>8.718</v>
+        <v>9.455</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>114.285</v>
+        <v>115.022</v>
       </c>
     </row>
   </sheetData>
@@ -51226,7 +51226,7 @@
         <v>22.876</v>
       </c>
       <c r="J23" t="n">
-        <v>30.822</v>
+        <v>41.155</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
@@ -52755,13 +52755,13 @@
         <v>6.73</v>
       </c>
       <c r="J34" t="n">
-        <v>12.53</v>
+        <v>28.12</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>75.97999999999999</v>
+        <v>91.56999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -54287,13 +54287,13 @@
         <v>18.11</v>
       </c>
       <c r="J34" t="n">
-        <v>14.26</v>
+        <v>14.69</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>164.86</v>
+        <v>165.29</v>
       </c>
     </row>
   </sheetData>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -28217,10 +28217,10 @@
         <v>49.86</v>
       </c>
       <c r="E1265" t="n">
-        <v>13.75</v>
+        <v>14.36</v>
       </c>
       <c r="F1265" t="n">
-        <v>257.24</v>
+        <v>294.99</v>
       </c>
     </row>
     <row r="1266">
@@ -43148,13 +43148,13 @@
         <v>17.04</v>
       </c>
       <c r="J23" t="n">
-        <v>13.75</v>
+        <v>14.36</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>162.99</v>
+        <v>163.6</v>
       </c>
     </row>
   </sheetData>
@@ -44112,7 +44112,7 @@
         <v>207.24</v>
       </c>
       <c r="J23" t="n">
-        <v>257.24</v>
+        <v>294.99</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -8308,13 +8308,13 @@
         <v>9</v>
       </c>
       <c r="D358" t="n">
-        <v>24.894</v>
+        <v>30.798</v>
       </c>
       <c r="E358" t="n">
-        <v>4.612</v>
+        <v>4.661</v>
       </c>
       <c r="F358" t="n">
-        <v>68.789</v>
+        <v>74.64400000000001</v>
       </c>
     </row>
     <row r="359">
@@ -13858,13 +13858,13 @@
         <v>9</v>
       </c>
       <c r="D611" t="n">
-        <v>24.303</v>
+        <v>30.834</v>
       </c>
       <c r="E611" t="n">
-        <v>9.455</v>
+        <v>10.732</v>
       </c>
       <c r="F611" t="n">
-        <v>41.155</v>
+        <v>46.565</v>
       </c>
     </row>
     <row r="612">
@@ -36004,13 +36004,13 @@
         <v>9</v>
       </c>
       <c r="D1658" t="n">
-        <v>77.31699999999999</v>
+        <v>89.752</v>
       </c>
       <c r="E1658" t="n">
-        <v>28.757</v>
+        <v>30.083</v>
       </c>
       <c r="F1658" t="n">
-        <v>215.674</v>
+        <v>226.939</v>
       </c>
     </row>
   </sheetData>
@@ -38676,13 +38676,13 @@
         <v>16.109</v>
       </c>
       <c r="J34" t="n">
-        <v>77.31699999999999</v>
+        <v>89.752</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>260.354</v>
+        <v>272.789</v>
       </c>
     </row>
   </sheetData>
@@ -39928,13 +39928,13 @@
         <v>36.758</v>
       </c>
       <c r="J34" t="n">
-        <v>28.757</v>
+        <v>30.083</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>344.022</v>
+        <v>345.348</v>
       </c>
     </row>
   </sheetData>
@@ -41071,7 +41071,7 @@
         <v>155.567</v>
       </c>
       <c r="J34" t="n">
-        <v>215.674</v>
+        <v>226.939</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
@@ -45509,13 +45509,13 @@
         <v>3.782</v>
       </c>
       <c r="J31" t="n">
-        <v>24.894</v>
+        <v>30.798</v>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>68.02199999999999</v>
+        <v>73.926</v>
       </c>
     </row>
   </sheetData>
@@ -46909,13 +46909,13 @@
         <v>4.822</v>
       </c>
       <c r="J31" t="n">
-        <v>4.612</v>
+        <v>4.661</v>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>63.71</v>
+        <v>63.759</v>
       </c>
     </row>
   </sheetData>
@@ -48217,7 +48217,7 @@
         <v>48.491</v>
       </c>
       <c r="J31" t="n">
-        <v>68.789</v>
+        <v>74.64400000000001</v>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
@@ -49238,13 +49238,13 @@
         <v>5.597</v>
       </c>
       <c r="J23" t="n">
-        <v>24.303</v>
+        <v>30.834</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>100.762</v>
+        <v>107.293</v>
       </c>
     </row>
   </sheetData>
@@ -50270,13 +50270,13 @@
         <v>13.826</v>
       </c>
       <c r="J23" t="n">
-        <v>9.455</v>
+        <v>10.732</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>115.022</v>
+        <v>116.299</v>
       </c>
     </row>
   </sheetData>
@@ -51226,7 +51226,7 @@
         <v>22.876</v>
       </c>
       <c r="J23" t="n">
-        <v>41.155</v>
+        <v>46.565</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -22504,13 +22504,13 @@
         <v>9</v>
       </c>
       <c r="D1004" t="n">
-        <v>28.12</v>
+        <v>39.31</v>
       </c>
       <c r="E1004" t="n">
-        <v>14.69</v>
+        <v>15.16</v>
       </c>
       <c r="F1004" t="n">
-        <v>105.73</v>
+        <v>117.68</v>
       </c>
     </row>
     <row r="1005">
@@ -28217,7 +28217,7 @@
         <v>49.86</v>
       </c>
       <c r="E1265" t="n">
-        <v>14.36</v>
+        <v>14.19</v>
       </c>
       <c r="F1265" t="n">
         <v>294.99</v>
@@ -36004,13 +36004,13 @@
         <v>9</v>
       </c>
       <c r="D1658" t="n">
-        <v>89.752</v>
+        <v>100.942</v>
       </c>
       <c r="E1658" t="n">
-        <v>30.083</v>
+        <v>30.553</v>
       </c>
       <c r="F1658" t="n">
-        <v>226.939</v>
+        <v>238.889</v>
       </c>
     </row>
   </sheetData>
@@ -37435,7 +37435,7 @@
         <v>84.2</v>
       </c>
       <c r="J34" t="n">
-        <v>105.73</v>
+        <v>117.68</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
@@ -38676,13 +38676,13 @@
         <v>16.109</v>
       </c>
       <c r="J34" t="n">
-        <v>89.752</v>
+        <v>100.942</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>272.789</v>
+        <v>283.979</v>
       </c>
     </row>
   </sheetData>
@@ -39928,13 +39928,13 @@
         <v>36.758</v>
       </c>
       <c r="J34" t="n">
-        <v>30.083</v>
+        <v>30.553</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>345.348</v>
+        <v>345.818</v>
       </c>
     </row>
   </sheetData>
@@ -41071,7 +41071,7 @@
         <v>155.567</v>
       </c>
       <c r="J34" t="n">
-        <v>226.939</v>
+        <v>238.889</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
@@ -43148,13 +43148,13 @@
         <v>17.04</v>
       </c>
       <c r="J23" t="n">
-        <v>14.36</v>
+        <v>14.19</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>163.6</v>
+        <v>163.43</v>
       </c>
     </row>
   </sheetData>
@@ -52755,13 +52755,13 @@
         <v>6.73</v>
       </c>
       <c r="J34" t="n">
-        <v>28.12</v>
+        <v>39.31</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>91.56999999999999</v>
+        <v>102.76</v>
       </c>
     </row>
   </sheetData>
@@ -54287,13 +54287,13 @@
         <v>18.11</v>
       </c>
       <c r="J34" t="n">
-        <v>14.69</v>
+        <v>15.16</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>165.29</v>
+        <v>165.76</v>
       </c>
     </row>
   </sheetData>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -8308,10 +8308,10 @@
         <v>9</v>
       </c>
       <c r="D358" t="n">
-        <v>30.798</v>
+        <v>30.847</v>
       </c>
       <c r="E358" t="n">
-        <v>4.661</v>
+        <v>4.71</v>
       </c>
       <c r="F358" t="n">
         <v>74.64400000000001</v>
@@ -13858,10 +13858,10 @@
         <v>9</v>
       </c>
       <c r="D611" t="n">
-        <v>30.834</v>
+        <v>32.111</v>
       </c>
       <c r="E611" t="n">
-        <v>10.732</v>
+        <v>12.009</v>
       </c>
       <c r="F611" t="n">
         <v>46.565</v>
@@ -28214,13 +28214,13 @@
         <v>9</v>
       </c>
       <c r="D1265" t="n">
-        <v>49.86</v>
+        <v>77.36</v>
       </c>
       <c r="E1265" t="n">
-        <v>14.19</v>
+        <v>41.69</v>
       </c>
       <c r="F1265" t="n">
-        <v>294.99</v>
+        <v>331</v>
       </c>
     </row>
     <row r="1266">
@@ -36004,10 +36004,10 @@
         <v>9</v>
       </c>
       <c r="D1658" t="n">
-        <v>100.942</v>
+        <v>102.268</v>
       </c>
       <c r="E1658" t="n">
-        <v>30.553</v>
+        <v>31.879</v>
       </c>
       <c r="F1658" t="n">
         <v>238.889</v>
@@ -38676,13 +38676,13 @@
         <v>16.109</v>
       </c>
       <c r="J34" t="n">
-        <v>100.942</v>
+        <v>102.268</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>283.979</v>
+        <v>285.305</v>
       </c>
     </row>
   </sheetData>
@@ -39928,13 +39928,13 @@
         <v>36.758</v>
       </c>
       <c r="J34" t="n">
-        <v>30.553</v>
+        <v>31.879</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>345.818</v>
+        <v>347.144</v>
       </c>
     </row>
   </sheetData>
@@ -42116,13 +42116,13 @@
         <v>42.52</v>
       </c>
       <c r="J23" t="n">
-        <v>49.86</v>
+        <v>77.36</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>161.87</v>
+        <v>189.37</v>
       </c>
     </row>
   </sheetData>
@@ -43148,13 +43148,13 @@
         <v>17.04</v>
       </c>
       <c r="J23" t="n">
-        <v>14.19</v>
+        <v>41.69</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>163.43</v>
+        <v>190.93</v>
       </c>
     </row>
   </sheetData>
@@ -44112,7 +44112,7 @@
         <v>207.24</v>
       </c>
       <c r="J23" t="n">
-        <v>294.99</v>
+        <v>331</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
@@ -45509,13 +45509,13 @@
         <v>3.782</v>
       </c>
       <c r="J31" t="n">
-        <v>30.798</v>
+        <v>30.847</v>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>73.926</v>
+        <v>73.97499999999999</v>
       </c>
     </row>
   </sheetData>
@@ -46909,13 +46909,13 @@
         <v>4.822</v>
       </c>
       <c r="J31" t="n">
-        <v>4.661</v>
+        <v>4.71</v>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>63.759</v>
+        <v>63.808</v>
       </c>
     </row>
   </sheetData>
@@ -49238,13 +49238,13 @@
         <v>5.597</v>
       </c>
       <c r="J23" t="n">
-        <v>30.834</v>
+        <v>32.111</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>107.293</v>
+        <v>108.57</v>
       </c>
     </row>
   </sheetData>
@@ -50270,13 +50270,13 @@
         <v>13.826</v>
       </c>
       <c r="J23" t="n">
-        <v>10.732</v>
+        <v>12.009</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>116.299</v>
+        <v>117.576</v>
       </c>
     </row>
   </sheetData>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -22504,13 +22504,13 @@
         <v>9</v>
       </c>
       <c r="D1004" t="n">
-        <v>39.31</v>
+        <v>54.19</v>
       </c>
       <c r="E1004" t="n">
-        <v>15.16</v>
+        <v>15.57</v>
       </c>
       <c r="F1004" t="n">
-        <v>117.68</v>
+        <v>133.45</v>
       </c>
     </row>
     <row r="1005">
@@ -28217,7 +28217,7 @@
         <v>77.36</v>
       </c>
       <c r="E1265" t="n">
-        <v>41.69</v>
+        <v>14.19</v>
       </c>
       <c r="F1265" t="n">
         <v>331</v>
@@ -36004,13 +36004,13 @@
         <v>9</v>
       </c>
       <c r="D1658" t="n">
-        <v>102.268</v>
+        <v>117.148</v>
       </c>
       <c r="E1658" t="n">
-        <v>31.879</v>
+        <v>32.289</v>
       </c>
       <c r="F1658" t="n">
-        <v>238.889</v>
+        <v>254.659</v>
       </c>
     </row>
   </sheetData>
@@ -37435,7 +37435,7 @@
         <v>84.2</v>
       </c>
       <c r="J34" t="n">
-        <v>117.68</v>
+        <v>133.45</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
@@ -38676,13 +38676,13 @@
         <v>16.109</v>
       </c>
       <c r="J34" t="n">
-        <v>102.268</v>
+        <v>117.148</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>285.305</v>
+        <v>300.185</v>
       </c>
     </row>
   </sheetData>
@@ -39928,13 +39928,13 @@
         <v>36.758</v>
       </c>
       <c r="J34" t="n">
-        <v>31.879</v>
+        <v>32.289</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>347.144</v>
+        <v>347.554</v>
       </c>
     </row>
   </sheetData>
@@ -41071,7 +41071,7 @@
         <v>155.567</v>
       </c>
       <c r="J34" t="n">
-        <v>238.889</v>
+        <v>254.659</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
@@ -43148,13 +43148,13 @@
         <v>17.04</v>
       </c>
       <c r="J23" t="n">
-        <v>41.69</v>
+        <v>14.19</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>190.93</v>
+        <v>163.43</v>
       </c>
     </row>
   </sheetData>
@@ -52755,13 +52755,13 @@
         <v>6.73</v>
       </c>
       <c r="J34" t="n">
-        <v>39.31</v>
+        <v>54.19</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>102.76</v>
+        <v>117.64</v>
       </c>
     </row>
   </sheetData>
@@ -54287,13 +54287,13 @@
         <v>18.11</v>
       </c>
       <c r="J34" t="n">
-        <v>15.16</v>
+        <v>15.57</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>165.76</v>
+        <v>166.17</v>
       </c>
     </row>
   </sheetData>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -28220,7 +28220,7 @@
         <v>14.19</v>
       </c>
       <c r="F1265" t="n">
-        <v>331</v>
+        <v>338</v>
       </c>
     </row>
     <row r="1266">
@@ -44112,7 +44112,7 @@
         <v>207.24</v>
       </c>
       <c r="J23" t="n">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -8308,13 +8308,13 @@
         <v>9</v>
       </c>
       <c r="D358" t="n">
-        <v>30.847</v>
+        <v>35.212</v>
       </c>
       <c r="E358" t="n">
-        <v>4.71</v>
+        <v>6.695</v>
       </c>
       <c r="F358" t="n">
-        <v>74.64400000000001</v>
+        <v>86.89100000000001</v>
       </c>
     </row>
     <row r="359">
@@ -13858,13 +13858,13 @@
         <v>9</v>
       </c>
       <c r="D611" t="n">
-        <v>32.111</v>
+        <v>34.902</v>
       </c>
       <c r="E611" t="n">
-        <v>12.009</v>
+        <v>13.826</v>
       </c>
       <c r="F611" t="n">
-        <v>46.565</v>
+        <v>53.353</v>
       </c>
     </row>
     <row r="612">
@@ -22504,13 +22504,13 @@
         <v>9</v>
       </c>
       <c r="D1004" t="n">
-        <v>54.19</v>
+        <v>64.23999999999999</v>
       </c>
       <c r="E1004" t="n">
-        <v>15.57</v>
+        <v>16</v>
       </c>
       <c r="F1004" t="n">
-        <v>133.45</v>
+        <v>144.47</v>
       </c>
     </row>
     <row r="1005">
@@ -36004,13 +36004,13 @@
         <v>9</v>
       </c>
       <c r="D1658" t="n">
-        <v>117.148</v>
+        <v>134.354</v>
       </c>
       <c r="E1658" t="n">
-        <v>32.289</v>
+        <v>36.521</v>
       </c>
       <c r="F1658" t="n">
-        <v>254.659</v>
+        <v>284.714</v>
       </c>
     </row>
   </sheetData>
@@ -37435,7 +37435,7 @@
         <v>84.2</v>
       </c>
       <c r="J34" t="n">
-        <v>133.45</v>
+        <v>144.47</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
@@ -38676,13 +38676,13 @@
         <v>16.109</v>
       </c>
       <c r="J34" t="n">
-        <v>117.148</v>
+        <v>134.354</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>300.185</v>
+        <v>317.391</v>
       </c>
     </row>
   </sheetData>
@@ -39928,13 +39928,13 @@
         <v>36.758</v>
       </c>
       <c r="J34" t="n">
-        <v>32.289</v>
+        <v>36.521</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>347.554</v>
+        <v>351.786</v>
       </c>
     </row>
   </sheetData>
@@ -41071,7 +41071,7 @@
         <v>155.567</v>
       </c>
       <c r="J34" t="n">
-        <v>254.659</v>
+        <v>284.714</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
@@ -45509,13 +45509,13 @@
         <v>3.782</v>
       </c>
       <c r="J31" t="n">
-        <v>30.847</v>
+        <v>35.212</v>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>73.97499999999999</v>
+        <v>78.34</v>
       </c>
     </row>
   </sheetData>
@@ -46909,13 +46909,13 @@
         <v>4.822</v>
       </c>
       <c r="J31" t="n">
-        <v>4.71</v>
+        <v>6.695</v>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>63.808</v>
+        <v>65.79300000000001</v>
       </c>
     </row>
   </sheetData>
@@ -48217,7 +48217,7 @@
         <v>48.491</v>
       </c>
       <c r="J31" t="n">
-        <v>74.64400000000001</v>
+        <v>86.89100000000001</v>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
@@ -49238,13 +49238,13 @@
         <v>5.597</v>
       </c>
       <c r="J23" t="n">
-        <v>32.111</v>
+        <v>34.902</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>108.57</v>
+        <v>111.361</v>
       </c>
     </row>
   </sheetData>
@@ -50270,13 +50270,13 @@
         <v>13.826</v>
       </c>
       <c r="J23" t="n">
-        <v>12.009</v>
+        <v>13.826</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>117.576</v>
+        <v>119.393</v>
       </c>
     </row>
   </sheetData>
@@ -51226,7 +51226,7 @@
         <v>22.876</v>
       </c>
       <c r="J23" t="n">
-        <v>46.565</v>
+        <v>53.353</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
@@ -52755,13 +52755,13 @@
         <v>6.73</v>
       </c>
       <c r="J34" t="n">
-        <v>54.19</v>
+        <v>64.23999999999999</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>117.64</v>
+        <v>127.69</v>
       </c>
     </row>
   </sheetData>
@@ -54287,13 +54287,13 @@
         <v>18.11</v>
       </c>
       <c r="J34" t="n">
-        <v>15.57</v>
+        <v>16</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>166.17</v>
+        <v>166.6</v>
       </c>
     </row>
   </sheetData>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -28214,13 +28214,13 @@
         <v>9</v>
       </c>
       <c r="D1265" t="n">
-        <v>77.36</v>
+        <v>129.81</v>
       </c>
       <c r="E1265" t="n">
         <v>14.19</v>
       </c>
       <c r="F1265" t="n">
-        <v>338</v>
+        <v>325.6</v>
       </c>
     </row>
     <row r="1266">
@@ -42116,13 +42116,13 @@
         <v>42.52</v>
       </c>
       <c r="J23" t="n">
-        <v>77.36</v>
+        <v>129.81</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>189.37</v>
+        <v>241.82</v>
       </c>
     </row>
   </sheetData>
@@ -44112,7 +44112,7 @@
         <v>207.24</v>
       </c>
       <c r="J23" t="n">
-        <v>338</v>
+        <v>325.6</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -8308,13 +8308,13 @@
         <v>9</v>
       </c>
       <c r="D358" t="n">
-        <v>35.212</v>
+        <v>37.966</v>
       </c>
       <c r="E358" t="n">
-        <v>6.695</v>
+        <v>10.832</v>
       </c>
       <c r="F358" t="n">
-        <v>86.89100000000001</v>
+        <v>85.508</v>
       </c>
     </row>
     <row r="359">
@@ -13861,10 +13861,10 @@
         <v>34.902</v>
       </c>
       <c r="E611" t="n">
-        <v>13.826</v>
+        <v>15.561</v>
       </c>
       <c r="F611" t="n">
-        <v>53.353</v>
+        <v>51.397</v>
       </c>
     </row>
     <row r="612">
@@ -22504,13 +22504,13 @@
         <v>9</v>
       </c>
       <c r="D1004" t="n">
-        <v>64.23999999999999</v>
+        <v>67.5</v>
       </c>
       <c r="E1004" t="n">
-        <v>16</v>
+        <v>16.42</v>
       </c>
       <c r="F1004" t="n">
-        <v>144.47</v>
+        <v>148.64</v>
       </c>
     </row>
     <row r="1005">
@@ -36004,13 +36004,13 @@
         <v>9</v>
       </c>
       <c r="D1658" t="n">
-        <v>134.354</v>
+        <v>140.368</v>
       </c>
       <c r="E1658" t="n">
-        <v>36.521</v>
+        <v>42.813</v>
       </c>
       <c r="F1658" t="n">
-        <v>284.714</v>
+        <v>285.545</v>
       </c>
     </row>
   </sheetData>
@@ -37435,7 +37435,7 @@
         <v>84.2</v>
       </c>
       <c r="J34" t="n">
-        <v>144.47</v>
+        <v>148.64</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
@@ -38676,13 +38676,13 @@
         <v>16.109</v>
       </c>
       <c r="J34" t="n">
-        <v>134.354</v>
+        <v>140.368</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>317.391</v>
+        <v>323.405</v>
       </c>
     </row>
   </sheetData>
@@ -39928,13 +39928,13 @@
         <v>36.758</v>
       </c>
       <c r="J34" t="n">
-        <v>36.521</v>
+        <v>42.813</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>351.786</v>
+        <v>358.078</v>
       </c>
     </row>
   </sheetData>
@@ -41071,7 +41071,7 @@
         <v>155.567</v>
       </c>
       <c r="J34" t="n">
-        <v>284.714</v>
+        <v>285.545</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
@@ -45509,13 +45509,13 @@
         <v>3.782</v>
       </c>
       <c r="J31" t="n">
-        <v>35.212</v>
+        <v>37.966</v>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>78.34</v>
+        <v>81.09399999999999</v>
       </c>
     </row>
   </sheetData>
@@ -46909,13 +46909,13 @@
         <v>4.822</v>
       </c>
       <c r="J31" t="n">
-        <v>6.695</v>
+        <v>10.832</v>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>65.79300000000001</v>
+        <v>69.93000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -48217,7 +48217,7 @@
         <v>48.491</v>
       </c>
       <c r="J31" t="n">
-        <v>86.89100000000001</v>
+        <v>85.508</v>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
@@ -50270,13 +50270,13 @@
         <v>13.826</v>
       </c>
       <c r="J23" t="n">
-        <v>13.826</v>
+        <v>15.561</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>119.393</v>
+        <v>121.128</v>
       </c>
     </row>
   </sheetData>
@@ -51226,7 +51226,7 @@
         <v>22.876</v>
       </c>
       <c r="J23" t="n">
-        <v>53.353</v>
+        <v>51.397</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
@@ -52755,13 +52755,13 @@
         <v>6.73</v>
       </c>
       <c r="J34" t="n">
-        <v>64.23999999999999</v>
+        <v>67.5</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>127.69</v>
+        <v>130.95</v>
       </c>
     </row>
   </sheetData>
@@ -54287,13 +54287,13 @@
         <v>18.11</v>
       </c>
       <c r="J34" t="n">
-        <v>16</v>
+        <v>16.42</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>166.6</v>
+        <v>167.02</v>
       </c>
     </row>
   </sheetData>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -8330,12 +8330,14 @@
         <v>10</v>
       </c>
       <c r="D359" t="n">
-        <v>0</v>
+        <v>2.754</v>
       </c>
       <c r="E359" t="n">
-        <v>0</v>
-      </c>
-      <c r="F359" t="inlineStr"/>
+        <v>2.754</v>
+      </c>
+      <c r="F359" t="n">
+        <v>85.508</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -13905,7 +13907,9 @@
       <c r="E613" t="n">
         <v>0</v>
       </c>
-      <c r="F613" t="inlineStr"/>
+      <c r="F613" t="n">
+        <v>51.397</v>
+      </c>
     </row>
     <row r="614">
       <c r="A614" t="inlineStr">
@@ -36108,10 +36112,10 @@
         <v>10</v>
       </c>
       <c r="D1663" t="n">
-        <v>0</v>
+        <v>2.754</v>
       </c>
       <c r="E1663" t="n">
-        <v>0</v>
+        <v>2.754</v>
       </c>
       <c r="F1663" t="inlineStr"/>
     </row>
@@ -38781,12 +38785,12 @@
         <v>140.368</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>2.754</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>323.405</v>
+        <v>326.159</v>
       </c>
     </row>
   </sheetData>
@@ -40035,12 +40039,12 @@
         <v>42.813</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>2.754</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>358.078</v>
+        <v>360.832</v>
       </c>
     </row>
   </sheetData>
@@ -45624,12 +45628,12 @@
         <v>37.966</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>2.754</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>81.09399999999999</v>
+        <v>83.848</v>
       </c>
     </row>
   </sheetData>
@@ -47026,12 +47030,12 @@
         <v>10.832</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>2.754</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>69.93000000000001</v>
+        <v>72.68400000000001</v>
       </c>
     </row>
   </sheetData>
@@ -48335,7 +48339,9 @@
       <c r="J31" t="n">
         <v>85.508</v>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="n">
+        <v>85.508</v>
+      </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
     </row>
@@ -51348,7 +51354,9 @@
       <c r="J23" t="n">
         <v>51.397</v>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="n">
+        <v>51.397</v>
+      </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
     </row>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -8330,13 +8330,13 @@
         <v>10</v>
       </c>
       <c r="D359" t="n">
-        <v>2.754</v>
+        <v>5.988</v>
       </c>
       <c r="E359" t="n">
-        <v>2.754</v>
+        <v>6.853</v>
       </c>
       <c r="F359" t="n">
-        <v>85.508</v>
+        <v>83.523</v>
       </c>
     </row>
     <row r="360">
@@ -13902,13 +13902,13 @@
         <v>10</v>
       </c>
       <c r="D613" t="n">
-        <v>0</v>
+        <v>0.631</v>
       </c>
       <c r="E613" t="n">
-        <v>0</v>
+        <v>1.303</v>
       </c>
       <c r="F613" t="n">
-        <v>51.397</v>
+        <v>48.12</v>
       </c>
     </row>
     <row r="614">
@@ -22570,12 +22570,14 @@
         <v>10</v>
       </c>
       <c r="D1007" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="E1007" t="n">
-        <v>0</v>
-      </c>
-      <c r="F1007" t="inlineStr"/>
+        <v>0.43</v>
+      </c>
+      <c r="F1007" t="n">
+        <v>157.4</v>
+      </c>
     </row>
     <row r="1008">
       <c r="A1008" t="inlineStr">
@@ -28300,13 +28302,13 @@
         <v>10</v>
       </c>
       <c r="D1269" t="n">
-        <v>10.69</v>
+        <v>19.11</v>
       </c>
       <c r="E1269" t="n">
-        <v>24.94</v>
+        <v>42.99</v>
       </c>
       <c r="F1269" t="n">
-        <v>311.18</v>
+        <v>301.38</v>
       </c>
     </row>
     <row r="1270">
@@ -36112,12 +36114,14 @@
         <v>10</v>
       </c>
       <c r="D1663" t="n">
-        <v>2.754</v>
+        <v>9.298999999999999</v>
       </c>
       <c r="E1663" t="n">
-        <v>2.754</v>
-      </c>
-      <c r="F1663" t="inlineStr"/>
+        <v>8.586</v>
+      </c>
+      <c r="F1663" t="n">
+        <v>289.043</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -37543,7 +37547,9 @@
       <c r="J34" t="n">
         <v>148.64</v>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="n">
+        <v>157.4</v>
+      </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
     </row>
@@ -38785,12 +38791,12 @@
         <v>140.368</v>
       </c>
       <c r="K34" t="n">
-        <v>2.754</v>
+        <v>9.298999999999999</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>326.159</v>
+        <v>332.704</v>
       </c>
     </row>
   </sheetData>
@@ -40039,12 +40045,12 @@
         <v>42.813</v>
       </c>
       <c r="K34" t="n">
-        <v>2.754</v>
+        <v>8.586</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>360.832</v>
+        <v>366.664</v>
       </c>
     </row>
   </sheetData>
@@ -41183,7 +41189,9 @@
       <c r="J34" t="n">
         <v>285.545</v>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="n">
+        <v>289.043</v>
+      </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
     </row>
@@ -42229,12 +42237,12 @@
         <v>129.81</v>
       </c>
       <c r="K23" t="n">
-        <v>10.69</v>
+        <v>19.11</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>252.51</v>
+        <v>260.93</v>
       </c>
     </row>
   </sheetData>
@@ -43263,12 +43271,12 @@
         <v>14.19</v>
       </c>
       <c r="K23" t="n">
-        <v>24.94</v>
+        <v>42.99</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>188.37</v>
+        <v>206.42</v>
       </c>
     </row>
   </sheetData>
@@ -44229,7 +44237,7 @@
         <v>325.6</v>
       </c>
       <c r="K23" t="n">
-        <v>311.18</v>
+        <v>301.38</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
@@ -45628,12 +45636,12 @@
         <v>37.966</v>
       </c>
       <c r="K31" t="n">
-        <v>2.754</v>
+        <v>5.988</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>83.848</v>
+        <v>87.08199999999999</v>
       </c>
     </row>
   </sheetData>
@@ -47030,12 +47038,12 @@
         <v>10.832</v>
       </c>
       <c r="K31" t="n">
-        <v>2.754</v>
+        <v>6.853</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>72.68400000000001</v>
+        <v>76.783</v>
       </c>
     </row>
   </sheetData>
@@ -48340,7 +48348,7 @@
         <v>85.508</v>
       </c>
       <c r="K31" t="n">
-        <v>85.508</v>
+        <v>83.523</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
@@ -49363,12 +49371,12 @@
         <v>34.902</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>0.631</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>111.361</v>
+        <v>111.992</v>
       </c>
     </row>
   </sheetData>
@@ -50397,12 +50405,12 @@
         <v>15.561</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>1.303</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>121.128</v>
+        <v>122.431</v>
       </c>
     </row>
   </sheetData>
@@ -51355,7 +51363,7 @@
         <v>51.397</v>
       </c>
       <c r="K23" t="n">
-        <v>51.397</v>
+        <v>48.12</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
@@ -52886,12 +52894,12 @@
         <v>67.5</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>130.95</v>
+        <v>133.63</v>
       </c>
     </row>
   </sheetData>
@@ -54420,12 +54428,12 @@
         <v>16.42</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>0.43</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>167.02</v>
+        <v>167.45</v>
       </c>
     </row>
   </sheetData>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -22570,10 +22570,10 @@
         <v>10</v>
       </c>
       <c r="D1007" t="n">
-        <v>2.68</v>
+        <v>7.07</v>
       </c>
       <c r="E1007" t="n">
-        <v>0.43</v>
+        <v>0.85</v>
       </c>
       <c r="F1007" t="n">
         <v>157.4</v>
@@ -28302,13 +28302,13 @@
         <v>10</v>
       </c>
       <c r="D1269" t="n">
-        <v>19.11</v>
+        <v>29.74</v>
       </c>
       <c r="E1269" t="n">
-        <v>42.99</v>
+        <v>59.33</v>
       </c>
       <c r="F1269" t="n">
-        <v>301.38</v>
+        <v>295.5</v>
       </c>
     </row>
     <row r="1270">
@@ -36114,10 +36114,10 @@
         <v>10</v>
       </c>
       <c r="D1663" t="n">
-        <v>9.298999999999999</v>
+        <v>13.689</v>
       </c>
       <c r="E1663" t="n">
-        <v>8.586</v>
+        <v>9.006</v>
       </c>
       <c r="F1663" t="n">
         <v>289.043</v>
@@ -38791,12 +38791,12 @@
         <v>140.368</v>
       </c>
       <c r="K34" t="n">
-        <v>9.298999999999999</v>
+        <v>13.689</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>332.704</v>
+        <v>337.094</v>
       </c>
     </row>
   </sheetData>
@@ -40045,12 +40045,12 @@
         <v>42.813</v>
       </c>
       <c r="K34" t="n">
-        <v>8.586</v>
+        <v>9.006</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>366.664</v>
+        <v>367.0839999999999</v>
       </c>
     </row>
   </sheetData>
@@ -42237,12 +42237,12 @@
         <v>129.81</v>
       </c>
       <c r="K23" t="n">
-        <v>19.11</v>
+        <v>29.74</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>260.93</v>
+        <v>271.56</v>
       </c>
     </row>
   </sheetData>
@@ -43271,12 +43271,12 @@
         <v>14.19</v>
       </c>
       <c r="K23" t="n">
-        <v>42.99</v>
+        <v>59.33</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>206.42</v>
+        <v>222.76</v>
       </c>
     </row>
   </sheetData>
@@ -44237,7 +44237,7 @@
         <v>325.6</v>
       </c>
       <c r="K23" t="n">
-        <v>301.38</v>
+        <v>295.5</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
@@ -52894,12 +52894,12 @@
         <v>67.5</v>
       </c>
       <c r="K34" t="n">
-        <v>2.68</v>
+        <v>7.07</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>133.63</v>
+        <v>138.02</v>
       </c>
     </row>
   </sheetData>
@@ -54428,12 +54428,12 @@
         <v>16.42</v>
       </c>
       <c r="K34" t="n">
-        <v>0.43</v>
+        <v>0.85</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>167.45</v>
+        <v>167.87</v>
       </c>
     </row>
   </sheetData>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -8330,13 +8330,13 @@
         <v>10</v>
       </c>
       <c r="D359" t="n">
-        <v>5.988</v>
+        <v>8.292999999999999</v>
       </c>
       <c r="E359" t="n">
-        <v>6.853</v>
+        <v>9.648999999999999</v>
       </c>
       <c r="F359" t="n">
-        <v>83.523</v>
+        <v>83.03100000000001</v>
       </c>
     </row>
     <row r="360">
@@ -13902,13 +13902,13 @@
         <v>10</v>
       </c>
       <c r="D613" t="n">
-        <v>0.631</v>
+        <v>1.131</v>
       </c>
       <c r="E613" t="n">
-        <v>1.303</v>
+        <v>2.583</v>
       </c>
       <c r="F613" t="n">
-        <v>48.12</v>
+        <v>47.34</v>
       </c>
     </row>
     <row r="614">
@@ -22570,13 +22570,13 @@
         <v>10</v>
       </c>
       <c r="D1007" t="n">
-        <v>7.07</v>
+        <v>10.5</v>
       </c>
       <c r="E1007" t="n">
-        <v>0.85</v>
+        <v>1.35</v>
       </c>
       <c r="F1007" t="n">
-        <v>157.4</v>
+        <v>161.56</v>
       </c>
     </row>
     <row r="1008">
@@ -36114,13 +36114,13 @@
         <v>10</v>
       </c>
       <c r="D1663" t="n">
-        <v>13.689</v>
+        <v>19.924</v>
       </c>
       <c r="E1663" t="n">
-        <v>9.006</v>
+        <v>13.582</v>
       </c>
       <c r="F1663" t="n">
-        <v>289.043</v>
+        <v>291.931</v>
       </c>
     </row>
   </sheetData>
@@ -37548,7 +37548,7 @@
         <v>148.64</v>
       </c>
       <c r="K34" t="n">
-        <v>157.4</v>
+        <v>161.56</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
@@ -38791,12 +38791,12 @@
         <v>140.368</v>
       </c>
       <c r="K34" t="n">
-        <v>13.689</v>
+        <v>19.924</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>337.094</v>
+        <v>343.329</v>
       </c>
     </row>
   </sheetData>
@@ -40045,12 +40045,12 @@
         <v>42.813</v>
       </c>
       <c r="K34" t="n">
-        <v>9.006</v>
+        <v>13.582</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>367.0839999999999</v>
+        <v>371.66</v>
       </c>
     </row>
   </sheetData>
@@ -41190,7 +41190,7 @@
         <v>285.545</v>
       </c>
       <c r="K34" t="n">
-        <v>289.043</v>
+        <v>291.931</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
@@ -45636,12 +45636,12 @@
         <v>37.966</v>
       </c>
       <c r="K31" t="n">
-        <v>5.988</v>
+        <v>8.292999999999999</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>87.08199999999999</v>
+        <v>89.387</v>
       </c>
     </row>
   </sheetData>
@@ -47038,12 +47038,12 @@
         <v>10.832</v>
       </c>
       <c r="K31" t="n">
-        <v>6.853</v>
+        <v>9.648999999999999</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>76.783</v>
+        <v>79.57900000000001</v>
       </c>
     </row>
   </sheetData>
@@ -48348,7 +48348,7 @@
         <v>85.508</v>
       </c>
       <c r="K31" t="n">
-        <v>83.523</v>
+        <v>83.03100000000001</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
@@ -49371,12 +49371,12 @@
         <v>34.902</v>
       </c>
       <c r="K23" t="n">
-        <v>0.631</v>
+        <v>1.131</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>111.992</v>
+        <v>112.492</v>
       </c>
     </row>
   </sheetData>
@@ -50405,12 +50405,12 @@
         <v>15.561</v>
       </c>
       <c r="K23" t="n">
-        <v>1.303</v>
+        <v>2.583</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>122.431</v>
+        <v>123.711</v>
       </c>
     </row>
   </sheetData>
@@ -51363,7 +51363,7 @@
         <v>51.397</v>
       </c>
       <c r="K23" t="n">
-        <v>48.12</v>
+        <v>47.34</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
@@ -52894,12 +52894,12 @@
         <v>67.5</v>
       </c>
       <c r="K34" t="n">
-        <v>7.07</v>
+        <v>10.5</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>138.02</v>
+        <v>141.45</v>
       </c>
     </row>
   </sheetData>
@@ -54428,12 +54428,12 @@
         <v>16.42</v>
       </c>
       <c r="K34" t="n">
-        <v>0.85</v>
+        <v>1.35</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>167.87</v>
+        <v>168.37</v>
       </c>
     </row>
   </sheetData>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -28302,13 +28302,13 @@
         <v>10</v>
       </c>
       <c r="D1269" t="n">
-        <v>29.74</v>
+        <v>41.99</v>
       </c>
       <c r="E1269" t="n">
-        <v>59.33</v>
+        <v>72.94</v>
       </c>
       <c r="F1269" t="n">
-        <v>295.5</v>
+        <v>293.97</v>
       </c>
     </row>
     <row r="1270">
@@ -42237,12 +42237,12 @@
         <v>129.81</v>
       </c>
       <c r="K23" t="n">
-        <v>29.74</v>
+        <v>41.99</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>271.56</v>
+        <v>283.81</v>
       </c>
     </row>
   </sheetData>
@@ -43271,12 +43271,12 @@
         <v>14.19</v>
       </c>
       <c r="K23" t="n">
-        <v>59.33</v>
+        <v>72.94</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>222.76</v>
+        <v>236.37</v>
       </c>
     </row>
   </sheetData>
@@ -44237,7 +44237,7 @@
         <v>325.6</v>
       </c>
       <c r="K23" t="n">
-        <v>295.5</v>
+        <v>293.97</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -8330,13 +8330,13 @@
         <v>10</v>
       </c>
       <c r="D359" t="n">
-        <v>8.292999999999999</v>
+        <v>11.207</v>
       </c>
       <c r="E359" t="n">
-        <v>9.648999999999999</v>
+        <v>12.441</v>
       </c>
       <c r="F359" t="n">
-        <v>83.03100000000001</v>
+        <v>83.154</v>
       </c>
     </row>
     <row r="360">
@@ -13902,13 +13902,13 @@
         <v>10</v>
       </c>
       <c r="D613" t="n">
-        <v>1.131</v>
+        <v>1.687</v>
       </c>
       <c r="E613" t="n">
-        <v>2.583</v>
+        <v>3.914</v>
       </c>
       <c r="F613" t="n">
-        <v>47.34</v>
+        <v>46.565</v>
       </c>
     </row>
     <row r="614">
@@ -36114,13 +36114,13 @@
         <v>10</v>
       </c>
       <c r="D1663" t="n">
-        <v>19.924</v>
+        <v>23.394</v>
       </c>
       <c r="E1663" t="n">
-        <v>13.582</v>
+        <v>17.705</v>
       </c>
       <c r="F1663" t="n">
-        <v>291.931</v>
+        <v>291.279</v>
       </c>
     </row>
   </sheetData>
@@ -38791,12 +38791,12 @@
         <v>140.368</v>
       </c>
       <c r="K34" t="n">
-        <v>19.924</v>
+        <v>23.394</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>343.329</v>
+        <v>346.799</v>
       </c>
     </row>
   </sheetData>
@@ -40045,12 +40045,12 @@
         <v>42.813</v>
       </c>
       <c r="K34" t="n">
-        <v>13.582</v>
+        <v>17.705</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>371.66</v>
+        <v>375.783</v>
       </c>
     </row>
   </sheetData>
@@ -41190,7 +41190,7 @@
         <v>285.545</v>
       </c>
       <c r="K34" t="n">
-        <v>291.931</v>
+        <v>291.279</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
@@ -45636,12 +45636,12 @@
         <v>37.966</v>
       </c>
       <c r="K31" t="n">
-        <v>8.292999999999999</v>
+        <v>11.207</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>89.387</v>
+        <v>92.30099999999999</v>
       </c>
     </row>
   </sheetData>
@@ -47038,12 +47038,12 @@
         <v>10.832</v>
       </c>
       <c r="K31" t="n">
-        <v>9.648999999999999</v>
+        <v>12.441</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>79.57900000000001</v>
+        <v>82.37100000000001</v>
       </c>
     </row>
   </sheetData>
@@ -48348,7 +48348,7 @@
         <v>85.508</v>
       </c>
       <c r="K31" t="n">
-        <v>83.03100000000001</v>
+        <v>83.154</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
@@ -49371,12 +49371,12 @@
         <v>34.902</v>
       </c>
       <c r="K23" t="n">
-        <v>1.131</v>
+        <v>1.687</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>112.492</v>
+        <v>113.048</v>
       </c>
     </row>
   </sheetData>
@@ -50405,12 +50405,12 @@
         <v>15.561</v>
       </c>
       <c r="K23" t="n">
-        <v>2.583</v>
+        <v>3.914</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>123.711</v>
+        <v>125.042</v>
       </c>
     </row>
   </sheetData>
@@ -51363,7 +51363,7 @@
         <v>51.397</v>
       </c>
       <c r="K23" t="n">
-        <v>47.34</v>
+        <v>46.565</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -22570,13 +22570,13 @@
         <v>10</v>
       </c>
       <c r="D1007" t="n">
-        <v>10.5</v>
+        <v>16.47</v>
       </c>
       <c r="E1007" t="n">
-        <v>1.35</v>
+        <v>1.88</v>
       </c>
       <c r="F1007" t="n">
-        <v>161.56</v>
+        <v>168.29</v>
       </c>
     </row>
     <row r="1008">
@@ -36114,13 +36114,13 @@
         <v>10</v>
       </c>
       <c r="D1663" t="n">
-        <v>23.394</v>
+        <v>29.364</v>
       </c>
       <c r="E1663" t="n">
-        <v>17.705</v>
+        <v>18.235</v>
       </c>
       <c r="F1663" t="n">
-        <v>291.279</v>
+        <v>298.009</v>
       </c>
     </row>
   </sheetData>
@@ -37548,7 +37548,7 @@
         <v>148.64</v>
       </c>
       <c r="K34" t="n">
-        <v>161.56</v>
+        <v>168.29</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
@@ -38791,12 +38791,12 @@
         <v>140.368</v>
       </c>
       <c r="K34" t="n">
-        <v>23.394</v>
+        <v>29.364</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>346.799</v>
+        <v>352.7689999999999</v>
       </c>
     </row>
   </sheetData>
@@ -40045,12 +40045,12 @@
         <v>42.813</v>
       </c>
       <c r="K34" t="n">
-        <v>17.705</v>
+        <v>18.235</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>375.783</v>
+        <v>376.313</v>
       </c>
     </row>
   </sheetData>
@@ -41190,7 +41190,7 @@
         <v>285.545</v>
       </c>
       <c r="K34" t="n">
-        <v>291.279</v>
+        <v>298.009</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
@@ -52894,12 +52894,12 @@
         <v>67.5</v>
       </c>
       <c r="K34" t="n">
-        <v>10.5</v>
+        <v>16.47</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>141.45</v>
+        <v>147.42</v>
       </c>
     </row>
   </sheetData>
@@ -54428,12 +54428,12 @@
         <v>16.42</v>
       </c>
       <c r="K34" t="n">
-        <v>1.35</v>
+        <v>1.88</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>168.37</v>
+        <v>168.9</v>
       </c>
     </row>
   </sheetData>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -28302,13 +28302,13 @@
         <v>10</v>
       </c>
       <c r="D1269" t="n">
-        <v>41.99</v>
+        <v>50.16</v>
       </c>
       <c r="E1269" t="n">
-        <v>72.94</v>
+        <v>86.55</v>
       </c>
       <c r="F1269" t="n">
-        <v>293.97</v>
+        <v>288.36</v>
       </c>
     </row>
     <row r="1270">
@@ -42237,12 +42237,12 @@
         <v>129.81</v>
       </c>
       <c r="K23" t="n">
-        <v>41.99</v>
+        <v>50.16</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>283.81</v>
+        <v>291.98</v>
       </c>
     </row>
   </sheetData>
@@ -43271,12 +43271,12 @@
         <v>14.19</v>
       </c>
       <c r="K23" t="n">
-        <v>72.94</v>
+        <v>86.55</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>236.37</v>
+        <v>249.98</v>
       </c>
     </row>
   </sheetData>
@@ -44237,7 +44237,7 @@
         <v>325.6</v>
       </c>
       <c r="K23" t="n">
-        <v>293.97</v>
+        <v>288.36</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -8330,13 +8330,13 @@
         <v>10</v>
       </c>
       <c r="D359" t="n">
-        <v>11.207</v>
+        <v>13.611</v>
       </c>
       <c r="E359" t="n">
-        <v>12.441</v>
+        <v>15.822</v>
       </c>
       <c r="F359" t="n">
-        <v>83.154</v>
+        <v>82.176</v>
       </c>
     </row>
     <row r="360">
@@ -13905,10 +13905,10 @@
         <v>1.687</v>
       </c>
       <c r="E613" t="n">
-        <v>3.914</v>
+        <v>5.773</v>
       </c>
       <c r="F613" t="n">
-        <v>46.565</v>
+        <v>44.7</v>
       </c>
     </row>
     <row r="614">
@@ -22570,13 +22570,13 @@
         <v>10</v>
       </c>
       <c r="D1007" t="n">
-        <v>16.47</v>
+        <v>18.46</v>
       </c>
       <c r="E1007" t="n">
-        <v>1.88</v>
+        <v>2.18</v>
       </c>
       <c r="F1007" t="n">
-        <v>168.29</v>
+        <v>171.87</v>
       </c>
     </row>
     <row r="1008">
@@ -36114,13 +36114,13 @@
         <v>10</v>
       </c>
       <c r="D1663" t="n">
-        <v>29.364</v>
+        <v>33.758</v>
       </c>
       <c r="E1663" t="n">
-        <v>18.235</v>
+        <v>23.775</v>
       </c>
       <c r="F1663" t="n">
-        <v>298.009</v>
+        <v>298.746</v>
       </c>
     </row>
   </sheetData>
@@ -37548,7 +37548,7 @@
         <v>148.64</v>
       </c>
       <c r="K34" t="n">
-        <v>168.29</v>
+        <v>171.87</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
@@ -38791,12 +38791,12 @@
         <v>140.368</v>
       </c>
       <c r="K34" t="n">
-        <v>29.364</v>
+        <v>33.758</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>352.7689999999999</v>
+        <v>357.163</v>
       </c>
     </row>
   </sheetData>
@@ -40045,12 +40045,12 @@
         <v>42.813</v>
       </c>
       <c r="K34" t="n">
-        <v>18.235</v>
+        <v>23.775</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>376.313</v>
+        <v>381.853</v>
       </c>
     </row>
   </sheetData>
@@ -41190,7 +41190,7 @@
         <v>285.545</v>
       </c>
       <c r="K34" t="n">
-        <v>298.009</v>
+        <v>298.746</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
@@ -45636,12 +45636,12 @@
         <v>37.966</v>
       </c>
       <c r="K31" t="n">
-        <v>11.207</v>
+        <v>13.611</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>92.30099999999999</v>
+        <v>94.705</v>
       </c>
     </row>
   </sheetData>
@@ -47038,12 +47038,12 @@
         <v>10.832</v>
       </c>
       <c r="K31" t="n">
-        <v>12.441</v>
+        <v>15.822</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>82.37100000000001</v>
+        <v>85.75200000000001</v>
       </c>
     </row>
   </sheetData>
@@ -48348,7 +48348,7 @@
         <v>85.508</v>
       </c>
       <c r="K31" t="n">
-        <v>83.154</v>
+        <v>82.176</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
@@ -50405,12 +50405,12 @@
         <v>15.561</v>
       </c>
       <c r="K23" t="n">
-        <v>3.914</v>
+        <v>5.773</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>125.042</v>
+        <v>126.901</v>
       </c>
     </row>
   </sheetData>
@@ -51363,7 +51363,7 @@
         <v>51.397</v>
       </c>
       <c r="K23" t="n">
-        <v>46.565</v>
+        <v>44.7</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
@@ -52894,12 +52894,12 @@
         <v>67.5</v>
       </c>
       <c r="K34" t="n">
-        <v>16.47</v>
+        <v>18.46</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>147.42</v>
+        <v>149.41</v>
       </c>
     </row>
   </sheetData>
@@ -54428,12 +54428,12 @@
         <v>16.42</v>
       </c>
       <c r="K34" t="n">
-        <v>1.88</v>
+        <v>2.18</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>168.9</v>
+        <v>169.2</v>
       </c>
     </row>
   </sheetData>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -28302,13 +28302,13 @@
         <v>10</v>
       </c>
       <c r="D1269" t="n">
-        <v>50.16</v>
+        <v>58.41</v>
       </c>
       <c r="E1269" t="n">
-        <v>86.55</v>
+        <v>97.18000000000001</v>
       </c>
       <c r="F1269" t="n">
-        <v>288.36</v>
+        <v>285.81</v>
       </c>
     </row>
     <row r="1270">
@@ -42237,12 +42237,12 @@
         <v>129.81</v>
       </c>
       <c r="K23" t="n">
-        <v>50.16</v>
+        <v>58.41</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>291.98</v>
+        <v>300.23</v>
       </c>
     </row>
   </sheetData>
@@ -43271,12 +43271,12 @@
         <v>14.19</v>
       </c>
       <c r="K23" t="n">
-        <v>86.55</v>
+        <v>97.18000000000001</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>249.98</v>
+        <v>260.61</v>
       </c>
     </row>
   </sheetData>
@@ -44237,7 +44237,7 @@
         <v>325.6</v>
       </c>
       <c r="K23" t="n">
-        <v>288.36</v>
+        <v>285.81</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -8330,10 +8330,10 @@
         <v>10</v>
       </c>
       <c r="D359" t="n">
-        <v>13.611</v>
+        <v>16.015</v>
       </c>
       <c r="E359" t="n">
-        <v>15.822</v>
+        <v>18.226</v>
       </c>
       <c r="F359" t="n">
         <v>82.176</v>
@@ -36114,10 +36114,10 @@
         <v>10</v>
       </c>
       <c r="D1663" t="n">
-        <v>33.758</v>
+        <v>36.162</v>
       </c>
       <c r="E1663" t="n">
-        <v>23.775</v>
+        <v>26.179</v>
       </c>
       <c r="F1663" t="n">
         <v>298.746</v>
@@ -38791,12 +38791,12 @@
         <v>140.368</v>
       </c>
       <c r="K34" t="n">
-        <v>33.758</v>
+        <v>36.162</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>357.163</v>
+        <v>359.567</v>
       </c>
     </row>
   </sheetData>
@@ -40045,12 +40045,12 @@
         <v>42.813</v>
       </c>
       <c r="K34" t="n">
-        <v>23.775</v>
+        <v>26.179</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>381.853</v>
+        <v>384.2569999999999</v>
       </c>
     </row>
   </sheetData>
@@ -45636,12 +45636,12 @@
         <v>37.966</v>
       </c>
       <c r="K31" t="n">
-        <v>13.611</v>
+        <v>16.015</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>94.705</v>
+        <v>97.10899999999999</v>
       </c>
     </row>
   </sheetData>
@@ -47038,12 +47038,12 @@
         <v>10.832</v>
       </c>
       <c r="K31" t="n">
-        <v>15.822</v>
+        <v>18.226</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>85.75200000000001</v>
+        <v>88.15600000000001</v>
       </c>
     </row>
   </sheetData>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -22570,13 +22570,13 @@
         <v>10</v>
       </c>
       <c r="D1007" t="n">
-        <v>18.46</v>
+        <v>19.54</v>
       </c>
       <c r="E1007" t="n">
-        <v>2.18</v>
+        <v>3.03</v>
       </c>
       <c r="F1007" t="n">
-        <v>171.87</v>
+        <v>173.3</v>
       </c>
     </row>
     <row r="1008">
@@ -36114,13 +36114,13 @@
         <v>10</v>
       </c>
       <c r="D1663" t="n">
-        <v>36.162</v>
+        <v>37.242</v>
       </c>
       <c r="E1663" t="n">
-        <v>26.179</v>
+        <v>27.029</v>
       </c>
       <c r="F1663" t="n">
-        <v>298.746</v>
+        <v>300.176</v>
       </c>
     </row>
   </sheetData>
@@ -37548,7 +37548,7 @@
         <v>148.64</v>
       </c>
       <c r="K34" t="n">
-        <v>171.87</v>
+        <v>173.3</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
@@ -38791,12 +38791,12 @@
         <v>140.368</v>
       </c>
       <c r="K34" t="n">
-        <v>36.162</v>
+        <v>37.242</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>359.567</v>
+        <v>360.647</v>
       </c>
     </row>
   </sheetData>
@@ -40045,12 +40045,12 @@
         <v>42.813</v>
       </c>
       <c r="K34" t="n">
-        <v>26.179</v>
+        <v>27.029</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>384.2569999999999</v>
+        <v>385.107</v>
       </c>
     </row>
   </sheetData>
@@ -41190,7 +41190,7 @@
         <v>285.545</v>
       </c>
       <c r="K34" t="n">
-        <v>298.746</v>
+        <v>300.176</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
@@ -52894,12 +52894,12 @@
         <v>67.5</v>
       </c>
       <c r="K34" t="n">
-        <v>18.46</v>
+        <v>19.54</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>149.41</v>
+        <v>150.49</v>
       </c>
     </row>
   </sheetData>
@@ -54428,12 +54428,12 @@
         <v>16.42</v>
       </c>
       <c r="K34" t="n">
-        <v>2.18</v>
+        <v>3.03</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>169.2</v>
+        <v>170.05</v>
       </c>
     </row>
   </sheetData>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -28302,13 +28302,13 @@
         <v>10</v>
       </c>
       <c r="D1269" t="n">
-        <v>58.41</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="E1269" t="n">
-        <v>97.18000000000001</v>
+        <v>106.76</v>
       </c>
       <c r="F1269" t="n">
-        <v>285.81</v>
+        <v>282.75</v>
       </c>
     </row>
     <row r="1270">
@@ -42237,12 +42237,12 @@
         <v>129.81</v>
       </c>
       <c r="K23" t="n">
-        <v>58.41</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>300.23</v>
+        <v>306.92</v>
       </c>
     </row>
   </sheetData>
@@ -43271,12 +43271,12 @@
         <v>14.19</v>
       </c>
       <c r="K23" t="n">
-        <v>97.18000000000001</v>
+        <v>106.76</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>260.61</v>
+        <v>270.19</v>
       </c>
     </row>
   </sheetData>
@@ -44237,7 +44237,7 @@
         <v>325.6</v>
       </c>
       <c r="K23" t="n">
-        <v>285.81</v>
+        <v>282.75</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -8330,13 +8330,13 @@
         <v>10</v>
       </c>
       <c r="D359" t="n">
-        <v>16.015</v>
+        <v>19.076</v>
       </c>
       <c r="E359" t="n">
-        <v>18.226</v>
+        <v>22.012</v>
       </c>
       <c r="F359" t="n">
-        <v>82.176</v>
+        <v>80.96599999999999</v>
       </c>
     </row>
     <row r="360">
@@ -13902,13 +13902,13 @@
         <v>10</v>
       </c>
       <c r="D613" t="n">
-        <v>1.687</v>
+        <v>3.412</v>
       </c>
       <c r="E613" t="n">
-        <v>5.773</v>
+        <v>7.928</v>
       </c>
       <c r="F613" t="n">
-        <v>44.7</v>
+        <v>42.754</v>
       </c>
     </row>
     <row r="614">
@@ -22570,13 +22570,13 @@
         <v>10</v>
       </c>
       <c r="D1007" t="n">
-        <v>19.54</v>
+        <v>20.15</v>
       </c>
       <c r="E1007" t="n">
-        <v>3.03</v>
+        <v>4.36</v>
       </c>
       <c r="F1007" t="n">
-        <v>173.3</v>
+        <v>173.78</v>
       </c>
     </row>
     <row r="1008">
@@ -36114,13 +36114,13 @@
         <v>10</v>
       </c>
       <c r="D1663" t="n">
-        <v>37.242</v>
+        <v>42.638</v>
       </c>
       <c r="E1663" t="n">
-        <v>27.029</v>
+        <v>34.3</v>
       </c>
       <c r="F1663" t="n">
-        <v>300.176</v>
+        <v>297.5</v>
       </c>
     </row>
   </sheetData>
@@ -37548,7 +37548,7 @@
         <v>148.64</v>
       </c>
       <c r="K34" t="n">
-        <v>173.3</v>
+        <v>173.78</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
@@ -38791,12 +38791,12 @@
         <v>140.368</v>
       </c>
       <c r="K34" t="n">
-        <v>37.242</v>
+        <v>42.638</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>360.647</v>
+        <v>366.0429999999999</v>
       </c>
     </row>
   </sheetData>
@@ -40045,12 +40045,12 @@
         <v>42.813</v>
       </c>
       <c r="K34" t="n">
-        <v>27.029</v>
+        <v>34.3</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>385.107</v>
+        <v>392.378</v>
       </c>
     </row>
   </sheetData>
@@ -41190,7 +41190,7 @@
         <v>285.545</v>
       </c>
       <c r="K34" t="n">
-        <v>300.176</v>
+        <v>297.5</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
@@ -45636,12 +45636,12 @@
         <v>37.966</v>
       </c>
       <c r="K31" t="n">
-        <v>16.015</v>
+        <v>19.076</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>97.10899999999999</v>
+        <v>100.17</v>
       </c>
     </row>
   </sheetData>
@@ -47038,12 +47038,12 @@
         <v>10.832</v>
       </c>
       <c r="K31" t="n">
-        <v>18.226</v>
+        <v>22.012</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>88.15600000000001</v>
+        <v>91.94200000000001</v>
       </c>
     </row>
   </sheetData>
@@ -48348,7 +48348,7 @@
         <v>85.508</v>
       </c>
       <c r="K31" t="n">
-        <v>82.176</v>
+        <v>80.96599999999999</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
@@ -49371,12 +49371,12 @@
         <v>34.902</v>
       </c>
       <c r="K23" t="n">
-        <v>1.687</v>
+        <v>3.412</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>113.048</v>
+        <v>114.773</v>
       </c>
     </row>
   </sheetData>
@@ -50405,12 +50405,12 @@
         <v>15.561</v>
       </c>
       <c r="K23" t="n">
-        <v>5.773</v>
+        <v>7.928</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>126.901</v>
+        <v>129.056</v>
       </c>
     </row>
   </sheetData>
@@ -51363,7 +51363,7 @@
         <v>51.397</v>
       </c>
       <c r="K23" t="n">
-        <v>44.7</v>
+        <v>42.754</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
@@ -52894,12 +52894,12 @@
         <v>67.5</v>
       </c>
       <c r="K34" t="n">
-        <v>19.54</v>
+        <v>20.15</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>150.49</v>
+        <v>151.1</v>
       </c>
     </row>
   </sheetData>
@@ -54428,12 +54428,12 @@
         <v>16.42</v>
       </c>
       <c r="K34" t="n">
-        <v>3.03</v>
+        <v>4.36</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>170.05</v>
+        <v>171.3800000000001</v>
       </c>
     </row>
   </sheetData>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -28302,13 +28302,13 @@
         <v>10</v>
       </c>
       <c r="D1269" t="n">
-        <v>65.09999999999999</v>
+        <v>69.93000000000001</v>
       </c>
       <c r="E1269" t="n">
-        <v>106.76</v>
+        <v>115.5</v>
       </c>
       <c r="F1269" t="n">
-        <v>282.75</v>
+        <v>278.67</v>
       </c>
     </row>
     <row r="1270">
@@ -42237,12 +42237,12 @@
         <v>129.81</v>
       </c>
       <c r="K23" t="n">
-        <v>65.09999999999999</v>
+        <v>69.93000000000001</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>306.92</v>
+        <v>311.75</v>
       </c>
     </row>
   </sheetData>
@@ -43271,12 +43271,12 @@
         <v>14.19</v>
       </c>
       <c r="K23" t="n">
-        <v>106.76</v>
+        <v>115.5</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>270.19</v>
+        <v>278.93</v>
       </c>
     </row>
   </sheetData>
@@ -44237,7 +44237,7 @@
         <v>325.6</v>
       </c>
       <c r="K23" t="n">
-        <v>282.75</v>
+        <v>278.67</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -8330,10 +8330,10 @@
         <v>10</v>
       </c>
       <c r="D359" t="n">
-        <v>19.076</v>
+        <v>22.137</v>
       </c>
       <c r="E359" t="n">
-        <v>22.012</v>
+        <v>25.073</v>
       </c>
       <c r="F359" t="n">
         <v>80.96599999999999</v>
@@ -13902,10 +13902,10 @@
         <v>10</v>
       </c>
       <c r="D613" t="n">
-        <v>3.412</v>
+        <v>5.137</v>
       </c>
       <c r="E613" t="n">
-        <v>7.928</v>
+        <v>10.083</v>
       </c>
       <c r="F613" t="n">
         <v>42.754</v>
@@ -22570,13 +22570,13 @@
         <v>10</v>
       </c>
       <c r="D1007" t="n">
-        <v>20.15</v>
+        <v>21.22</v>
       </c>
       <c r="E1007" t="n">
-        <v>4.36</v>
+        <v>5.91</v>
       </c>
       <c r="F1007" t="n">
-        <v>173.78</v>
+        <v>173.3</v>
       </c>
     </row>
     <row r="1008">
@@ -36114,13 +36114,13 @@
         <v>10</v>
       </c>
       <c r="D1663" t="n">
-        <v>42.638</v>
+        <v>48.494</v>
       </c>
       <c r="E1663" t="n">
-        <v>34.3</v>
+        <v>41.066</v>
       </c>
       <c r="F1663" t="n">
-        <v>297.5</v>
+        <v>297.02</v>
       </c>
     </row>
   </sheetData>
@@ -37548,7 +37548,7 @@
         <v>148.64</v>
       </c>
       <c r="K34" t="n">
-        <v>173.78</v>
+        <v>173.3</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
@@ -38791,12 +38791,12 @@
         <v>140.368</v>
       </c>
       <c r="K34" t="n">
-        <v>42.638</v>
+        <v>48.494</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>366.0429999999999</v>
+        <v>371.899</v>
       </c>
     </row>
   </sheetData>
@@ -40045,12 +40045,12 @@
         <v>42.813</v>
       </c>
       <c r="K34" t="n">
-        <v>34.3</v>
+        <v>41.066</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>392.378</v>
+        <v>399.144</v>
       </c>
     </row>
   </sheetData>
@@ -41190,7 +41190,7 @@
         <v>285.545</v>
       </c>
       <c r="K34" t="n">
-        <v>297.5</v>
+        <v>297.02</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
@@ -45636,12 +45636,12 @@
         <v>37.966</v>
       </c>
       <c r="K31" t="n">
-        <v>19.076</v>
+        <v>22.137</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>100.17</v>
+        <v>103.231</v>
       </c>
     </row>
   </sheetData>
@@ -47038,12 +47038,12 @@
         <v>10.832</v>
       </c>
       <c r="K31" t="n">
-        <v>22.012</v>
+        <v>25.073</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>91.94200000000001</v>
+        <v>95.00300000000001</v>
       </c>
     </row>
   </sheetData>
@@ -49371,12 +49371,12 @@
         <v>34.902</v>
       </c>
       <c r="K23" t="n">
-        <v>3.412</v>
+        <v>5.137</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>114.773</v>
+        <v>116.498</v>
       </c>
     </row>
   </sheetData>
@@ -50405,12 +50405,12 @@
         <v>15.561</v>
       </c>
       <c r="K23" t="n">
-        <v>7.928</v>
+        <v>10.083</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>129.056</v>
+        <v>131.211</v>
       </c>
     </row>
   </sheetData>
@@ -52894,12 +52894,12 @@
         <v>67.5</v>
       </c>
       <c r="K34" t="n">
-        <v>20.15</v>
+        <v>21.22</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>151.1</v>
+        <v>152.17</v>
       </c>
     </row>
   </sheetData>
@@ -54428,12 +54428,12 @@
         <v>16.42</v>
       </c>
       <c r="K34" t="n">
-        <v>4.36</v>
+        <v>5.91</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>171.3800000000001</v>
+        <v>172.93</v>
       </c>
     </row>
   </sheetData>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -28302,13 +28302,13 @@
         <v>10</v>
       </c>
       <c r="D1269" t="n">
-        <v>69.93000000000001</v>
+        <v>73.55</v>
       </c>
       <c r="E1269" t="n">
-        <v>115.5</v>
+        <v>123.03</v>
       </c>
       <c r="F1269" t="n">
-        <v>278.67</v>
+        <v>274.59</v>
       </c>
     </row>
     <row r="1270">
@@ -42237,12 +42237,12 @@
         <v>129.81</v>
       </c>
       <c r="K23" t="n">
-        <v>69.93000000000001</v>
+        <v>73.55</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>311.75</v>
+        <v>315.37</v>
       </c>
     </row>
   </sheetData>
@@ -43271,12 +43271,12 @@
         <v>14.19</v>
       </c>
       <c r="K23" t="n">
-        <v>115.5</v>
+        <v>123.03</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>278.93</v>
+        <v>286.46</v>
       </c>
     </row>
   </sheetData>
@@ -44237,7 +44237,7 @@
         <v>325.6</v>
       </c>
       <c r="K23" t="n">
-        <v>278.67</v>
+        <v>274.59</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -8330,13 +8330,13 @@
         <v>10</v>
       </c>
       <c r="D359" t="n">
-        <v>22.137</v>
+        <v>24.296</v>
       </c>
       <c r="E359" t="n">
-        <v>25.073</v>
+        <v>27.947</v>
       </c>
       <c r="F359" t="n">
-        <v>80.96599999999999</v>
+        <v>79.411</v>
       </c>
     </row>
     <row r="360">
@@ -13902,13 +13902,13 @@
         <v>10</v>
       </c>
       <c r="D613" t="n">
-        <v>5.137</v>
+        <v>5.975</v>
       </c>
       <c r="E613" t="n">
-        <v>10.083</v>
+        <v>11.347</v>
       </c>
       <c r="F613" t="n">
-        <v>42.754</v>
+        <v>41.579</v>
       </c>
     </row>
     <row r="614">
@@ -22570,13 +22570,13 @@
         <v>10</v>
       </c>
       <c r="D1007" t="n">
-        <v>21.22</v>
+        <v>21.81</v>
       </c>
       <c r="E1007" t="n">
-        <v>5.91</v>
+        <v>7.21</v>
       </c>
       <c r="F1007" t="n">
-        <v>173.3</v>
+        <v>172.58</v>
       </c>
     </row>
     <row r="1008">
@@ -36114,13 +36114,13 @@
         <v>10</v>
       </c>
       <c r="D1663" t="n">
-        <v>48.494</v>
+        <v>52.081</v>
       </c>
       <c r="E1663" t="n">
-        <v>41.066</v>
+        <v>46.504</v>
       </c>
       <c r="F1663" t="n">
-        <v>297.02</v>
+        <v>293.57</v>
       </c>
     </row>
   </sheetData>
@@ -37548,7 +37548,7 @@
         <v>148.64</v>
       </c>
       <c r="K34" t="n">
-        <v>173.3</v>
+        <v>172.58</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
@@ -38791,12 +38791,12 @@
         <v>140.368</v>
       </c>
       <c r="K34" t="n">
-        <v>48.494</v>
+        <v>52.081</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>371.899</v>
+        <v>375.486</v>
       </c>
     </row>
   </sheetData>
@@ -40045,12 +40045,12 @@
         <v>42.813</v>
       </c>
       <c r="K34" t="n">
-        <v>41.066</v>
+        <v>46.504</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>399.144</v>
+        <v>404.582</v>
       </c>
     </row>
   </sheetData>
@@ -41190,7 +41190,7 @@
         <v>285.545</v>
       </c>
       <c r="K34" t="n">
-        <v>297.02</v>
+        <v>293.57</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
@@ -45636,12 +45636,12 @@
         <v>37.966</v>
       </c>
       <c r="K31" t="n">
-        <v>22.137</v>
+        <v>24.296</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>103.231</v>
+        <v>105.39</v>
       </c>
     </row>
   </sheetData>
@@ -47038,12 +47038,12 @@
         <v>10.832</v>
       </c>
       <c r="K31" t="n">
-        <v>25.073</v>
+        <v>27.947</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>95.00300000000001</v>
+        <v>97.87700000000001</v>
       </c>
     </row>
   </sheetData>
@@ -48348,7 +48348,7 @@
         <v>85.508</v>
       </c>
       <c r="K31" t="n">
-        <v>80.96599999999999</v>
+        <v>79.411</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
@@ -49371,12 +49371,12 @@
         <v>34.902</v>
       </c>
       <c r="K23" t="n">
-        <v>5.137</v>
+        <v>5.975</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>116.498</v>
+        <v>117.336</v>
       </c>
     </row>
   </sheetData>
@@ -50405,12 +50405,12 @@
         <v>15.561</v>
       </c>
       <c r="K23" t="n">
-        <v>10.083</v>
+        <v>11.347</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>131.211</v>
+        <v>132.475</v>
       </c>
     </row>
   </sheetData>
@@ -51363,7 +51363,7 @@
         <v>51.397</v>
       </c>
       <c r="K23" t="n">
-        <v>42.754</v>
+        <v>41.579</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
@@ -52894,12 +52894,12 @@
         <v>67.5</v>
       </c>
       <c r="K34" t="n">
-        <v>21.22</v>
+        <v>21.81</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>152.17</v>
+        <v>152.76</v>
       </c>
     </row>
   </sheetData>
@@ -54428,12 +54428,12 @@
         <v>16.42</v>
       </c>
       <c r="K34" t="n">
-        <v>5.91</v>
+        <v>7.21</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>172.93</v>
+        <v>174.23</v>
       </c>
     </row>
   </sheetData>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -28302,13 +28302,13 @@
         <v>10</v>
       </c>
       <c r="D1269" t="n">
-        <v>73.55</v>
+        <v>77</v>
       </c>
       <c r="E1269" t="n">
-        <v>123.03</v>
+        <v>129.37</v>
       </c>
       <c r="F1269" t="n">
-        <v>274.59</v>
+        <v>271.53</v>
       </c>
     </row>
     <row r="1270">
@@ -42237,12 +42237,12 @@
         <v>129.81</v>
       </c>
       <c r="K23" t="n">
-        <v>73.55</v>
+        <v>77</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>315.37</v>
+        <v>318.82</v>
       </c>
     </row>
   </sheetData>
@@ -43271,12 +43271,12 @@
         <v>14.19</v>
       </c>
       <c r="K23" t="n">
-        <v>123.03</v>
+        <v>129.37</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>286.46</v>
+        <v>292.8</v>
       </c>
     </row>
   </sheetData>
@@ -44237,7 +44237,7 @@
         <v>325.6</v>
       </c>
       <c r="K23" t="n">
-        <v>274.59</v>
+        <v>271.53</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -8330,10 +8330,10 @@
         <v>10</v>
       </c>
       <c r="D359" t="n">
-        <v>24.296</v>
+        <v>26.455</v>
       </c>
       <c r="E359" t="n">
-        <v>27.947</v>
+        <v>30.821</v>
       </c>
       <c r="F359" t="n">
         <v>79.411</v>
@@ -13902,10 +13902,10 @@
         <v>10</v>
       </c>
       <c r="D613" t="n">
-        <v>5.975</v>
+        <v>6.813</v>
       </c>
       <c r="E613" t="n">
-        <v>11.347</v>
+        <v>12.611</v>
       </c>
       <c r="F613" t="n">
         <v>41.579</v>
@@ -22570,13 +22570,13 @@
         <v>10</v>
       </c>
       <c r="D1007" t="n">
-        <v>21.81</v>
+        <v>22.93</v>
       </c>
       <c r="E1007" t="n">
-        <v>7.21</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F1007" t="n">
-        <v>172.58</v>
+        <v>172.11</v>
       </c>
     </row>
     <row r="1008">
@@ -36114,13 +36114,13 @@
         <v>10</v>
       </c>
       <c r="D1663" t="n">
-        <v>52.081</v>
+        <v>56.198</v>
       </c>
       <c r="E1663" t="n">
-        <v>46.504</v>
+        <v>52.232</v>
       </c>
       <c r="F1663" t="n">
-        <v>293.57</v>
+        <v>293.1</v>
       </c>
     </row>
   </sheetData>
@@ -37548,7 +37548,7 @@
         <v>148.64</v>
       </c>
       <c r="K34" t="n">
-        <v>172.58</v>
+        <v>172.11</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
@@ -38791,12 +38791,12 @@
         <v>140.368</v>
       </c>
       <c r="K34" t="n">
-        <v>52.081</v>
+        <v>56.198</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>375.486</v>
+        <v>379.603</v>
       </c>
     </row>
   </sheetData>
@@ -40045,12 +40045,12 @@
         <v>42.813</v>
       </c>
       <c r="K34" t="n">
-        <v>46.504</v>
+        <v>52.232</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>404.582</v>
+        <v>410.3099999999999</v>
       </c>
     </row>
   </sheetData>
@@ -41190,7 +41190,7 @@
         <v>285.545</v>
       </c>
       <c r="K34" t="n">
-        <v>293.57</v>
+        <v>293.1</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
@@ -45636,12 +45636,12 @@
         <v>37.966</v>
       </c>
       <c r="K31" t="n">
-        <v>24.296</v>
+        <v>26.455</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>105.39</v>
+        <v>107.549</v>
       </c>
     </row>
   </sheetData>
@@ -47038,12 +47038,12 @@
         <v>10.832</v>
       </c>
       <c r="K31" t="n">
-        <v>27.947</v>
+        <v>30.821</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>97.87700000000001</v>
+        <v>100.751</v>
       </c>
     </row>
   </sheetData>
@@ -49371,12 +49371,12 @@
         <v>34.902</v>
       </c>
       <c r="K23" t="n">
-        <v>5.975</v>
+        <v>6.813</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>117.336</v>
+        <v>118.174</v>
       </c>
     </row>
   </sheetData>
@@ -50405,12 +50405,12 @@
         <v>15.561</v>
       </c>
       <c r="K23" t="n">
-        <v>11.347</v>
+        <v>12.611</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>132.475</v>
+        <v>133.739</v>
       </c>
     </row>
   </sheetData>
@@ -52894,12 +52894,12 @@
         <v>67.5</v>
       </c>
       <c r="K34" t="n">
-        <v>21.81</v>
+        <v>22.93</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>152.76</v>
+        <v>153.88</v>
       </c>
     </row>
   </sheetData>
@@ -54428,12 +54428,12 @@
         <v>16.42</v>
       </c>
       <c r="K34" t="n">
-        <v>7.21</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>174.23</v>
+        <v>175.8200000000001</v>
       </c>
     </row>
   </sheetData>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -28302,13 +28302,13 @@
         <v>10</v>
       </c>
       <c r="D1269" t="n">
-        <v>77</v>
+        <v>80.23</v>
       </c>
       <c r="E1269" t="n">
-        <v>129.37</v>
+        <v>134.84</v>
       </c>
       <c r="F1269" t="n">
-        <v>271.53</v>
+        <v>269.12</v>
       </c>
     </row>
     <row r="1270">
@@ -42237,12 +42237,12 @@
         <v>129.81</v>
       </c>
       <c r="K23" t="n">
-        <v>77</v>
+        <v>80.23</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>318.82</v>
+        <v>322.05</v>
       </c>
     </row>
   </sheetData>
@@ -43271,12 +43271,12 @@
         <v>14.19</v>
       </c>
       <c r="K23" t="n">
-        <v>129.37</v>
+        <v>134.84</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>292.8</v>
+        <v>298.27</v>
       </c>
     </row>
   </sheetData>
@@ -44237,7 +44237,7 @@
         <v>325.6</v>
       </c>
       <c r="K23" t="n">
-        <v>271.53</v>
+        <v>269.12</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -8330,13 +8330,13 @@
         <v>10</v>
       </c>
       <c r="D359" t="n">
-        <v>26.455</v>
+        <v>28.242</v>
       </c>
       <c r="E359" t="n">
-        <v>30.821</v>
+        <v>33.196</v>
       </c>
       <c r="F359" t="n">
-        <v>79.411</v>
+        <v>77.994</v>
       </c>
     </row>
     <row r="360">
@@ -13902,13 +13902,13 @@
         <v>10</v>
       </c>
       <c r="D613" t="n">
-        <v>6.813</v>
+        <v>6.92</v>
       </c>
       <c r="E613" t="n">
-        <v>12.611</v>
+        <v>13.552</v>
       </c>
       <c r="F613" t="n">
-        <v>41.579</v>
+        <v>39.792</v>
       </c>
     </row>
     <row r="614">
@@ -22570,13 +22570,13 @@
         <v>10</v>
       </c>
       <c r="D1007" t="n">
-        <v>22.93</v>
+        <v>24.04</v>
       </c>
       <c r="E1007" t="n">
-        <v>8.800000000000001</v>
+        <v>10.15</v>
       </c>
       <c r="F1007" t="n">
-        <v>172.11</v>
+        <v>171.87</v>
       </c>
     </row>
     <row r="1008">
@@ -36114,13 +36114,13 @@
         <v>10</v>
       </c>
       <c r="D1663" t="n">
-        <v>56.198</v>
+        <v>59.202</v>
       </c>
       <c r="E1663" t="n">
-        <v>52.232</v>
+        <v>56.898</v>
       </c>
       <c r="F1663" t="n">
-        <v>293.1</v>
+        <v>289.656</v>
       </c>
     </row>
   </sheetData>
@@ -37548,7 +37548,7 @@
         <v>148.64</v>
       </c>
       <c r="K34" t="n">
-        <v>172.11</v>
+        <v>171.87</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
@@ -38791,12 +38791,12 @@
         <v>140.368</v>
       </c>
       <c r="K34" t="n">
-        <v>56.198</v>
+        <v>59.202</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>379.603</v>
+        <v>382.607</v>
       </c>
     </row>
   </sheetData>
@@ -40045,12 +40045,12 @@
         <v>42.813</v>
       </c>
       <c r="K34" t="n">
-        <v>52.232</v>
+        <v>56.898</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>410.3099999999999</v>
+        <v>414.976</v>
       </c>
     </row>
   </sheetData>
@@ -41190,7 +41190,7 @@
         <v>285.545</v>
       </c>
       <c r="K34" t="n">
-        <v>293.1</v>
+        <v>289.656</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
@@ -45636,12 +45636,12 @@
         <v>37.966</v>
       </c>
       <c r="K31" t="n">
-        <v>26.455</v>
+        <v>28.242</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>107.549</v>
+        <v>109.336</v>
       </c>
     </row>
   </sheetData>
@@ -47038,12 +47038,12 @@
         <v>10.832</v>
       </c>
       <c r="K31" t="n">
-        <v>30.821</v>
+        <v>33.196</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>100.751</v>
+        <v>103.126</v>
       </c>
     </row>
   </sheetData>
@@ -48348,7 +48348,7 @@
         <v>85.508</v>
       </c>
       <c r="K31" t="n">
-        <v>79.411</v>
+        <v>77.994</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
@@ -49371,12 +49371,12 @@
         <v>34.902</v>
       </c>
       <c r="K23" t="n">
-        <v>6.813</v>
+        <v>6.92</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>118.174</v>
+        <v>118.281</v>
       </c>
     </row>
   </sheetData>
@@ -50405,12 +50405,12 @@
         <v>15.561</v>
       </c>
       <c r="K23" t="n">
-        <v>12.611</v>
+        <v>13.552</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>133.739</v>
+        <v>134.68</v>
       </c>
     </row>
   </sheetData>
@@ -51363,7 +51363,7 @@
         <v>51.397</v>
       </c>
       <c r="K23" t="n">
-        <v>41.579</v>
+        <v>39.792</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
@@ -52894,12 +52894,12 @@
         <v>67.5</v>
       </c>
       <c r="K34" t="n">
-        <v>22.93</v>
+        <v>24.04</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>153.88</v>
+        <v>154.99</v>
       </c>
     </row>
   </sheetData>
@@ -54428,12 +54428,12 @@
         <v>16.42</v>
       </c>
       <c r="K34" t="n">
-        <v>8.800000000000001</v>
+        <v>10.15</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>175.8200000000001</v>
+        <v>177.17</v>
       </c>
     </row>
   </sheetData>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -8330,13 +8330,13 @@
         <v>10</v>
       </c>
       <c r="D359" t="n">
-        <v>28.242</v>
+        <v>29.68</v>
       </c>
       <c r="E359" t="n">
-        <v>33.196</v>
+        <v>35.568</v>
       </c>
       <c r="F359" t="n">
-        <v>77.994</v>
+        <v>77.059</v>
       </c>
     </row>
     <row r="360">
@@ -13902,13 +13902,13 @@
         <v>10</v>
       </c>
       <c r="D613" t="n">
-        <v>6.92</v>
+        <v>6.954</v>
       </c>
       <c r="E613" t="n">
-        <v>13.552</v>
+        <v>14.315</v>
       </c>
       <c r="F613" t="n">
-        <v>39.792</v>
+        <v>39.063</v>
       </c>
     </row>
     <row r="614">
@@ -22570,13 +22570,13 @@
         <v>10</v>
       </c>
       <c r="D1007" t="n">
-        <v>24.04</v>
+        <v>25.1</v>
       </c>
       <c r="E1007" t="n">
-        <v>10.15</v>
+        <v>11.45</v>
       </c>
       <c r="F1007" t="n">
-        <v>171.87</v>
+        <v>171.63</v>
       </c>
     </row>
     <row r="1008">
@@ -28302,13 +28302,13 @@
         <v>10</v>
       </c>
       <c r="D1269" t="n">
-        <v>80.23</v>
+        <v>83.43000000000001</v>
       </c>
       <c r="E1269" t="n">
-        <v>134.84</v>
+        <v>139.63</v>
       </c>
       <c r="F1269" t="n">
-        <v>269.12</v>
+        <v>267.36</v>
       </c>
     </row>
     <row r="1270">
@@ -36114,13 +36114,13 @@
         <v>10</v>
       </c>
       <c r="D1663" t="n">
-        <v>59.202</v>
+        <v>61.734</v>
       </c>
       <c r="E1663" t="n">
-        <v>56.898</v>
+        <v>61.333</v>
       </c>
       <c r="F1663" t="n">
-        <v>289.656</v>
+        <v>287.752</v>
       </c>
     </row>
   </sheetData>
@@ -37548,7 +37548,7 @@
         <v>148.64</v>
       </c>
       <c r="K34" t="n">
-        <v>171.87</v>
+        <v>171.63</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
@@ -38791,12 +38791,12 @@
         <v>140.368</v>
       </c>
       <c r="K34" t="n">
-        <v>59.202</v>
+        <v>61.734</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>382.607</v>
+        <v>385.139</v>
       </c>
     </row>
   </sheetData>
@@ -40045,12 +40045,12 @@
         <v>42.813</v>
       </c>
       <c r="K34" t="n">
-        <v>56.898</v>
+        <v>61.333</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>414.976</v>
+        <v>419.4109999999999</v>
       </c>
     </row>
   </sheetData>
@@ -41190,7 +41190,7 @@
         <v>285.545</v>
       </c>
       <c r="K34" t="n">
-        <v>289.656</v>
+        <v>287.752</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
@@ -42237,12 +42237,12 @@
         <v>129.81</v>
       </c>
       <c r="K23" t="n">
-        <v>80.23</v>
+        <v>83.43000000000001</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>322.05</v>
+        <v>325.25</v>
       </c>
     </row>
   </sheetData>
@@ -43271,12 +43271,12 @@
         <v>14.19</v>
       </c>
       <c r="K23" t="n">
-        <v>134.84</v>
+        <v>139.63</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>298.27</v>
+        <v>303.06</v>
       </c>
     </row>
   </sheetData>
@@ -44237,7 +44237,7 @@
         <v>325.6</v>
       </c>
       <c r="K23" t="n">
-        <v>269.12</v>
+        <v>267.36</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
@@ -45636,12 +45636,12 @@
         <v>37.966</v>
       </c>
       <c r="K31" t="n">
-        <v>28.242</v>
+        <v>29.68</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>109.336</v>
+        <v>110.774</v>
       </c>
     </row>
   </sheetData>
@@ -47038,12 +47038,12 @@
         <v>10.832</v>
       </c>
       <c r="K31" t="n">
-        <v>33.196</v>
+        <v>35.568</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>103.126</v>
+        <v>105.498</v>
       </c>
     </row>
   </sheetData>
@@ -48348,7 +48348,7 @@
         <v>85.508</v>
       </c>
       <c r="K31" t="n">
-        <v>77.994</v>
+        <v>77.059</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
@@ -49371,12 +49371,12 @@
         <v>34.902</v>
       </c>
       <c r="K23" t="n">
-        <v>6.92</v>
+        <v>6.954</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>118.281</v>
+        <v>118.315</v>
       </c>
     </row>
   </sheetData>
@@ -50405,12 +50405,12 @@
         <v>15.561</v>
       </c>
       <c r="K23" t="n">
-        <v>13.552</v>
+        <v>14.315</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>134.68</v>
+        <v>135.443</v>
       </c>
     </row>
   </sheetData>
@@ -51363,7 +51363,7 @@
         <v>51.397</v>
       </c>
       <c r="K23" t="n">
-        <v>39.792</v>
+        <v>39.063</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
@@ -52894,12 +52894,12 @@
         <v>67.5</v>
       </c>
       <c r="K34" t="n">
-        <v>24.04</v>
+        <v>25.1</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>154.99</v>
+        <v>156.05</v>
       </c>
     </row>
   </sheetData>
@@ -54428,12 +54428,12 @@
         <v>16.42</v>
       </c>
       <c r="K34" t="n">
-        <v>10.15</v>
+        <v>11.45</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>177.17</v>
+        <v>178.47</v>
       </c>
     </row>
   </sheetData>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -28302,13 +28302,13 @@
         <v>10</v>
       </c>
       <c r="D1269" t="n">
-        <v>83.43000000000001</v>
+        <v>85.22</v>
       </c>
       <c r="E1269" t="n">
-        <v>139.63</v>
+        <v>143.89</v>
       </c>
       <c r="F1269" t="n">
-        <v>267.36</v>
+        <v>264.72</v>
       </c>
     </row>
     <row r="1270">
@@ -42237,12 +42237,12 @@
         <v>129.81</v>
       </c>
       <c r="K23" t="n">
-        <v>83.43000000000001</v>
+        <v>85.22</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>325.25</v>
+        <v>327.04</v>
       </c>
     </row>
   </sheetData>
@@ -43271,12 +43271,12 @@
         <v>14.19</v>
       </c>
       <c r="K23" t="n">
-        <v>139.63</v>
+        <v>143.89</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>303.06</v>
+        <v>307.32</v>
       </c>
     </row>
   </sheetData>
@@ -44237,7 +44237,7 @@
         <v>325.6</v>
       </c>
       <c r="K23" t="n">
-        <v>267.36</v>
+        <v>264.72</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -8330,13 +8330,13 @@
         <v>10</v>
       </c>
       <c r="D359" t="n">
-        <v>29.68</v>
+        <v>32.504</v>
       </c>
       <c r="E359" t="n">
-        <v>35.568</v>
+        <v>37.926</v>
       </c>
       <c r="F359" t="n">
-        <v>77.059</v>
+        <v>77.526</v>
       </c>
     </row>
     <row r="360">
@@ -13902,13 +13902,13 @@
         <v>10</v>
       </c>
       <c r="D613" t="n">
-        <v>6.954</v>
+        <v>7.401</v>
       </c>
       <c r="E613" t="n">
-        <v>14.315</v>
+        <v>14.865</v>
       </c>
       <c r="F613" t="n">
-        <v>39.063</v>
+        <v>38.959</v>
       </c>
     </row>
     <row r="614">
@@ -36114,13 +36114,13 @@
         <v>10</v>
       </c>
       <c r="D1663" t="n">
-        <v>61.734</v>
+        <v>65.005</v>
       </c>
       <c r="E1663" t="n">
-        <v>61.333</v>
+        <v>64.241</v>
       </c>
       <c r="F1663" t="n">
-        <v>287.752</v>
+        <v>288.115</v>
       </c>
     </row>
   </sheetData>
@@ -38791,12 +38791,12 @@
         <v>140.368</v>
       </c>
       <c r="K34" t="n">
-        <v>61.734</v>
+        <v>65.005</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>385.139</v>
+        <v>388.41</v>
       </c>
     </row>
   </sheetData>
@@ -40045,12 +40045,12 @@
         <v>42.813</v>
       </c>
       <c r="K34" t="n">
-        <v>61.333</v>
+        <v>64.241</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>419.4109999999999</v>
+        <v>422.319</v>
       </c>
     </row>
   </sheetData>
@@ -41190,7 +41190,7 @@
         <v>285.545</v>
       </c>
       <c r="K34" t="n">
-        <v>287.752</v>
+        <v>288.115</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
@@ -45636,12 +45636,12 @@
         <v>37.966</v>
       </c>
       <c r="K31" t="n">
-        <v>29.68</v>
+        <v>32.504</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>110.774</v>
+        <v>113.598</v>
       </c>
     </row>
   </sheetData>
@@ -47038,12 +47038,12 @@
         <v>10.832</v>
       </c>
       <c r="K31" t="n">
-        <v>35.568</v>
+        <v>37.926</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>105.498</v>
+        <v>107.856</v>
       </c>
     </row>
   </sheetData>
@@ -48348,7 +48348,7 @@
         <v>85.508</v>
       </c>
       <c r="K31" t="n">
-        <v>77.059</v>
+        <v>77.526</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
@@ -49371,12 +49371,12 @@
         <v>34.902</v>
       </c>
       <c r="K23" t="n">
-        <v>6.954</v>
+        <v>7.401</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>118.315</v>
+        <v>118.762</v>
       </c>
     </row>
   </sheetData>
@@ -50405,12 +50405,12 @@
         <v>15.561</v>
       </c>
       <c r="K23" t="n">
-        <v>14.315</v>
+        <v>14.865</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>135.443</v>
+        <v>135.993</v>
       </c>
     </row>
   </sheetData>
@@ -51363,7 +51363,7 @@
         <v>51.397</v>
       </c>
       <c r="K23" t="n">
-        <v>39.063</v>
+        <v>38.959</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -22570,13 +22570,13 @@
         <v>10</v>
       </c>
       <c r="D1007" t="n">
-        <v>25.1</v>
+        <v>28.31</v>
       </c>
       <c r="E1007" t="n">
-        <v>11.45</v>
+        <v>12.75</v>
       </c>
       <c r="F1007" t="n">
-        <v>171.63</v>
+        <v>173.54</v>
       </c>
     </row>
     <row r="1008">
@@ -36114,13 +36114,13 @@
         <v>10</v>
       </c>
       <c r="D1663" t="n">
-        <v>65.005</v>
+        <v>68.215</v>
       </c>
       <c r="E1663" t="n">
-        <v>64.241</v>
+        <v>65.541</v>
       </c>
       <c r="F1663" t="n">
-        <v>288.115</v>
+        <v>290.025</v>
       </c>
     </row>
   </sheetData>
@@ -37548,7 +37548,7 @@
         <v>148.64</v>
       </c>
       <c r="K34" t="n">
-        <v>171.63</v>
+        <v>173.54</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
@@ -38791,12 +38791,12 @@
         <v>140.368</v>
       </c>
       <c r="K34" t="n">
-        <v>65.005</v>
+        <v>68.215</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>388.41</v>
+        <v>391.62</v>
       </c>
     </row>
   </sheetData>
@@ -40045,12 +40045,12 @@
         <v>42.813</v>
       </c>
       <c r="K34" t="n">
-        <v>64.241</v>
+        <v>65.541</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>422.319</v>
+        <v>423.619</v>
       </c>
     </row>
   </sheetData>
@@ -41190,7 +41190,7 @@
         <v>285.545</v>
       </c>
       <c r="K34" t="n">
-        <v>288.115</v>
+        <v>290.025</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
@@ -52894,12 +52894,12 @@
         <v>67.5</v>
       </c>
       <c r="K34" t="n">
-        <v>25.1</v>
+        <v>28.31</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>156.05</v>
+        <v>159.26</v>
       </c>
     </row>
   </sheetData>
@@ -54428,12 +54428,12 @@
         <v>16.42</v>
       </c>
       <c r="K34" t="n">
-        <v>11.45</v>
+        <v>12.75</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>178.47</v>
+        <v>179.77</v>
       </c>
     </row>
   </sheetData>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -28302,13 +28302,13 @@
         <v>10</v>
       </c>
       <c r="D1269" t="n">
-        <v>85.22</v>
+        <v>87.15000000000001</v>
       </c>
       <c r="E1269" t="n">
-        <v>143.89</v>
+        <v>147.41</v>
       </c>
       <c r="F1269" t="n">
-        <v>264.72</v>
+        <v>262.96</v>
       </c>
     </row>
     <row r="1270">
@@ -42237,12 +42237,12 @@
         <v>129.81</v>
       </c>
       <c r="K23" t="n">
-        <v>85.22</v>
+        <v>87.15000000000001</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>327.04</v>
+        <v>328.97</v>
       </c>
     </row>
   </sheetData>
@@ -43271,12 +43271,12 @@
         <v>14.19</v>
       </c>
       <c r="K23" t="n">
-        <v>143.89</v>
+        <v>147.41</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>307.32</v>
+        <v>310.84</v>
       </c>
     </row>
   </sheetData>
@@ -44237,7 +44237,7 @@
         <v>325.6</v>
       </c>
       <c r="K23" t="n">
-        <v>264.72</v>
+        <v>262.96</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -8330,13 +8330,13 @@
         <v>10</v>
       </c>
       <c r="D359" t="n">
-        <v>32.504</v>
+        <v>34.516</v>
       </c>
       <c r="E359" t="n">
-        <v>37.926</v>
+        <v>40.288</v>
       </c>
       <c r="F359" t="n">
-        <v>77.526</v>
+        <v>77.176</v>
       </c>
     </row>
     <row r="360">
@@ -13902,13 +13902,13 @@
         <v>10</v>
       </c>
       <c r="D613" t="n">
-        <v>7.401</v>
+        <v>7.848</v>
       </c>
       <c r="E613" t="n">
-        <v>14.865</v>
+        <v>15.415</v>
       </c>
       <c r="F613" t="n">
-        <v>38.959</v>
+        <v>38.856</v>
       </c>
     </row>
     <row r="614">
@@ -22570,13 +22570,13 @@
         <v>10</v>
       </c>
       <c r="D1007" t="n">
-        <v>28.31</v>
+        <v>29.43</v>
       </c>
       <c r="E1007" t="n">
-        <v>12.75</v>
+        <v>13.39</v>
       </c>
       <c r="F1007" t="n">
-        <v>173.54</v>
+        <v>174.02</v>
       </c>
     </row>
     <row r="1008">
@@ -36114,13 +36114,13 @@
         <v>10</v>
       </c>
       <c r="D1663" t="n">
-        <v>68.215</v>
+        <v>71.794</v>
       </c>
       <c r="E1663" t="n">
-        <v>65.541</v>
+        <v>69.093</v>
       </c>
       <c r="F1663" t="n">
-        <v>290.025</v>
+        <v>290.052</v>
       </c>
     </row>
   </sheetData>
@@ -37548,7 +37548,7 @@
         <v>148.64</v>
       </c>
       <c r="K34" t="n">
-        <v>173.54</v>
+        <v>174.02</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
@@ -38791,12 +38791,12 @@
         <v>140.368</v>
       </c>
       <c r="K34" t="n">
-        <v>68.215</v>
+        <v>71.794</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>391.62</v>
+        <v>395.199</v>
       </c>
     </row>
   </sheetData>
@@ -40045,12 +40045,12 @@
         <v>42.813</v>
       </c>
       <c r="K34" t="n">
-        <v>65.541</v>
+        <v>69.093</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>423.619</v>
+        <v>427.171</v>
       </c>
     </row>
   </sheetData>
@@ -41190,7 +41190,7 @@
         <v>285.545</v>
       </c>
       <c r="K34" t="n">
-        <v>290.025</v>
+        <v>290.052</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
@@ -45636,12 +45636,12 @@
         <v>37.966</v>
       </c>
       <c r="K31" t="n">
-        <v>32.504</v>
+        <v>34.516</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>113.598</v>
+        <v>115.61</v>
       </c>
     </row>
   </sheetData>
@@ -47038,12 +47038,12 @@
         <v>10.832</v>
       </c>
       <c r="K31" t="n">
-        <v>37.926</v>
+        <v>40.288</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>107.856</v>
+        <v>110.218</v>
       </c>
     </row>
   </sheetData>
@@ -48348,7 +48348,7 @@
         <v>85.508</v>
       </c>
       <c r="K31" t="n">
-        <v>77.526</v>
+        <v>77.176</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
@@ -49371,12 +49371,12 @@
         <v>34.902</v>
       </c>
       <c r="K23" t="n">
-        <v>7.401</v>
+        <v>7.848</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>118.762</v>
+        <v>119.209</v>
       </c>
     </row>
   </sheetData>
@@ -50405,12 +50405,12 @@
         <v>15.561</v>
       </c>
       <c r="K23" t="n">
-        <v>14.865</v>
+        <v>15.415</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>135.993</v>
+        <v>136.543</v>
       </c>
     </row>
   </sheetData>
@@ -51363,7 +51363,7 @@
         <v>51.397</v>
       </c>
       <c r="K23" t="n">
-        <v>38.959</v>
+        <v>38.856</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
@@ -52894,12 +52894,12 @@
         <v>67.5</v>
       </c>
       <c r="K34" t="n">
-        <v>28.31</v>
+        <v>29.43</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>159.26</v>
+        <v>160.38</v>
       </c>
     </row>
   </sheetData>
@@ -54428,12 +54428,12 @@
         <v>16.42</v>
       </c>
       <c r="K34" t="n">
-        <v>12.75</v>
+        <v>13.39</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>179.77</v>
+        <v>180.41</v>
       </c>
     </row>
   </sheetData>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -28302,13 +28302,13 @@
         <v>10</v>
       </c>
       <c r="D1269" t="n">
-        <v>87.15000000000001</v>
+        <v>89.06</v>
       </c>
       <c r="E1269" t="n">
-        <v>147.41</v>
+        <v>150.47</v>
       </c>
       <c r="F1269" t="n">
-        <v>262.96</v>
+        <v>261.64</v>
       </c>
     </row>
     <row r="1270">
@@ -42237,12 +42237,12 @@
         <v>129.81</v>
       </c>
       <c r="K23" t="n">
-        <v>87.15000000000001</v>
+        <v>89.06</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>328.97</v>
+        <v>330.88</v>
       </c>
     </row>
   </sheetData>
@@ -43271,12 +43271,12 @@
         <v>14.19</v>
       </c>
       <c r="K23" t="n">
-        <v>147.41</v>
+        <v>150.47</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>310.84</v>
+        <v>313.9</v>
       </c>
     </row>
   </sheetData>
@@ -44237,7 +44237,7 @@
         <v>325.6</v>
       </c>
       <c r="K23" t="n">
-        <v>262.96</v>
+        <v>261.64</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -8330,10 +8330,10 @@
         <v>10</v>
       </c>
       <c r="D359" t="n">
-        <v>34.516</v>
+        <v>36.528</v>
       </c>
       <c r="E359" t="n">
-        <v>40.288</v>
+        <v>42.65</v>
       </c>
       <c r="F359" t="n">
         <v>77.176</v>
@@ -13902,10 +13902,10 @@
         <v>10</v>
       </c>
       <c r="D613" t="n">
-        <v>7.848</v>
+        <v>8.295</v>
       </c>
       <c r="E613" t="n">
-        <v>15.415</v>
+        <v>15.965</v>
       </c>
       <c r="F613" t="n">
         <v>38.856</v>
@@ -22570,13 +22570,13 @@
         <v>10</v>
       </c>
       <c r="D1007" t="n">
-        <v>29.43</v>
+        <v>36.71</v>
       </c>
       <c r="E1007" t="n">
-        <v>13.39</v>
+        <v>14.23</v>
       </c>
       <c r="F1007" t="n">
-        <v>174.02</v>
+        <v>180.46</v>
       </c>
     </row>
     <row r="1008">
@@ -36114,13 +36114,13 @@
         <v>10</v>
       </c>
       <c r="D1663" t="n">
-        <v>71.794</v>
+        <v>81.533</v>
       </c>
       <c r="E1663" t="n">
-        <v>69.093</v>
+        <v>72.845</v>
       </c>
       <c r="F1663" t="n">
-        <v>290.052</v>
+        <v>296.492</v>
       </c>
     </row>
   </sheetData>
@@ -37548,7 +37548,7 @@
         <v>148.64</v>
       </c>
       <c r="K34" t="n">
-        <v>174.02</v>
+        <v>180.46</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
@@ -38791,12 +38791,12 @@
         <v>140.368</v>
       </c>
       <c r="K34" t="n">
-        <v>71.794</v>
+        <v>81.533</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>395.199</v>
+        <v>404.938</v>
       </c>
     </row>
   </sheetData>
@@ -40045,12 +40045,12 @@
         <v>42.813</v>
       </c>
       <c r="K34" t="n">
-        <v>69.093</v>
+        <v>72.845</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>427.171</v>
+        <v>430.923</v>
       </c>
     </row>
   </sheetData>
@@ -41190,7 +41190,7 @@
         <v>285.545</v>
       </c>
       <c r="K34" t="n">
-        <v>290.052</v>
+        <v>296.492</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
@@ -45636,12 +45636,12 @@
         <v>37.966</v>
       </c>
       <c r="K31" t="n">
-        <v>34.516</v>
+        <v>36.528</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>115.61</v>
+        <v>117.622</v>
       </c>
     </row>
   </sheetData>
@@ -47038,12 +47038,12 @@
         <v>10.832</v>
       </c>
       <c r="K31" t="n">
-        <v>40.288</v>
+        <v>42.65</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>110.218</v>
+        <v>112.58</v>
       </c>
     </row>
   </sheetData>
@@ -49371,12 +49371,12 @@
         <v>34.902</v>
       </c>
       <c r="K23" t="n">
-        <v>7.848</v>
+        <v>8.295</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>119.209</v>
+        <v>119.656</v>
       </c>
     </row>
   </sheetData>
@@ -50405,12 +50405,12 @@
         <v>15.561</v>
       </c>
       <c r="K23" t="n">
-        <v>15.415</v>
+        <v>15.965</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>136.543</v>
+        <v>137.093</v>
       </c>
     </row>
   </sheetData>
@@ -52894,12 +52894,12 @@
         <v>67.5</v>
       </c>
       <c r="K34" t="n">
-        <v>29.43</v>
+        <v>36.71</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>160.38</v>
+        <v>167.66</v>
       </c>
     </row>
   </sheetData>
@@ -54428,12 +54428,12 @@
         <v>16.42</v>
       </c>
       <c r="K34" t="n">
-        <v>13.39</v>
+        <v>14.23</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>180.41</v>
+        <v>181.25</v>
       </c>
     </row>
   </sheetData>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -28302,13 +28302,13 @@
         <v>10</v>
       </c>
       <c r="D1269" t="n">
-        <v>89.06</v>
+        <v>93.26000000000001</v>
       </c>
       <c r="E1269" t="n">
-        <v>150.47</v>
+        <v>150.98</v>
       </c>
       <c r="F1269" t="n">
-        <v>261.64</v>
+        <v>265.16</v>
       </c>
     </row>
     <row r="1270">
@@ -42237,12 +42237,12 @@
         <v>129.81</v>
       </c>
       <c r="K23" t="n">
-        <v>89.06</v>
+        <v>93.26000000000001</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>330.88</v>
+        <v>335.08</v>
       </c>
     </row>
   </sheetData>
@@ -43271,12 +43271,12 @@
         <v>14.19</v>
       </c>
       <c r="K23" t="n">
-        <v>150.47</v>
+        <v>150.98</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>313.9</v>
+        <v>314.41</v>
       </c>
     </row>
   </sheetData>
@@ -44237,7 +44237,7 @@
         <v>325.6</v>
       </c>
       <c r="K23" t="n">
-        <v>261.64</v>
+        <v>265.16</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -8330,13 +8330,13 @@
         <v>10</v>
       </c>
       <c r="D359" t="n">
-        <v>36.528</v>
+        <v>40.178</v>
       </c>
       <c r="E359" t="n">
-        <v>42.65</v>
+        <v>45.01</v>
       </c>
       <c r="F359" t="n">
-        <v>77.176</v>
+        <v>78.58199999999999</v>
       </c>
     </row>
     <row r="360">
@@ -13902,13 +13902,13 @@
         <v>10</v>
       </c>
       <c r="D613" t="n">
-        <v>8.295</v>
+        <v>9.055</v>
       </c>
       <c r="E613" t="n">
-        <v>15.965</v>
+        <v>16.515</v>
       </c>
       <c r="F613" t="n">
-        <v>38.856</v>
+        <v>40.002</v>
       </c>
     </row>
     <row r="614">
@@ -36114,13 +36114,13 @@
         <v>10</v>
       </c>
       <c r="D1663" t="n">
-        <v>81.533</v>
+        <v>85.943</v>
       </c>
       <c r="E1663" t="n">
-        <v>72.845</v>
+        <v>75.755</v>
       </c>
       <c r="F1663" t="n">
-        <v>296.492</v>
+        <v>299.044</v>
       </c>
     </row>
   </sheetData>
@@ -38791,12 +38791,12 @@
         <v>140.368</v>
       </c>
       <c r="K34" t="n">
-        <v>81.533</v>
+        <v>85.943</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>404.938</v>
+        <v>409.348</v>
       </c>
     </row>
   </sheetData>
@@ -40045,12 +40045,12 @@
         <v>42.813</v>
       </c>
       <c r="K34" t="n">
-        <v>72.845</v>
+        <v>75.755</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>430.923</v>
+        <v>433.833</v>
       </c>
     </row>
   </sheetData>
@@ -41190,7 +41190,7 @@
         <v>285.545</v>
       </c>
       <c r="K34" t="n">
-        <v>296.492</v>
+        <v>299.044</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
@@ -45636,12 +45636,12 @@
         <v>37.966</v>
       </c>
       <c r="K31" t="n">
-        <v>36.528</v>
+        <v>40.178</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>117.622</v>
+        <v>121.272</v>
       </c>
     </row>
   </sheetData>
@@ -47038,12 +47038,12 @@
         <v>10.832</v>
       </c>
       <c r="K31" t="n">
-        <v>42.65</v>
+        <v>45.01</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>112.58</v>
+        <v>114.94</v>
       </c>
     </row>
   </sheetData>
@@ -48348,7 +48348,7 @@
         <v>85.508</v>
       </c>
       <c r="K31" t="n">
-        <v>77.176</v>
+        <v>78.58199999999999</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
@@ -49371,12 +49371,12 @@
         <v>34.902</v>
       </c>
       <c r="K23" t="n">
-        <v>8.295</v>
+        <v>9.055</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>119.656</v>
+        <v>120.416</v>
       </c>
     </row>
   </sheetData>
@@ -50405,12 +50405,12 @@
         <v>15.561</v>
       </c>
       <c r="K23" t="n">
-        <v>15.965</v>
+        <v>16.515</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>137.093</v>
+        <v>137.643</v>
       </c>
     </row>
   </sheetData>
@@ -51363,7 +51363,7 @@
         <v>51.397</v>
       </c>
       <c r="K23" t="n">
-        <v>38.856</v>
+        <v>40.002</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -22570,13 +22570,13 @@
         <v>10</v>
       </c>
       <c r="D1007" t="n">
-        <v>36.71</v>
+        <v>40.92</v>
       </c>
       <c r="E1007" t="n">
-        <v>14.23</v>
+        <v>15.81</v>
       </c>
       <c r="F1007" t="n">
-        <v>180.46</v>
+        <v>183.09</v>
       </c>
     </row>
     <row r="1008">
@@ -36114,13 +36114,13 @@
         <v>10</v>
       </c>
       <c r="D1663" t="n">
-        <v>85.943</v>
+        <v>90.15300000000001</v>
       </c>
       <c r="E1663" t="n">
-        <v>75.755</v>
+        <v>77.33499999999999</v>
       </c>
       <c r="F1663" t="n">
-        <v>299.044</v>
+        <v>301.674</v>
       </c>
     </row>
   </sheetData>
@@ -37548,7 +37548,7 @@
         <v>148.64</v>
       </c>
       <c r="K34" t="n">
-        <v>180.46</v>
+        <v>183.09</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
@@ -38791,12 +38791,12 @@
         <v>140.368</v>
       </c>
       <c r="K34" t="n">
-        <v>85.943</v>
+        <v>90.15300000000001</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>409.348</v>
+        <v>413.558</v>
       </c>
     </row>
   </sheetData>
@@ -40045,12 +40045,12 @@
         <v>42.813</v>
       </c>
       <c r="K34" t="n">
-        <v>75.755</v>
+        <v>77.33499999999999</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>433.833</v>
+        <v>435.413</v>
       </c>
     </row>
   </sheetData>
@@ -41190,7 +41190,7 @@
         <v>285.545</v>
       </c>
       <c r="K34" t="n">
-        <v>299.044</v>
+        <v>301.674</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
@@ -52894,12 +52894,12 @@
         <v>67.5</v>
       </c>
       <c r="K34" t="n">
-        <v>36.71</v>
+        <v>40.92</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>167.66</v>
+        <v>171.87</v>
       </c>
     </row>
   </sheetData>
@@ -54428,12 +54428,12 @@
         <v>16.42</v>
       </c>
       <c r="K34" t="n">
-        <v>14.23</v>
+        <v>15.81</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>181.25</v>
+        <v>182.83</v>
       </c>
     </row>
   </sheetData>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -28302,13 +28302,13 @@
         <v>10</v>
       </c>
       <c r="D1269" t="n">
-        <v>93.26000000000001</v>
+        <v>94.59</v>
       </c>
       <c r="E1269" t="n">
-        <v>150.98</v>
+        <v>151.26</v>
       </c>
       <c r="F1269" t="n">
-        <v>265.16</v>
+        <v>266.04</v>
       </c>
     </row>
     <row r="1270">
@@ -42237,12 +42237,12 @@
         <v>129.81</v>
       </c>
       <c r="K23" t="n">
-        <v>93.26000000000001</v>
+        <v>94.59</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>335.08</v>
+        <v>336.41</v>
       </c>
     </row>
   </sheetData>
@@ -43271,12 +43271,12 @@
         <v>14.19</v>
       </c>
       <c r="K23" t="n">
-        <v>150.98</v>
+        <v>151.26</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>314.41</v>
+        <v>314.69</v>
       </c>
     </row>
   </sheetData>
@@ -44237,7 +44237,7 @@
         <v>325.6</v>
       </c>
       <c r="K23" t="n">
-        <v>265.16</v>
+        <v>266.04</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -8330,13 +8330,13 @@
         <v>10</v>
       </c>
       <c r="D359" t="n">
-        <v>40.178</v>
+        <v>42.078</v>
       </c>
       <c r="E359" t="n">
-        <v>45.01</v>
+        <v>47.38</v>
       </c>
       <c r="F359" t="n">
-        <v>78.58199999999999</v>
+        <v>78.111</v>
       </c>
     </row>
     <row r="360">
@@ -13902,10 +13902,10 @@
         <v>10</v>
       </c>
       <c r="D613" t="n">
-        <v>9.055</v>
+        <v>9.608000000000001</v>
       </c>
       <c r="E613" t="n">
-        <v>16.515</v>
+        <v>17.068</v>
       </c>
       <c r="F613" t="n">
         <v>40.002</v>
@@ -22570,13 +22570,13 @@
         <v>10</v>
       </c>
       <c r="D1007" t="n">
-        <v>40.92</v>
+        <v>43.24</v>
       </c>
       <c r="E1007" t="n">
-        <v>15.81</v>
+        <v>18.85</v>
       </c>
       <c r="F1007" t="n">
-        <v>183.09</v>
+        <v>182.37</v>
       </c>
     </row>
     <row r="1008">
@@ -36114,13 +36114,13 @@
         <v>10</v>
       </c>
       <c r="D1663" t="n">
-        <v>90.15300000000001</v>
+        <v>94.926</v>
       </c>
       <c r="E1663" t="n">
-        <v>77.33499999999999</v>
+        <v>83.298</v>
       </c>
       <c r="F1663" t="n">
-        <v>301.674</v>
+        <v>300.483</v>
       </c>
     </row>
   </sheetData>
@@ -37548,7 +37548,7 @@
         <v>148.64</v>
       </c>
       <c r="K34" t="n">
-        <v>183.09</v>
+        <v>182.37</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
@@ -38791,12 +38791,12 @@
         <v>140.368</v>
       </c>
       <c r="K34" t="n">
-        <v>90.15300000000001</v>
+        <v>94.926</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>413.558</v>
+        <v>418.331</v>
       </c>
     </row>
   </sheetData>
@@ -40045,12 +40045,12 @@
         <v>42.813</v>
       </c>
       <c r="K34" t="n">
-        <v>77.33499999999999</v>
+        <v>83.298</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>435.413</v>
+        <v>441.376</v>
       </c>
     </row>
   </sheetData>
@@ -41190,7 +41190,7 @@
         <v>285.545</v>
       </c>
       <c r="K34" t="n">
-        <v>301.674</v>
+        <v>300.483</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
@@ -45636,12 +45636,12 @@
         <v>37.966</v>
       </c>
       <c r="K31" t="n">
-        <v>40.178</v>
+        <v>42.078</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>121.272</v>
+        <v>123.172</v>
       </c>
     </row>
   </sheetData>
@@ -47038,12 +47038,12 @@
         <v>10.832</v>
       </c>
       <c r="K31" t="n">
-        <v>45.01</v>
+        <v>47.38</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>114.94</v>
+        <v>117.31</v>
       </c>
     </row>
   </sheetData>
@@ -48348,7 +48348,7 @@
         <v>85.508</v>
       </c>
       <c r="K31" t="n">
-        <v>78.58199999999999</v>
+        <v>78.111</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
@@ -49371,12 +49371,12 @@
         <v>34.902</v>
       </c>
       <c r="K23" t="n">
-        <v>9.055</v>
+        <v>9.608000000000001</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>120.416</v>
+        <v>120.969</v>
       </c>
     </row>
   </sheetData>
@@ -50405,12 +50405,12 @@
         <v>15.561</v>
       </c>
       <c r="K23" t="n">
-        <v>16.515</v>
+        <v>17.068</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>137.643</v>
+        <v>138.196</v>
       </c>
     </row>
   </sheetData>
@@ -52894,12 +52894,12 @@
         <v>67.5</v>
       </c>
       <c r="K34" t="n">
-        <v>40.92</v>
+        <v>43.24</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>171.87</v>
+        <v>174.19</v>
       </c>
     </row>
   </sheetData>
@@ -54428,12 +54428,12 @@
         <v>16.42</v>
       </c>
       <c r="K34" t="n">
-        <v>15.81</v>
+        <v>18.85</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>182.83</v>
+        <v>185.87</v>
       </c>
     </row>
   </sheetData>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -22570,13 +22570,13 @@
         <v>10</v>
       </c>
       <c r="D1007" t="n">
-        <v>43.24</v>
+        <v>48.44</v>
       </c>
       <c r="E1007" t="n">
-        <v>18.85</v>
+        <v>21.9</v>
       </c>
       <c r="F1007" t="n">
-        <v>182.37</v>
+        <v>184.52</v>
       </c>
     </row>
     <row r="1008">
@@ -28302,13 +28302,13 @@
         <v>10</v>
       </c>
       <c r="D1269" t="n">
-        <v>94.59</v>
+        <v>97.68000000000001</v>
       </c>
       <c r="E1269" t="n">
-        <v>151.26</v>
+        <v>151.54</v>
       </c>
       <c r="F1269" t="n">
-        <v>266.04</v>
+        <v>268.68</v>
       </c>
     </row>
     <row r="1270">
@@ -36114,13 +36114,13 @@
         <v>10</v>
       </c>
       <c r="D1663" t="n">
-        <v>94.926</v>
+        <v>100.126</v>
       </c>
       <c r="E1663" t="n">
-        <v>83.298</v>
+        <v>86.348</v>
       </c>
       <c r="F1663" t="n">
-        <v>300.483</v>
+        <v>302.633</v>
       </c>
     </row>
   </sheetData>
@@ -37548,7 +37548,7 @@
         <v>148.64</v>
       </c>
       <c r="K34" t="n">
-        <v>182.37</v>
+        <v>184.52</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
@@ -38791,12 +38791,12 @@
         <v>140.368</v>
       </c>
       <c r="K34" t="n">
-        <v>94.926</v>
+        <v>100.126</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>418.331</v>
+        <v>423.5309999999999</v>
       </c>
     </row>
   </sheetData>
@@ -40045,12 +40045,12 @@
         <v>42.813</v>
       </c>
       <c r="K34" t="n">
-        <v>83.298</v>
+        <v>86.348</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>441.376</v>
+        <v>444.426</v>
       </c>
     </row>
   </sheetData>
@@ -41190,7 +41190,7 @@
         <v>285.545</v>
       </c>
       <c r="K34" t="n">
-        <v>300.483</v>
+        <v>302.633</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
@@ -42237,12 +42237,12 @@
         <v>129.81</v>
       </c>
       <c r="K23" t="n">
-        <v>94.59</v>
+        <v>97.68000000000001</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>336.41</v>
+        <v>339.5</v>
       </c>
     </row>
   </sheetData>
@@ -43271,12 +43271,12 @@
         <v>14.19</v>
       </c>
       <c r="K23" t="n">
-        <v>151.26</v>
+        <v>151.54</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>314.69</v>
+        <v>314.97</v>
       </c>
     </row>
   </sheetData>
@@ -44237,7 +44237,7 @@
         <v>325.6</v>
       </c>
       <c r="K23" t="n">
-        <v>266.04</v>
+        <v>268.68</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
@@ -52894,12 +52894,12 @@
         <v>67.5</v>
       </c>
       <c r="K34" t="n">
-        <v>43.24</v>
+        <v>48.44</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>174.19</v>
+        <v>179.39</v>
       </c>
     </row>
   </sheetData>
@@ -54428,12 +54428,12 @@
         <v>16.42</v>
       </c>
       <c r="K34" t="n">
-        <v>18.85</v>
+        <v>21.9</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>185.87</v>
+        <v>188.92</v>
       </c>
     </row>
   </sheetData>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -8330,10 +8330,10 @@
         <v>10</v>
       </c>
       <c r="D359" t="n">
-        <v>42.078</v>
+        <v>43.978</v>
       </c>
       <c r="E359" t="n">
-        <v>47.38</v>
+        <v>49.75</v>
       </c>
       <c r="F359" t="n">
         <v>78.111</v>
@@ -13902,10 +13902,10 @@
         <v>10</v>
       </c>
       <c r="D613" t="n">
-        <v>9.608000000000001</v>
+        <v>10.161</v>
       </c>
       <c r="E613" t="n">
-        <v>17.068</v>
+        <v>17.621</v>
       </c>
       <c r="F613" t="n">
         <v>40.002</v>
@@ -36114,10 +36114,10 @@
         <v>10</v>
       </c>
       <c r="D1663" t="n">
-        <v>100.126</v>
+        <v>102.579</v>
       </c>
       <c r="E1663" t="n">
-        <v>86.348</v>
+        <v>89.271</v>
       </c>
       <c r="F1663" t="n">
         <v>302.633</v>
@@ -38791,12 +38791,12 @@
         <v>140.368</v>
       </c>
       <c r="K34" t="n">
-        <v>100.126</v>
+        <v>102.579</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>423.5309999999999</v>
+        <v>425.984</v>
       </c>
     </row>
   </sheetData>
@@ -40045,12 +40045,12 @@
         <v>42.813</v>
       </c>
       <c r="K34" t="n">
-        <v>86.348</v>
+        <v>89.271</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>444.426</v>
+        <v>447.349</v>
       </c>
     </row>
   </sheetData>
@@ -45636,12 +45636,12 @@
         <v>37.966</v>
       </c>
       <c r="K31" t="n">
-        <v>42.078</v>
+        <v>43.978</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>123.172</v>
+        <v>125.072</v>
       </c>
     </row>
   </sheetData>
@@ -47038,12 +47038,12 @@
         <v>10.832</v>
       </c>
       <c r="K31" t="n">
-        <v>47.38</v>
+        <v>49.75</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>117.31</v>
+        <v>119.68</v>
       </c>
     </row>
   </sheetData>
@@ -49371,12 +49371,12 @@
         <v>34.902</v>
       </c>
       <c r="K23" t="n">
-        <v>9.608000000000001</v>
+        <v>10.161</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>120.969</v>
+        <v>121.522</v>
       </c>
     </row>
   </sheetData>
@@ -50405,12 +50405,12 @@
         <v>15.561</v>
       </c>
       <c r="K23" t="n">
-        <v>17.068</v>
+        <v>17.621</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>138.196</v>
+        <v>138.749</v>
       </c>
     </row>
   </sheetData>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -28302,10 +28302,10 @@
         <v>10</v>
       </c>
       <c r="D1269" t="n">
-        <v>97.68000000000001</v>
+        <v>98.37</v>
       </c>
       <c r="E1269" t="n">
-        <v>151.54</v>
+        <v>152.06</v>
       </c>
       <c r="F1269" t="n">
         <v>268.68</v>
@@ -42237,12 +42237,12 @@
         <v>129.81</v>
       </c>
       <c r="K23" t="n">
-        <v>97.68000000000001</v>
+        <v>98.37</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>339.5</v>
+        <v>340.19</v>
       </c>
     </row>
   </sheetData>
@@ -43271,12 +43271,12 @@
         <v>14.19</v>
       </c>
       <c r="K23" t="n">
-        <v>151.54</v>
+        <v>152.06</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>314.97</v>
+        <v>315.49</v>
       </c>
     </row>
   </sheetData>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -8330,13 +8330,13 @@
         <v>10</v>
       </c>
       <c r="D359" t="n">
-        <v>43.978</v>
+        <v>46.114</v>
       </c>
       <c r="E359" t="n">
-        <v>49.75</v>
+        <v>52.122</v>
       </c>
       <c r="F359" t="n">
-        <v>78.111</v>
+        <v>78.58199999999999</v>
       </c>
     </row>
     <row r="360">
@@ -13902,13 +13902,13 @@
         <v>10</v>
       </c>
       <c r="D613" t="n">
-        <v>10.161</v>
+        <v>10.506</v>
       </c>
       <c r="E613" t="n">
-        <v>17.621</v>
+        <v>18.174</v>
       </c>
       <c r="F613" t="n">
-        <v>40.002</v>
+        <v>39.479</v>
       </c>
     </row>
     <row r="614">
@@ -22570,13 +22570,13 @@
         <v>10</v>
       </c>
       <c r="D1007" t="n">
-        <v>48.44</v>
+        <v>51.64</v>
       </c>
       <c r="E1007" t="n">
-        <v>21.9</v>
+        <v>25.58</v>
       </c>
       <c r="F1007" t="n">
-        <v>184.52</v>
+        <v>184.04</v>
       </c>
     </row>
     <row r="1008">
@@ -36114,13 +36114,13 @@
         <v>10</v>
       </c>
       <c r="D1663" t="n">
-        <v>102.579</v>
+        <v>108.26</v>
       </c>
       <c r="E1663" t="n">
-        <v>89.271</v>
+        <v>95.876</v>
       </c>
       <c r="F1663" t="n">
-        <v>302.633</v>
+        <v>302.101</v>
       </c>
     </row>
   </sheetData>
@@ -37548,7 +37548,7 @@
         <v>148.64</v>
       </c>
       <c r="K34" t="n">
-        <v>184.52</v>
+        <v>184.04</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
@@ -38791,12 +38791,12 @@
         <v>140.368</v>
       </c>
       <c r="K34" t="n">
-        <v>102.579</v>
+        <v>108.26</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>425.984</v>
+        <v>431.665</v>
       </c>
     </row>
   </sheetData>
@@ -40045,12 +40045,12 @@
         <v>42.813</v>
       </c>
       <c r="K34" t="n">
-        <v>89.271</v>
+        <v>95.876</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>447.349</v>
+        <v>453.954</v>
       </c>
     </row>
   </sheetData>
@@ -41190,7 +41190,7 @@
         <v>285.545</v>
       </c>
       <c r="K34" t="n">
-        <v>302.633</v>
+        <v>302.101</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
@@ -45636,12 +45636,12 @@
         <v>37.966</v>
       </c>
       <c r="K31" t="n">
-        <v>43.978</v>
+        <v>46.114</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>125.072</v>
+        <v>127.208</v>
       </c>
     </row>
   </sheetData>
@@ -47038,12 +47038,12 @@
         <v>10.832</v>
       </c>
       <c r="K31" t="n">
-        <v>49.75</v>
+        <v>52.122</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>119.68</v>
+        <v>122.052</v>
       </c>
     </row>
   </sheetData>
@@ -48348,7 +48348,7 @@
         <v>85.508</v>
       </c>
       <c r="K31" t="n">
-        <v>78.111</v>
+        <v>78.58199999999999</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
@@ -49371,12 +49371,12 @@
         <v>34.902</v>
       </c>
       <c r="K23" t="n">
-        <v>10.161</v>
+        <v>10.506</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>121.522</v>
+        <v>121.867</v>
       </c>
     </row>
   </sheetData>
@@ -50405,12 +50405,12 @@
         <v>15.561</v>
       </c>
       <c r="K23" t="n">
-        <v>17.621</v>
+        <v>18.174</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>138.749</v>
+        <v>139.302</v>
       </c>
     </row>
   </sheetData>
@@ -51363,7 +51363,7 @@
         <v>51.397</v>
       </c>
       <c r="K23" t="n">
-        <v>40.002</v>
+        <v>39.479</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
@@ -52894,12 +52894,12 @@
         <v>67.5</v>
       </c>
       <c r="K34" t="n">
-        <v>48.44</v>
+        <v>51.64</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>179.39</v>
+        <v>182.59</v>
       </c>
     </row>
   </sheetData>
@@ -54428,12 +54428,12 @@
         <v>16.42</v>
       </c>
       <c r="K34" t="n">
-        <v>21.9</v>
+        <v>25.58</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>188.92</v>
+        <v>192.6</v>
       </c>
     </row>
   </sheetData>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -28302,10 +28302,10 @@
         <v>10</v>
       </c>
       <c r="D1269" t="n">
-        <v>98.37</v>
+        <v>99.06</v>
       </c>
       <c r="E1269" t="n">
-        <v>152.06</v>
+        <v>152.58</v>
       </c>
       <c r="F1269" t="n">
         <v>268.68</v>
@@ -42237,12 +42237,12 @@
         <v>129.81</v>
       </c>
       <c r="K23" t="n">
-        <v>98.37</v>
+        <v>99.06</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>340.19</v>
+        <v>340.88</v>
       </c>
     </row>
   </sheetData>
@@ -43271,12 +43271,12 @@
         <v>14.19</v>
       </c>
       <c r="K23" t="n">
-        <v>152.06</v>
+        <v>152.58</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>315.49</v>
+        <v>316.01</v>
       </c>
     </row>
   </sheetData>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -8330,10 +8330,10 @@
         <v>10</v>
       </c>
       <c r="D359" t="n">
-        <v>46.114</v>
+        <v>48.484</v>
       </c>
       <c r="E359" t="n">
-        <v>52.122</v>
+        <v>54.492</v>
       </c>
       <c r="F359" t="n">
         <v>78.58199999999999</v>
@@ -13902,13 +13902,13 @@
         <v>10</v>
       </c>
       <c r="D613" t="n">
-        <v>10.506</v>
+        <v>12.947</v>
       </c>
       <c r="E613" t="n">
-        <v>18.174</v>
+        <v>18.726</v>
       </c>
       <c r="F613" t="n">
-        <v>39.479</v>
+        <v>41.367</v>
       </c>
     </row>
     <row r="614">
@@ -22570,13 +22570,13 @@
         <v>10</v>
       </c>
       <c r="D1007" t="n">
-        <v>51.64</v>
+        <v>54.12</v>
       </c>
       <c r="E1007" t="n">
-        <v>25.58</v>
+        <v>29.26</v>
       </c>
       <c r="F1007" t="n">
-        <v>184.04</v>
+        <v>182.85</v>
       </c>
     </row>
     <row r="1008">
@@ -36114,13 +36114,13 @@
         <v>10</v>
       </c>
       <c r="D1663" t="n">
-        <v>108.26</v>
+        <v>115.551</v>
       </c>
       <c r="E1663" t="n">
-        <v>95.876</v>
+        <v>102.478</v>
       </c>
       <c r="F1663" t="n">
-        <v>302.101</v>
+        <v>302.799</v>
       </c>
     </row>
   </sheetData>
@@ -37548,7 +37548,7 @@
         <v>148.64</v>
       </c>
       <c r="K34" t="n">
-        <v>184.04</v>
+        <v>182.85</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
@@ -38791,12 +38791,12 @@
         <v>140.368</v>
       </c>
       <c r="K34" t="n">
-        <v>108.26</v>
+        <v>115.551</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>431.665</v>
+        <v>438.956</v>
       </c>
     </row>
   </sheetData>
@@ -40045,12 +40045,12 @@
         <v>42.813</v>
       </c>
       <c r="K34" t="n">
-        <v>95.876</v>
+        <v>102.478</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>453.954</v>
+        <v>460.556</v>
       </c>
     </row>
   </sheetData>
@@ -41190,7 +41190,7 @@
         <v>285.545</v>
       </c>
       <c r="K34" t="n">
-        <v>302.101</v>
+        <v>302.799</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
@@ -45636,12 +45636,12 @@
         <v>37.966</v>
       </c>
       <c r="K31" t="n">
-        <v>46.114</v>
+        <v>48.484</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>127.208</v>
+        <v>129.578</v>
       </c>
     </row>
   </sheetData>
@@ -47038,12 +47038,12 @@
         <v>10.832</v>
       </c>
       <c r="K31" t="n">
-        <v>52.122</v>
+        <v>54.492</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>122.052</v>
+        <v>124.422</v>
       </c>
     </row>
   </sheetData>
@@ -49371,12 +49371,12 @@
         <v>34.902</v>
       </c>
       <c r="K23" t="n">
-        <v>10.506</v>
+        <v>12.947</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>121.867</v>
+        <v>124.308</v>
       </c>
     </row>
   </sheetData>
@@ -50405,12 +50405,12 @@
         <v>15.561</v>
       </c>
       <c r="K23" t="n">
-        <v>18.174</v>
+        <v>18.726</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>139.302</v>
+        <v>139.854</v>
       </c>
     </row>
   </sheetData>
@@ -51363,7 +51363,7 @@
         <v>51.397</v>
       </c>
       <c r="K23" t="n">
-        <v>39.479</v>
+        <v>41.367</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
@@ -52894,12 +52894,12 @@
         <v>67.5</v>
       </c>
       <c r="K34" t="n">
-        <v>51.64</v>
+        <v>54.12</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>182.59</v>
+        <v>185.07</v>
       </c>
     </row>
   </sheetData>
@@ -54428,12 +54428,12 @@
         <v>16.42</v>
       </c>
       <c r="K34" t="n">
-        <v>25.58</v>
+        <v>29.26</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>192.6</v>
+        <v>196.28</v>
       </c>
     </row>
   </sheetData>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -28302,13 +28302,13 @@
         <v>10</v>
       </c>
       <c r="D1269" t="n">
-        <v>99.06</v>
+        <v>99.23</v>
       </c>
       <c r="E1269" t="n">
-        <v>152.58</v>
+        <v>153.02</v>
       </c>
       <c r="F1269" t="n">
-        <v>268.68</v>
+        <v>268.24</v>
       </c>
     </row>
     <row r="1270">
@@ -42237,12 +42237,12 @@
         <v>129.81</v>
       </c>
       <c r="K23" t="n">
-        <v>99.06</v>
+        <v>99.23</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>340.88</v>
+        <v>341.05</v>
       </c>
     </row>
   </sheetData>
@@ -43271,12 +43271,12 @@
         <v>14.19</v>
       </c>
       <c r="K23" t="n">
-        <v>152.58</v>
+        <v>153.02</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>316.01</v>
+        <v>316.45</v>
       </c>
     </row>
   </sheetData>
@@ -44237,7 +44237,7 @@
         <v>325.6</v>
       </c>
       <c r="K23" t="n">
-        <v>268.68</v>
+        <v>268.24</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -8330,10 +8330,10 @@
         <v>10</v>
       </c>
       <c r="D359" t="n">
-        <v>48.484</v>
+        <v>50.854</v>
       </c>
       <c r="E359" t="n">
-        <v>54.492</v>
+        <v>56.862</v>
       </c>
       <c r="F359" t="n">
         <v>78.58199999999999</v>
@@ -13902,10 +13902,10 @@
         <v>10</v>
       </c>
       <c r="D613" t="n">
-        <v>12.947</v>
+        <v>13.499</v>
       </c>
       <c r="E613" t="n">
-        <v>18.726</v>
+        <v>19.278</v>
       </c>
       <c r="F613" t="n">
         <v>41.367</v>
@@ -22570,13 +22570,13 @@
         <v>10</v>
       </c>
       <c r="D1007" t="n">
-        <v>54.12</v>
+        <v>55.37</v>
       </c>
       <c r="E1007" t="n">
-        <v>29.26</v>
+        <v>32.65</v>
       </c>
       <c r="F1007" t="n">
-        <v>182.85</v>
+        <v>180.7</v>
       </c>
     </row>
     <row r="1008">
@@ -36114,13 +36114,13 @@
         <v>10</v>
       </c>
       <c r="D1663" t="n">
-        <v>115.551</v>
+        <v>119.723</v>
       </c>
       <c r="E1663" t="n">
-        <v>102.478</v>
+        <v>108.79</v>
       </c>
       <c r="F1663" t="n">
-        <v>302.799</v>
+        <v>300.649</v>
       </c>
     </row>
   </sheetData>
@@ -37548,7 +37548,7 @@
         <v>148.64</v>
       </c>
       <c r="K34" t="n">
-        <v>182.85</v>
+        <v>180.7</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
@@ -38791,12 +38791,12 @@
         <v>140.368</v>
       </c>
       <c r="K34" t="n">
-        <v>115.551</v>
+        <v>119.723</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>438.956</v>
+        <v>443.128</v>
       </c>
     </row>
   </sheetData>
@@ -40045,12 +40045,12 @@
         <v>42.813</v>
       </c>
       <c r="K34" t="n">
-        <v>102.478</v>
+        <v>108.79</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>460.556</v>
+        <v>466.868</v>
       </c>
     </row>
   </sheetData>
@@ -41190,7 +41190,7 @@
         <v>285.545</v>
       </c>
       <c r="K34" t="n">
-        <v>302.799</v>
+        <v>300.649</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
@@ -45636,12 +45636,12 @@
         <v>37.966</v>
       </c>
       <c r="K31" t="n">
-        <v>48.484</v>
+        <v>50.854</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>129.578</v>
+        <v>131.948</v>
       </c>
     </row>
   </sheetData>
@@ -47038,12 +47038,12 @@
         <v>10.832</v>
       </c>
       <c r="K31" t="n">
-        <v>54.492</v>
+        <v>56.862</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>124.422</v>
+        <v>126.792</v>
       </c>
     </row>
   </sheetData>
@@ -49371,12 +49371,12 @@
         <v>34.902</v>
       </c>
       <c r="K23" t="n">
-        <v>12.947</v>
+        <v>13.499</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>124.308</v>
+        <v>124.86</v>
       </c>
     </row>
   </sheetData>
@@ -50405,12 +50405,12 @@
         <v>15.561</v>
       </c>
       <c r="K23" t="n">
-        <v>18.726</v>
+        <v>19.278</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>139.854</v>
+        <v>140.406</v>
       </c>
     </row>
   </sheetData>
@@ -52894,12 +52894,12 @@
         <v>67.5</v>
       </c>
       <c r="K34" t="n">
-        <v>54.12</v>
+        <v>55.37</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>185.07</v>
+        <v>186.32</v>
       </c>
     </row>
   </sheetData>
@@ -54428,12 +54428,12 @@
         <v>16.42</v>
       </c>
       <c r="K34" t="n">
-        <v>29.26</v>
+        <v>32.65</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>196.28</v>
+        <v>199.67</v>
       </c>
     </row>
   </sheetData>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -28302,10 +28302,10 @@
         <v>10</v>
       </c>
       <c r="D1269" t="n">
-        <v>99.23</v>
+        <v>99.84</v>
       </c>
       <c r="E1269" t="n">
-        <v>153.02</v>
+        <v>153.46</v>
       </c>
       <c r="F1269" t="n">
         <v>268.24</v>
@@ -42237,12 +42237,12 @@
         <v>129.81</v>
       </c>
       <c r="K23" t="n">
-        <v>99.23</v>
+        <v>99.84</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>341.05</v>
+        <v>341.66</v>
       </c>
     </row>
   </sheetData>
@@ -43271,12 +43271,12 @@
         <v>14.19</v>
       </c>
       <c r="K23" t="n">
-        <v>153.02</v>
+        <v>153.46</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>316.45</v>
+        <v>316.89</v>
       </c>
     </row>
   </sheetData>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -8330,10 +8330,10 @@
         <v>10</v>
       </c>
       <c r="D359" t="n">
-        <v>50.854</v>
+        <v>53.224</v>
       </c>
       <c r="E359" t="n">
-        <v>56.862</v>
+        <v>59.232</v>
       </c>
       <c r="F359" t="n">
         <v>78.58199999999999</v>
@@ -13902,10 +13902,10 @@
         <v>10</v>
       </c>
       <c r="D613" t="n">
-        <v>13.499</v>
+        <v>14.051</v>
       </c>
       <c r="E613" t="n">
-        <v>19.278</v>
+        <v>19.83</v>
       </c>
       <c r="F613" t="n">
         <v>41.367</v>
@@ -22570,13 +22570,13 @@
         <v>10</v>
       </c>
       <c r="D1007" t="n">
-        <v>55.37</v>
+        <v>57.88</v>
       </c>
       <c r="E1007" t="n">
-        <v>32.65</v>
+        <v>36.35</v>
       </c>
       <c r="F1007" t="n">
-        <v>180.7</v>
+        <v>179.51</v>
       </c>
     </row>
     <row r="1008">
@@ -36114,13 +36114,13 @@
         <v>10</v>
       </c>
       <c r="D1663" t="n">
-        <v>119.723</v>
+        <v>125.155</v>
       </c>
       <c r="E1663" t="n">
-        <v>108.79</v>
+        <v>115.412</v>
       </c>
       <c r="F1663" t="n">
-        <v>300.649</v>
+        <v>299.459</v>
       </c>
     </row>
   </sheetData>
@@ -37548,7 +37548,7 @@
         <v>148.64</v>
       </c>
       <c r="K34" t="n">
-        <v>180.7</v>
+        <v>179.51</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
@@ -38791,12 +38791,12 @@
         <v>140.368</v>
       </c>
       <c r="K34" t="n">
-        <v>119.723</v>
+        <v>125.155</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>443.128</v>
+        <v>448.5599999999999</v>
       </c>
     </row>
   </sheetData>
@@ -40045,12 +40045,12 @@
         <v>42.813</v>
       </c>
       <c r="K34" t="n">
-        <v>108.79</v>
+        <v>115.412</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>466.868</v>
+        <v>473.49</v>
       </c>
     </row>
   </sheetData>
@@ -41190,7 +41190,7 @@
         <v>285.545</v>
       </c>
       <c r="K34" t="n">
-        <v>300.649</v>
+        <v>299.459</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
@@ -45636,12 +45636,12 @@
         <v>37.966</v>
       </c>
       <c r="K31" t="n">
-        <v>50.854</v>
+        <v>53.224</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>131.948</v>
+        <v>134.318</v>
       </c>
     </row>
   </sheetData>
@@ -47038,12 +47038,12 @@
         <v>10.832</v>
       </c>
       <c r="K31" t="n">
-        <v>56.862</v>
+        <v>59.232</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>126.792</v>
+        <v>129.162</v>
       </c>
     </row>
   </sheetData>
@@ -49371,12 +49371,12 @@
         <v>34.902</v>
       </c>
       <c r="K23" t="n">
-        <v>13.499</v>
+        <v>14.051</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>124.86</v>
+        <v>125.412</v>
       </c>
     </row>
   </sheetData>
@@ -50405,12 +50405,12 @@
         <v>15.561</v>
       </c>
       <c r="K23" t="n">
-        <v>19.278</v>
+        <v>19.83</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>140.406</v>
+        <v>140.958</v>
       </c>
     </row>
   </sheetData>
@@ -52894,12 +52894,12 @@
         <v>67.5</v>
       </c>
       <c r="K34" t="n">
-        <v>55.37</v>
+        <v>57.88</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>186.32</v>
+        <v>188.83</v>
       </c>
     </row>
   </sheetData>
@@ -54428,12 +54428,12 @@
         <v>16.42</v>
       </c>
       <c r="K34" t="n">
-        <v>32.65</v>
+        <v>36.35</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>199.67</v>
+        <v>203.37</v>
       </c>
     </row>
   </sheetData>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -28302,10 +28302,10 @@
         <v>10</v>
       </c>
       <c r="D1269" t="n">
-        <v>99.84</v>
+        <v>100.45</v>
       </c>
       <c r="E1269" t="n">
-        <v>153.46</v>
+        <v>153.9</v>
       </c>
       <c r="F1269" t="n">
         <v>268.24</v>
@@ -37920,7 +37920,7 @@
         <v>10.4827</v>
       </c>
       <c r="N14" t="n">
-        <v>486.624</v>
+        <v>486.6240000000001</v>
       </c>
     </row>
     <row r="15">
@@ -38536,7 +38536,7 @@
         <v>16.642</v>
       </c>
       <c r="N28" t="n">
-        <v>515.8931</v>
+        <v>515.8931000000001</v>
       </c>
     </row>
     <row r="29">
@@ -39526,7 +39526,7 @@
         <v>36.6663</v>
       </c>
       <c r="N22" t="n">
-        <v>453.6328</v>
+        <v>453.6327999999999</v>
       </c>
     </row>
     <row r="23">
@@ -39790,7 +39790,7 @@
         <v>9.945</v>
       </c>
       <c r="N28" t="n">
-        <v>73.14699999999999</v>
+        <v>73.14700000000002</v>
       </c>
     </row>
     <row r="29">
@@ -40010,7 +40010,7 @@
         <v>46.682</v>
       </c>
       <c r="N33" t="n">
-        <v>402.702</v>
+        <v>402.7019999999999</v>
       </c>
     </row>
     <row r="34">
@@ -41894,7 +41894,7 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>347.8199999999999</v>
+        <v>347.82</v>
       </c>
     </row>
     <row r="16">
@@ -42237,12 +42237,12 @@
         <v>129.81</v>
       </c>
       <c r="K23" t="n">
-        <v>99.84</v>
+        <v>100.45</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>341.66</v>
+        <v>342.27</v>
       </c>
     </row>
   </sheetData>
@@ -43236,7 +43236,7 @@
         <v>6.01</v>
       </c>
       <c r="N22" t="n">
-        <v>159.18</v>
+        <v>159.1799999999999</v>
       </c>
     </row>
     <row r="23">
@@ -43271,12 +43271,12 @@
         <v>14.19</v>
       </c>
       <c r="K23" t="n">
-        <v>153.46</v>
+        <v>153.9</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>316.89</v>
+        <v>317.33</v>
       </c>
     </row>
   </sheetData>
@@ -45117,7 +45117,7 @@
         <v>4.4987</v>
       </c>
       <c r="N19" t="n">
-        <v>94.0125</v>
+        <v>94.01249999999999</v>
       </c>
     </row>
     <row r="20">
@@ -46123,7 +46123,7 @@
         <v>8.3177</v>
       </c>
       <c r="N10" t="n">
-        <v>82.13340000000001</v>
+        <v>82.13339999999999</v>
       </c>
     </row>
     <row r="11">
@@ -46299,7 +46299,7 @@
         <v>21.8441</v>
       </c>
       <c r="N14" t="n">
-        <v>292.2930000000001</v>
+        <v>292.293</v>
       </c>
     </row>
     <row r="15">
@@ -47003,7 +47003,7 @@
         <v>4.815</v>
       </c>
       <c r="N30" t="n">
-        <v>73.253</v>
+        <v>73.25299999999999</v>
       </c>
     </row>
     <row r="31">
@@ -52111,7 +52111,7 @@
         <v>8.016999999999999</v>
       </c>
       <c r="N16" t="n">
-        <v>260.9814000000001</v>
+        <v>260.9814</v>
       </c>
     </row>
     <row r="17">
@@ -52727,7 +52727,7 @@
         <v>8.23</v>
       </c>
       <c r="N30" t="n">
-        <v>302.31</v>
+        <v>302.3100000000001</v>
       </c>
     </row>
     <row r="31">
@@ -53029,7 +53029,7 @@
         <v>10.2654</v>
       </c>
       <c r="N2" t="n">
-        <v>88.25079999999998</v>
+        <v>88.2508</v>
       </c>
     </row>
     <row r="3">

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -8330,10 +8330,10 @@
         <v>10</v>
       </c>
       <c r="D359" t="n">
-        <v>53.224</v>
+        <v>55.594</v>
       </c>
       <c r="E359" t="n">
-        <v>59.232</v>
+        <v>61.602</v>
       </c>
       <c r="F359" t="n">
         <v>78.58199999999999</v>
@@ -13902,10 +13902,10 @@
         <v>10</v>
       </c>
       <c r="D613" t="n">
-        <v>14.051</v>
+        <v>14.603</v>
       </c>
       <c r="E613" t="n">
-        <v>19.83</v>
+        <v>20.382</v>
       </c>
       <c r="F613" t="n">
         <v>41.367</v>
@@ -36114,10 +36114,10 @@
         <v>10</v>
       </c>
       <c r="D1663" t="n">
-        <v>125.155</v>
+        <v>128.077</v>
       </c>
       <c r="E1663" t="n">
-        <v>115.412</v>
+        <v>118.334</v>
       </c>
       <c r="F1663" t="n">
         <v>299.459</v>
@@ -38791,12 +38791,12 @@
         <v>140.368</v>
       </c>
       <c r="K34" t="n">
-        <v>125.155</v>
+        <v>128.077</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>448.5599999999999</v>
+        <v>451.482</v>
       </c>
     </row>
   </sheetData>
@@ -40045,12 +40045,12 @@
         <v>42.813</v>
       </c>
       <c r="K34" t="n">
-        <v>115.412</v>
+        <v>118.334</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>473.49</v>
+        <v>476.412</v>
       </c>
     </row>
   </sheetData>
@@ -45636,12 +45636,12 @@
         <v>37.966</v>
       </c>
       <c r="K31" t="n">
-        <v>53.224</v>
+        <v>55.594</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>134.318</v>
+        <v>136.688</v>
       </c>
     </row>
   </sheetData>
@@ -47038,12 +47038,12 @@
         <v>10.832</v>
       </c>
       <c r="K31" t="n">
-        <v>59.232</v>
+        <v>61.602</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>129.162</v>
+        <v>131.532</v>
       </c>
     </row>
   </sheetData>
@@ -49371,12 +49371,12 @@
         <v>34.902</v>
       </c>
       <c r="K23" t="n">
-        <v>14.051</v>
+        <v>14.603</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>125.412</v>
+        <v>125.964</v>
       </c>
     </row>
   </sheetData>
@@ -50405,12 +50405,12 @@
         <v>15.561</v>
       </c>
       <c r="K23" t="n">
-        <v>19.83</v>
+        <v>20.382</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>140.958</v>
+        <v>141.51</v>
       </c>
     </row>
   </sheetData>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -22570,13 +22570,13 @@
         <v>10</v>
       </c>
       <c r="D1007" t="n">
-        <v>57.88</v>
+        <v>60.18</v>
       </c>
       <c r="E1007" t="n">
-        <v>36.35</v>
+        <v>38.89</v>
       </c>
       <c r="F1007" t="n">
-        <v>179.51</v>
+        <v>179.27</v>
       </c>
     </row>
     <row r="1008">
@@ -36114,13 +36114,13 @@
         <v>10</v>
       </c>
       <c r="D1663" t="n">
-        <v>128.077</v>
+        <v>130.377</v>
       </c>
       <c r="E1663" t="n">
-        <v>118.334</v>
+        <v>120.874</v>
       </c>
       <c r="F1663" t="n">
-        <v>299.459</v>
+        <v>299.219</v>
       </c>
     </row>
   </sheetData>
@@ -37548,7 +37548,7 @@
         <v>148.64</v>
       </c>
       <c r="K34" t="n">
-        <v>179.51</v>
+        <v>179.27</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
@@ -38791,12 +38791,12 @@
         <v>140.368</v>
       </c>
       <c r="K34" t="n">
-        <v>128.077</v>
+        <v>130.377</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>451.482</v>
+        <v>453.782</v>
       </c>
     </row>
   </sheetData>
@@ -40045,12 +40045,12 @@
         <v>42.813</v>
       </c>
       <c r="K34" t="n">
-        <v>118.334</v>
+        <v>120.874</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>476.412</v>
+        <v>478.952</v>
       </c>
     </row>
   </sheetData>
@@ -41190,7 +41190,7 @@
         <v>285.545</v>
       </c>
       <c r="K34" t="n">
-        <v>299.459</v>
+        <v>299.219</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
@@ -52894,12 +52894,12 @@
         <v>67.5</v>
       </c>
       <c r="K34" t="n">
-        <v>57.88</v>
+        <v>60.18</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>188.83</v>
+        <v>191.13</v>
       </c>
     </row>
   </sheetData>
@@ -54428,12 +54428,12 @@
         <v>16.42</v>
       </c>
       <c r="K34" t="n">
-        <v>36.35</v>
+        <v>38.89</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>203.37</v>
+        <v>205.91</v>
       </c>
     </row>
   </sheetData>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -28302,13 +28302,13 @@
         <v>10</v>
       </c>
       <c r="D1269" t="n">
-        <v>100.45</v>
+        <v>100.62</v>
       </c>
       <c r="E1269" t="n">
-        <v>153.9</v>
+        <v>154.34</v>
       </c>
       <c r="F1269" t="n">
-        <v>268.24</v>
+        <v>267.8</v>
       </c>
     </row>
     <row r="1270">
@@ -42237,12 +42237,12 @@
         <v>129.81</v>
       </c>
       <c r="K23" t="n">
-        <v>100.45</v>
+        <v>100.62</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>342.27</v>
+        <v>342.4400000000001</v>
       </c>
     </row>
   </sheetData>
@@ -43271,12 +43271,12 @@
         <v>14.19</v>
       </c>
       <c r="K23" t="n">
-        <v>153.9</v>
+        <v>154.34</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>317.33</v>
+        <v>317.77</v>
       </c>
     </row>
   </sheetData>
@@ -44237,7 +44237,7 @@
         <v>325.6</v>
       </c>
       <c r="K23" t="n">
-        <v>268.24</v>
+        <v>267.8</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -8330,10 +8330,10 @@
         <v>10</v>
       </c>
       <c r="D359" t="n">
-        <v>55.594</v>
+        <v>57.964</v>
       </c>
       <c r="E359" t="n">
-        <v>61.602</v>
+        <v>63.972</v>
       </c>
       <c r="F359" t="n">
         <v>78.58199999999999</v>
@@ -13902,10 +13902,10 @@
         <v>10</v>
       </c>
       <c r="D613" t="n">
-        <v>14.603</v>
+        <v>15.155</v>
       </c>
       <c r="E613" t="n">
-        <v>20.382</v>
+        <v>20.934</v>
       </c>
       <c r="F613" t="n">
         <v>41.367</v>
@@ -22570,13 +22570,13 @@
         <v>10</v>
       </c>
       <c r="D1007" t="n">
-        <v>60.18</v>
+        <v>63.52</v>
       </c>
       <c r="E1007" t="n">
-        <v>38.89</v>
+        <v>41.03</v>
       </c>
       <c r="F1007" t="n">
-        <v>179.27</v>
+        <v>180.46</v>
       </c>
     </row>
     <row r="1008">
@@ -36114,13 +36114,13 @@
         <v>10</v>
       </c>
       <c r="D1663" t="n">
-        <v>130.377</v>
+        <v>136.639</v>
       </c>
       <c r="E1663" t="n">
-        <v>120.874</v>
+        <v>125.936</v>
       </c>
       <c r="F1663" t="n">
-        <v>299.219</v>
+        <v>300.409</v>
       </c>
     </row>
   </sheetData>
@@ -37548,7 +37548,7 @@
         <v>148.64</v>
       </c>
       <c r="K34" t="n">
-        <v>179.27</v>
+        <v>180.46</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
@@ -38791,12 +38791,12 @@
         <v>140.368</v>
       </c>
       <c r="K34" t="n">
-        <v>130.377</v>
+        <v>136.639</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>453.782</v>
+        <v>460.044</v>
       </c>
     </row>
   </sheetData>
@@ -40045,12 +40045,12 @@
         <v>42.813</v>
       </c>
       <c r="K34" t="n">
-        <v>120.874</v>
+        <v>125.936</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>478.952</v>
+        <v>484.014</v>
       </c>
     </row>
   </sheetData>
@@ -41190,7 +41190,7 @@
         <v>285.545</v>
       </c>
       <c r="K34" t="n">
-        <v>299.219</v>
+        <v>300.409</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
@@ -45636,12 +45636,12 @@
         <v>37.966</v>
       </c>
       <c r="K31" t="n">
-        <v>55.594</v>
+        <v>57.964</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>136.688</v>
+        <v>139.058</v>
       </c>
     </row>
   </sheetData>
@@ -47038,12 +47038,12 @@
         <v>10.832</v>
       </c>
       <c r="K31" t="n">
-        <v>61.602</v>
+        <v>63.972</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>131.532</v>
+        <v>133.902</v>
       </c>
     </row>
   </sheetData>
@@ -49371,12 +49371,12 @@
         <v>34.902</v>
       </c>
       <c r="K23" t="n">
-        <v>14.603</v>
+        <v>15.155</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>125.964</v>
+        <v>126.516</v>
       </c>
     </row>
   </sheetData>
@@ -50405,12 +50405,12 @@
         <v>15.561</v>
       </c>
       <c r="K23" t="n">
-        <v>20.382</v>
+        <v>20.934</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>141.51</v>
+        <v>142.062</v>
       </c>
     </row>
   </sheetData>
@@ -52894,12 +52894,12 @@
         <v>67.5</v>
       </c>
       <c r="K34" t="n">
-        <v>60.18</v>
+        <v>63.52</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>191.13</v>
+        <v>194.47</v>
       </c>
     </row>
   </sheetData>
@@ -54428,12 +54428,12 @@
         <v>16.42</v>
       </c>
       <c r="K34" t="n">
-        <v>38.89</v>
+        <v>41.03</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>205.91</v>
+        <v>208.05</v>
       </c>
     </row>
   </sheetData>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -28302,13 +28302,13 @@
         <v>10</v>
       </c>
       <c r="D1269" t="n">
-        <v>100.62</v>
+        <v>100.79</v>
       </c>
       <c r="E1269" t="n">
-        <v>154.34</v>
+        <v>154.78</v>
       </c>
       <c r="F1269" t="n">
-        <v>267.8</v>
+        <v>267.36</v>
       </c>
     </row>
     <row r="1270">
@@ -42237,12 +42237,12 @@
         <v>129.81</v>
       </c>
       <c r="K23" t="n">
-        <v>100.62</v>
+        <v>100.79</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>342.4400000000001</v>
+        <v>342.61</v>
       </c>
     </row>
   </sheetData>
@@ -43271,12 +43271,12 @@
         <v>14.19</v>
       </c>
       <c r="K23" t="n">
-        <v>154.34</v>
+        <v>154.78</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>317.77</v>
+        <v>318.21</v>
       </c>
     </row>
   </sheetData>
@@ -44237,7 +44237,7 @@
         <v>325.6</v>
       </c>
       <c r="K23" t="n">
-        <v>267.8</v>
+        <v>267.36</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -22570,13 +22570,13 @@
         <v>10</v>
       </c>
       <c r="D1007" t="n">
-        <v>63.52</v>
+        <v>66.03</v>
       </c>
       <c r="E1007" t="n">
-        <v>41.03</v>
+        <v>42.82</v>
       </c>
       <c r="F1007" t="n">
-        <v>180.46</v>
+        <v>181.18</v>
       </c>
     </row>
     <row r="1008">
@@ -36114,13 +36114,13 @@
         <v>10</v>
       </c>
       <c r="D1663" t="n">
-        <v>136.639</v>
+        <v>139.149</v>
       </c>
       <c r="E1663" t="n">
-        <v>125.936</v>
+        <v>127.726</v>
       </c>
       <c r="F1663" t="n">
-        <v>300.409</v>
+        <v>301.129</v>
       </c>
     </row>
   </sheetData>
@@ -37548,7 +37548,7 @@
         <v>148.64</v>
       </c>
       <c r="K34" t="n">
-        <v>180.46</v>
+        <v>181.18</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
@@ -38791,12 +38791,12 @@
         <v>140.368</v>
       </c>
       <c r="K34" t="n">
-        <v>136.639</v>
+        <v>139.149</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>460.044</v>
+        <v>462.554</v>
       </c>
     </row>
   </sheetData>
@@ -40045,12 +40045,12 @@
         <v>42.813</v>
       </c>
       <c r="K34" t="n">
-        <v>125.936</v>
+        <v>127.726</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>484.014</v>
+        <v>485.804</v>
       </c>
     </row>
   </sheetData>
@@ -41190,7 +41190,7 @@
         <v>285.545</v>
       </c>
       <c r="K34" t="n">
-        <v>300.409</v>
+        <v>301.129</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
@@ -52894,12 +52894,12 @@
         <v>67.5</v>
       </c>
       <c r="K34" t="n">
-        <v>63.52</v>
+        <v>66.03</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>194.47</v>
+        <v>196.98</v>
       </c>
     </row>
   </sheetData>
@@ -54428,12 +54428,12 @@
         <v>16.42</v>
       </c>
       <c r="K34" t="n">
-        <v>41.03</v>
+        <v>42.82</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>208.05</v>
+        <v>209.84</v>
       </c>
     </row>
   </sheetData>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -8330,10 +8330,10 @@
         <v>10</v>
       </c>
       <c r="D359" t="n">
-        <v>57.964</v>
+        <v>60.334</v>
       </c>
       <c r="E359" t="n">
-        <v>63.972</v>
+        <v>66.342</v>
       </c>
       <c r="F359" t="n">
         <v>78.58199999999999</v>
@@ -13902,10 +13902,10 @@
         <v>10</v>
       </c>
       <c r="D613" t="n">
-        <v>15.155</v>
+        <v>15.707</v>
       </c>
       <c r="E613" t="n">
-        <v>20.934</v>
+        <v>21.486</v>
       </c>
       <c r="F613" t="n">
         <v>41.367</v>
@@ -36114,10 +36114,10 @@
         <v>10</v>
       </c>
       <c r="D1663" t="n">
-        <v>139.149</v>
+        <v>142.071</v>
       </c>
       <c r="E1663" t="n">
-        <v>127.726</v>
+        <v>130.648</v>
       </c>
       <c r="F1663" t="n">
         <v>301.129</v>
@@ -38791,12 +38791,12 @@
         <v>140.368</v>
       </c>
       <c r="K34" t="n">
-        <v>139.149</v>
+        <v>142.071</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>462.554</v>
+        <v>465.476</v>
       </c>
     </row>
   </sheetData>
@@ -40045,12 +40045,12 @@
         <v>42.813</v>
       </c>
       <c r="K34" t="n">
-        <v>127.726</v>
+        <v>130.648</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>485.804</v>
+        <v>488.726</v>
       </c>
     </row>
   </sheetData>
@@ -45636,12 +45636,12 @@
         <v>37.966</v>
       </c>
       <c r="K31" t="n">
-        <v>57.964</v>
+        <v>60.334</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>139.058</v>
+        <v>141.428</v>
       </c>
     </row>
   </sheetData>
@@ -47038,12 +47038,12 @@
         <v>10.832</v>
       </c>
       <c r="K31" t="n">
-        <v>63.972</v>
+        <v>66.342</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>133.902</v>
+        <v>136.272</v>
       </c>
     </row>
   </sheetData>
@@ -49371,12 +49371,12 @@
         <v>34.902</v>
       </c>
       <c r="K23" t="n">
-        <v>15.155</v>
+        <v>15.707</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>126.516</v>
+        <v>127.068</v>
       </c>
     </row>
   </sheetData>
@@ -50405,12 +50405,12 @@
         <v>15.561</v>
       </c>
       <c r="K23" t="n">
-        <v>20.934</v>
+        <v>21.486</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>142.062</v>
+        <v>142.614</v>
       </c>
     </row>
   </sheetData>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -28302,10 +28302,10 @@
         <v>10</v>
       </c>
       <c r="D1269" t="n">
-        <v>100.79</v>
+        <v>101.4</v>
       </c>
       <c r="E1269" t="n">
-        <v>154.78</v>
+        <v>155.22</v>
       </c>
       <c r="F1269" t="n">
         <v>267.36</v>
@@ -42237,12 +42237,12 @@
         <v>129.81</v>
       </c>
       <c r="K23" t="n">
-        <v>100.79</v>
+        <v>101.4</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>342.61</v>
+        <v>343.22</v>
       </c>
     </row>
   </sheetData>
@@ -43271,12 +43271,12 @@
         <v>14.19</v>
       </c>
       <c r="K23" t="n">
-        <v>154.78</v>
+        <v>155.22</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>318.21</v>
+        <v>318.65</v>
       </c>
     </row>
   </sheetData>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -8330,10 +8330,10 @@
         <v>10</v>
       </c>
       <c r="D359" t="n">
-        <v>60.334</v>
+        <v>62.704</v>
       </c>
       <c r="E359" t="n">
-        <v>66.342</v>
+        <v>68.712</v>
       </c>
       <c r="F359" t="n">
         <v>78.58199999999999</v>
@@ -13902,10 +13902,10 @@
         <v>10</v>
       </c>
       <c r="D613" t="n">
-        <v>15.707</v>
+        <v>16.259</v>
       </c>
       <c r="E613" t="n">
-        <v>21.486</v>
+        <v>22.038</v>
       </c>
       <c r="F613" t="n">
         <v>41.367</v>
@@ -22570,13 +22570,13 @@
         <v>10</v>
       </c>
       <c r="D1007" t="n">
-        <v>66.03</v>
+        <v>67.56</v>
       </c>
       <c r="E1007" t="n">
-        <v>42.82</v>
+        <v>45.54</v>
       </c>
       <c r="F1007" t="n">
-        <v>181.18</v>
+        <v>179.98</v>
       </c>
     </row>
     <row r="1008">
@@ -36114,13 +36114,13 @@
         <v>10</v>
       </c>
       <c r="D1663" t="n">
-        <v>142.071</v>
+        <v>146.523</v>
       </c>
       <c r="E1663" t="n">
-        <v>130.648</v>
+        <v>136.29</v>
       </c>
       <c r="F1663" t="n">
-        <v>301.129</v>
+        <v>299.929</v>
       </c>
     </row>
   </sheetData>
@@ -37548,7 +37548,7 @@
         <v>148.64</v>
       </c>
       <c r="K34" t="n">
-        <v>181.18</v>
+        <v>179.98</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
@@ -38791,12 +38791,12 @@
         <v>140.368</v>
       </c>
       <c r="K34" t="n">
-        <v>142.071</v>
+        <v>146.523</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>465.476</v>
+        <v>469.928</v>
       </c>
     </row>
   </sheetData>
@@ -40045,12 +40045,12 @@
         <v>42.813</v>
       </c>
       <c r="K34" t="n">
-        <v>130.648</v>
+        <v>136.29</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>488.726</v>
+        <v>494.3679999999999</v>
       </c>
     </row>
   </sheetData>
@@ -41190,7 +41190,7 @@
         <v>285.545</v>
       </c>
       <c r="K34" t="n">
-        <v>301.129</v>
+        <v>299.929</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
@@ -45636,12 +45636,12 @@
         <v>37.966</v>
       </c>
       <c r="K31" t="n">
-        <v>60.334</v>
+        <v>62.704</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>141.428</v>
+        <v>143.798</v>
       </c>
     </row>
   </sheetData>
@@ -47038,12 +47038,12 @@
         <v>10.832</v>
       </c>
       <c r="K31" t="n">
-        <v>66.342</v>
+        <v>68.712</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>136.272</v>
+        <v>138.642</v>
       </c>
     </row>
   </sheetData>
@@ -49371,12 +49371,12 @@
         <v>34.902</v>
       </c>
       <c r="K23" t="n">
-        <v>15.707</v>
+        <v>16.259</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>127.068</v>
+        <v>127.62</v>
       </c>
     </row>
   </sheetData>
@@ -50405,12 +50405,12 @@
         <v>15.561</v>
       </c>
       <c r="K23" t="n">
-        <v>21.486</v>
+        <v>22.038</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>142.614</v>
+        <v>143.166</v>
       </c>
     </row>
   </sheetData>
@@ -52894,12 +52894,12 @@
         <v>67.5</v>
       </c>
       <c r="K34" t="n">
-        <v>66.03</v>
+        <v>67.56</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>196.98</v>
+        <v>198.51</v>
       </c>
     </row>
   </sheetData>
@@ -54428,12 +54428,12 @@
         <v>16.42</v>
       </c>
       <c r="K34" t="n">
-        <v>42.82</v>
+        <v>45.54</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>209.84</v>
+        <v>212.56</v>
       </c>
     </row>
   </sheetData>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -28302,13 +28302,13 @@
         <v>10</v>
       </c>
       <c r="D1269" t="n">
-        <v>101.4</v>
+        <v>102.89</v>
       </c>
       <c r="E1269" t="n">
-        <v>155.22</v>
+        <v>155.66</v>
       </c>
       <c r="F1269" t="n">
-        <v>267.36</v>
+        <v>268.24</v>
       </c>
     </row>
     <row r="1270">
@@ -42237,12 +42237,12 @@
         <v>129.81</v>
       </c>
       <c r="K23" t="n">
-        <v>101.4</v>
+        <v>102.89</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>343.22</v>
+        <v>344.71</v>
       </c>
     </row>
   </sheetData>
@@ -43271,12 +43271,12 @@
         <v>14.19</v>
       </c>
       <c r="K23" t="n">
-        <v>155.22</v>
+        <v>155.66</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>318.65</v>
+        <v>319.09</v>
       </c>
     </row>
   </sheetData>
@@ -44237,7 +44237,7 @@
         <v>325.6</v>
       </c>
       <c r="K23" t="n">
-        <v>267.36</v>
+        <v>268.24</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -8330,10 +8330,10 @@
         <v>10</v>
       </c>
       <c r="D359" t="n">
-        <v>62.704</v>
+        <v>65.074</v>
       </c>
       <c r="E359" t="n">
-        <v>68.712</v>
+        <v>71.08199999999999</v>
       </c>
       <c r="F359" t="n">
         <v>78.58199999999999</v>
@@ -13902,10 +13902,10 @@
         <v>10</v>
       </c>
       <c r="D613" t="n">
-        <v>16.259</v>
+        <v>16.811</v>
       </c>
       <c r="E613" t="n">
-        <v>22.038</v>
+        <v>22.59</v>
       </c>
       <c r="F613" t="n">
         <v>41.367</v>
@@ -22570,13 +22570,13 @@
         <v>10</v>
       </c>
       <c r="D1007" t="n">
-        <v>67.56</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="E1007" t="n">
-        <v>45.54</v>
+        <v>48.12</v>
       </c>
       <c r="F1007" t="n">
-        <v>179.98</v>
+        <v>179.74</v>
       </c>
     </row>
     <row r="1008">
@@ -36114,13 +36114,13 @@
         <v>10</v>
       </c>
       <c r="D1663" t="n">
-        <v>146.523</v>
+        <v>151.785</v>
       </c>
       <c r="E1663" t="n">
-        <v>136.29</v>
+        <v>141.792</v>
       </c>
       <c r="F1663" t="n">
-        <v>299.929</v>
+        <v>299.689</v>
       </c>
     </row>
   </sheetData>
@@ -37548,7 +37548,7 @@
         <v>148.64</v>
       </c>
       <c r="K34" t="n">
-        <v>179.98</v>
+        <v>179.74</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
@@ -38791,12 +38791,12 @@
         <v>140.368</v>
       </c>
       <c r="K34" t="n">
-        <v>146.523</v>
+        <v>151.785</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>469.928</v>
+        <v>475.1899999999999</v>
       </c>
     </row>
   </sheetData>
@@ -40045,12 +40045,12 @@
         <v>42.813</v>
       </c>
       <c r="K34" t="n">
-        <v>136.29</v>
+        <v>141.792</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>494.3679999999999</v>
+        <v>499.87</v>
       </c>
     </row>
   </sheetData>
@@ -41190,7 +41190,7 @@
         <v>285.545</v>
       </c>
       <c r="K34" t="n">
-        <v>299.929</v>
+        <v>299.689</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
@@ -45636,12 +45636,12 @@
         <v>37.966</v>
       </c>
       <c r="K31" t="n">
-        <v>62.704</v>
+        <v>65.074</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>143.798</v>
+        <v>146.168</v>
       </c>
     </row>
   </sheetData>
@@ -47038,12 +47038,12 @@
         <v>10.832</v>
       </c>
       <c r="K31" t="n">
-        <v>68.712</v>
+        <v>71.08199999999999</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>138.642</v>
+        <v>141.012</v>
       </c>
     </row>
   </sheetData>
@@ -49371,12 +49371,12 @@
         <v>34.902</v>
       </c>
       <c r="K23" t="n">
-        <v>16.259</v>
+        <v>16.811</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>127.62</v>
+        <v>128.172</v>
       </c>
     </row>
   </sheetData>
@@ -50405,12 +50405,12 @@
         <v>15.561</v>
       </c>
       <c r="K23" t="n">
-        <v>22.038</v>
+        <v>22.59</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>143.166</v>
+        <v>143.718</v>
       </c>
     </row>
   </sheetData>
@@ -52894,12 +52894,12 @@
         <v>67.5</v>
       </c>
       <c r="K34" t="n">
-        <v>67.56</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>198.51</v>
+        <v>200.85</v>
       </c>
     </row>
   </sheetData>
@@ -54428,12 +54428,12 @@
         <v>16.42</v>
       </c>
       <c r="K34" t="n">
-        <v>45.54</v>
+        <v>48.12</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>212.56</v>
+        <v>215.14</v>
       </c>
     </row>
   </sheetData>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -28302,13 +28302,13 @@
         <v>10</v>
       </c>
       <c r="D1269" t="n">
-        <v>102.89</v>
+        <v>103.06</v>
       </c>
       <c r="E1269" t="n">
-        <v>155.66</v>
+        <v>156.1</v>
       </c>
       <c r="F1269" t="n">
-        <v>268.24</v>
+        <v>267.8</v>
       </c>
     </row>
     <row r="1270">
@@ -42237,12 +42237,12 @@
         <v>129.81</v>
       </c>
       <c r="K23" t="n">
-        <v>102.89</v>
+        <v>103.06</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>344.71</v>
+        <v>344.88</v>
       </c>
     </row>
   </sheetData>
@@ -43271,12 +43271,12 @@
         <v>14.19</v>
       </c>
       <c r="K23" t="n">
-        <v>155.66</v>
+        <v>156.1</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>319.09</v>
+        <v>319.53</v>
       </c>
     </row>
   </sheetData>
@@ -44237,7 +44237,7 @@
         <v>325.6</v>
       </c>
       <c r="K23" t="n">
-        <v>268.24</v>
+        <v>267.8</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -8330,13 +8330,13 @@
         <v>10</v>
       </c>
       <c r="D359" t="n">
-        <v>65.074</v>
+        <v>66.04600000000001</v>
       </c>
       <c r="E359" t="n">
-        <v>71.08199999999999</v>
+        <v>73.438</v>
       </c>
       <c r="F359" t="n">
-        <v>78.58199999999999</v>
+        <v>75.443</v>
       </c>
     </row>
     <row r="360">
@@ -13902,13 +13902,13 @@
         <v>10</v>
       </c>
       <c r="D613" t="n">
-        <v>16.811</v>
+        <v>17.069</v>
       </c>
       <c r="E613" t="n">
-        <v>22.59</v>
+        <v>22.638</v>
       </c>
       <c r="F613" t="n">
-        <v>41.367</v>
+        <v>40.626</v>
       </c>
     </row>
     <row r="614">
@@ -22570,13 +22570,13 @@
         <v>10</v>
       </c>
       <c r="D1007" t="n">
-        <v>69.90000000000001</v>
+        <v>71.62</v>
       </c>
       <c r="E1007" t="n">
-        <v>48.12</v>
+        <v>50.56</v>
       </c>
       <c r="F1007" t="n">
-        <v>179.74</v>
+        <v>179.03</v>
       </c>
     </row>
     <row r="1008">
@@ -36114,13 +36114,13 @@
         <v>10</v>
       </c>
       <c r="D1663" t="n">
-        <v>151.785</v>
+        <v>154.735</v>
       </c>
       <c r="E1663" t="n">
-        <v>141.792</v>
+        <v>146.636</v>
       </c>
       <c r="F1663" t="n">
-        <v>299.689</v>
+        <v>295.099</v>
       </c>
     </row>
   </sheetData>
@@ -37548,7 +37548,7 @@
         <v>148.64</v>
       </c>
       <c r="K34" t="n">
-        <v>179.74</v>
+        <v>179.03</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
@@ -38791,12 +38791,12 @@
         <v>140.368</v>
       </c>
       <c r="K34" t="n">
-        <v>151.785</v>
+        <v>154.735</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>475.1899999999999</v>
+        <v>478.14</v>
       </c>
     </row>
   </sheetData>
@@ -40045,12 +40045,12 @@
         <v>42.813</v>
       </c>
       <c r="K34" t="n">
-        <v>141.792</v>
+        <v>146.636</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>499.87</v>
+        <v>504.7139999999999</v>
       </c>
     </row>
   </sheetData>
@@ -41190,7 +41190,7 @@
         <v>285.545</v>
       </c>
       <c r="K34" t="n">
-        <v>299.689</v>
+        <v>295.099</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
@@ -45636,12 +45636,12 @@
         <v>37.966</v>
       </c>
       <c r="K31" t="n">
-        <v>65.074</v>
+        <v>66.04600000000001</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>146.168</v>
+        <v>147.14</v>
       </c>
     </row>
   </sheetData>
@@ -47038,12 +47038,12 @@
         <v>10.832</v>
       </c>
       <c r="K31" t="n">
-        <v>71.08199999999999</v>
+        <v>73.438</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>141.012</v>
+        <v>143.368</v>
       </c>
     </row>
   </sheetData>
@@ -48348,7 +48348,7 @@
         <v>85.508</v>
       </c>
       <c r="K31" t="n">
-        <v>78.58199999999999</v>
+        <v>75.443</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
@@ -49371,12 +49371,12 @@
         <v>34.902</v>
       </c>
       <c r="K23" t="n">
-        <v>16.811</v>
+        <v>17.069</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>128.172</v>
+        <v>128.43</v>
       </c>
     </row>
   </sheetData>
@@ -50405,12 +50405,12 @@
         <v>15.561</v>
       </c>
       <c r="K23" t="n">
-        <v>22.59</v>
+        <v>22.638</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>143.718</v>
+        <v>143.766</v>
       </c>
     </row>
   </sheetData>
@@ -51363,7 +51363,7 @@
         <v>51.397</v>
       </c>
       <c r="K23" t="n">
-        <v>41.367</v>
+        <v>40.626</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
@@ -52894,12 +52894,12 @@
         <v>67.5</v>
       </c>
       <c r="K34" t="n">
-        <v>69.90000000000001</v>
+        <v>71.62</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>200.85</v>
+        <v>202.57</v>
       </c>
     </row>
   </sheetData>
@@ -54428,12 +54428,12 @@
         <v>16.42</v>
       </c>
       <c r="K34" t="n">
-        <v>48.12</v>
+        <v>50.56</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>215.14</v>
+        <v>217.58</v>
       </c>
     </row>
   </sheetData>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -28302,13 +28302,13 @@
         <v>10</v>
       </c>
       <c r="D1269" t="n">
-        <v>103.06</v>
+        <v>103.23</v>
       </c>
       <c r="E1269" t="n">
-        <v>156.1</v>
+        <v>156.54</v>
       </c>
       <c r="F1269" t="n">
-        <v>267.8</v>
+        <v>267.36</v>
       </c>
     </row>
     <row r="1270">
@@ -42237,12 +42237,12 @@
         <v>129.81</v>
       </c>
       <c r="K23" t="n">
-        <v>103.06</v>
+        <v>103.23</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>344.88</v>
+        <v>345.05</v>
       </c>
     </row>
   </sheetData>
@@ -43271,12 +43271,12 @@
         <v>14.19</v>
       </c>
       <c r="K23" t="n">
-        <v>156.1</v>
+        <v>156.54</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>319.53</v>
+        <v>319.97</v>
       </c>
     </row>
   </sheetData>
@@ -44237,7 +44237,7 @@
         <v>325.6</v>
       </c>
       <c r="K23" t="n">
-        <v>267.8</v>
+        <v>267.36</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -8330,10 +8330,10 @@
         <v>10</v>
       </c>
       <c r="D359" t="n">
-        <v>66.04600000000001</v>
+        <v>67.018</v>
       </c>
       <c r="E359" t="n">
-        <v>73.438</v>
+        <v>74.41</v>
       </c>
       <c r="F359" t="n">
         <v>75.443</v>
@@ -13902,10 +13902,10 @@
         <v>10</v>
       </c>
       <c r="D613" t="n">
-        <v>17.069</v>
+        <v>17.327</v>
       </c>
       <c r="E613" t="n">
-        <v>22.638</v>
+        <v>22.686</v>
       </c>
       <c r="F613" t="n">
         <v>40.626</v>
@@ -22570,13 +22570,13 @@
         <v>10</v>
       </c>
       <c r="D1007" t="n">
-        <v>71.62</v>
+        <v>73.06</v>
       </c>
       <c r="E1007" t="n">
-        <v>50.56</v>
+        <v>52.71</v>
       </c>
       <c r="F1007" t="n">
-        <v>179.03</v>
+        <v>178.31</v>
       </c>
     </row>
     <row r="1008">
@@ -36114,13 +36114,13 @@
         <v>10</v>
       </c>
       <c r="D1663" t="n">
-        <v>154.735</v>
+        <v>157.405</v>
       </c>
       <c r="E1663" t="n">
-        <v>146.636</v>
+        <v>149.806</v>
       </c>
       <c r="F1663" t="n">
-        <v>295.099</v>
+        <v>294.379</v>
       </c>
     </row>
   </sheetData>
@@ -37548,7 +37548,7 @@
         <v>148.64</v>
       </c>
       <c r="K34" t="n">
-        <v>179.03</v>
+        <v>178.31</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
@@ -38791,12 +38791,12 @@
         <v>140.368</v>
       </c>
       <c r="K34" t="n">
-        <v>154.735</v>
+        <v>157.405</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>478.14</v>
+        <v>480.8099999999999</v>
       </c>
     </row>
   </sheetData>
@@ -40045,12 +40045,12 @@
         <v>42.813</v>
       </c>
       <c r="K34" t="n">
-        <v>146.636</v>
+        <v>149.806</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>504.7139999999999</v>
+        <v>507.884</v>
       </c>
     </row>
   </sheetData>
@@ -41190,7 +41190,7 @@
         <v>285.545</v>
       </c>
       <c r="K34" t="n">
-        <v>295.099</v>
+        <v>294.379</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
@@ -45636,12 +45636,12 @@
         <v>37.966</v>
       </c>
       <c r="K31" t="n">
-        <v>66.04600000000001</v>
+        <v>67.018</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>147.14</v>
+        <v>148.112</v>
       </c>
     </row>
   </sheetData>
@@ -47038,12 +47038,12 @@
         <v>10.832</v>
       </c>
       <c r="K31" t="n">
-        <v>73.438</v>
+        <v>74.41</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>143.368</v>
+        <v>144.34</v>
       </c>
     </row>
   </sheetData>
@@ -49371,12 +49371,12 @@
         <v>34.902</v>
       </c>
       <c r="K23" t="n">
-        <v>17.069</v>
+        <v>17.327</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>128.43</v>
+        <v>128.688</v>
       </c>
     </row>
   </sheetData>
@@ -50405,12 +50405,12 @@
         <v>15.561</v>
       </c>
       <c r="K23" t="n">
-        <v>22.638</v>
+        <v>22.686</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>143.766</v>
+        <v>143.814</v>
       </c>
     </row>
   </sheetData>
@@ -52894,12 +52894,12 @@
         <v>67.5</v>
       </c>
       <c r="K34" t="n">
-        <v>71.62</v>
+        <v>73.06</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>202.57</v>
+        <v>204.01</v>
       </c>
     </row>
   </sheetData>
@@ -54428,12 +54428,12 @@
         <v>16.42</v>
       </c>
       <c r="K34" t="n">
-        <v>50.56</v>
+        <v>52.71</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>217.58</v>
+        <v>219.73</v>
       </c>
     </row>
   </sheetData>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -28302,13 +28302,13 @@
         <v>10</v>
       </c>
       <c r="D1269" t="n">
-        <v>103.23</v>
+        <v>103.4</v>
       </c>
       <c r="E1269" t="n">
-        <v>156.54</v>
+        <v>156.98</v>
       </c>
       <c r="F1269" t="n">
-        <v>267.36</v>
+        <v>266.92</v>
       </c>
     </row>
     <row r="1270">
@@ -42237,12 +42237,12 @@
         <v>129.81</v>
       </c>
       <c r="K23" t="n">
-        <v>103.23</v>
+        <v>103.4</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>345.05</v>
+        <v>345.22</v>
       </c>
     </row>
   </sheetData>
@@ -43271,12 +43271,12 @@
         <v>14.19</v>
       </c>
       <c r="K23" t="n">
-        <v>156.54</v>
+        <v>156.98</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>319.97</v>
+        <v>320.41</v>
       </c>
     </row>
   </sheetData>
@@ -44237,7 +44237,7 @@
         <v>325.6</v>
       </c>
       <c r="K23" t="n">
-        <v>267.36</v>
+        <v>266.92</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -8330,13 +8330,13 @@
         <v>10</v>
       </c>
       <c r="D359" t="n">
-        <v>67.018</v>
+        <v>69.015</v>
       </c>
       <c r="E359" t="n">
-        <v>74.41</v>
+        <v>76.747</v>
       </c>
       <c r="F359" t="n">
-        <v>75.443</v>
+        <v>74.191</v>
       </c>
     </row>
     <row r="360">
@@ -13902,13 +13902,13 @@
         <v>10</v>
       </c>
       <c r="D613" t="n">
-        <v>17.327</v>
+        <v>17.48</v>
       </c>
       <c r="E613" t="n">
-        <v>22.686</v>
+        <v>22.734</v>
       </c>
       <c r="F613" t="n">
-        <v>40.626</v>
+        <v>40.732</v>
       </c>
     </row>
     <row r="614">
@@ -36114,13 +36114,13 @@
         <v>10</v>
       </c>
       <c r="D1663" t="n">
-        <v>157.405</v>
+        <v>159.555</v>
       </c>
       <c r="E1663" t="n">
-        <v>149.806</v>
+        <v>152.191</v>
       </c>
       <c r="F1663" t="n">
-        <v>294.379</v>
+        <v>293.233</v>
       </c>
     </row>
   </sheetData>
@@ -38791,12 +38791,12 @@
         <v>140.368</v>
       </c>
       <c r="K34" t="n">
-        <v>157.405</v>
+        <v>159.555</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>480.8099999999999</v>
+        <v>482.96</v>
       </c>
     </row>
   </sheetData>
@@ -40045,12 +40045,12 @@
         <v>42.813</v>
       </c>
       <c r="K34" t="n">
-        <v>149.806</v>
+        <v>152.191</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>507.884</v>
+        <v>510.269</v>
       </c>
     </row>
   </sheetData>
@@ -41190,7 +41190,7 @@
         <v>285.545</v>
       </c>
       <c r="K34" t="n">
-        <v>294.379</v>
+        <v>293.233</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
@@ -45636,12 +45636,12 @@
         <v>37.966</v>
       </c>
       <c r="K31" t="n">
-        <v>67.018</v>
+        <v>69.015</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>148.112</v>
+        <v>150.109</v>
       </c>
     </row>
   </sheetData>
@@ -47038,12 +47038,12 @@
         <v>10.832</v>
       </c>
       <c r="K31" t="n">
-        <v>74.41</v>
+        <v>76.747</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>144.34</v>
+        <v>146.677</v>
       </c>
     </row>
   </sheetData>
@@ -48348,7 +48348,7 @@
         <v>85.508</v>
       </c>
       <c r="K31" t="n">
-        <v>75.443</v>
+        <v>74.191</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
@@ -49371,12 +49371,12 @@
         <v>34.902</v>
       </c>
       <c r="K23" t="n">
-        <v>17.327</v>
+        <v>17.48</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>128.688</v>
+        <v>128.841</v>
       </c>
     </row>
   </sheetData>
@@ -50405,12 +50405,12 @@
         <v>15.561</v>
       </c>
       <c r="K23" t="n">
-        <v>22.686</v>
+        <v>22.734</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>143.814</v>
+        <v>143.862</v>
       </c>
     </row>
   </sheetData>
@@ -51363,7 +51363,7 @@
         <v>51.397</v>
       </c>
       <c r="K23" t="n">
-        <v>40.626</v>
+        <v>40.732</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -22570,13 +22570,13 @@
         <v>10</v>
       </c>
       <c r="D1007" t="n">
-        <v>73.06</v>
+        <v>74.23</v>
       </c>
       <c r="E1007" t="n">
-        <v>52.71</v>
+        <v>54.12</v>
       </c>
       <c r="F1007" t="n">
-        <v>178.31</v>
+        <v>178.07</v>
       </c>
     </row>
     <row r="1008">
@@ -28308,7 +28308,7 @@
         <v>156.98</v>
       </c>
       <c r="F1269" t="n">
-        <v>266.92</v>
+        <v>266.93</v>
       </c>
     </row>
     <row r="1270">
@@ -36114,13 +36114,13 @@
         <v>10</v>
       </c>
       <c r="D1663" t="n">
-        <v>159.555</v>
+        <v>160.725</v>
       </c>
       <c r="E1663" t="n">
-        <v>152.191</v>
+        <v>153.601</v>
       </c>
       <c r="F1663" t="n">
-        <v>293.233</v>
+        <v>292.993</v>
       </c>
     </row>
   </sheetData>
@@ -37548,7 +37548,7 @@
         <v>148.64</v>
       </c>
       <c r="K34" t="n">
-        <v>178.31</v>
+        <v>178.07</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
@@ -38791,12 +38791,12 @@
         <v>140.368</v>
       </c>
       <c r="K34" t="n">
-        <v>159.555</v>
+        <v>160.725</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>482.96</v>
+        <v>484.13</v>
       </c>
     </row>
   </sheetData>
@@ -40045,12 +40045,12 @@
         <v>42.813</v>
       </c>
       <c r="K34" t="n">
-        <v>152.191</v>
+        <v>153.601</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>510.269</v>
+        <v>511.679</v>
       </c>
     </row>
   </sheetData>
@@ -41190,7 +41190,7 @@
         <v>285.545</v>
       </c>
       <c r="K34" t="n">
-        <v>293.233</v>
+        <v>292.993</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
@@ -44237,7 +44237,7 @@
         <v>325.6</v>
       </c>
       <c r="K23" t="n">
-        <v>266.92</v>
+        <v>266.93</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
@@ -52894,12 +52894,12 @@
         <v>67.5</v>
       </c>
       <c r="K34" t="n">
-        <v>73.06</v>
+        <v>74.23</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>204.01</v>
+        <v>205.18</v>
       </c>
     </row>
   </sheetData>
@@ -54428,12 +54428,12 @@
         <v>16.42</v>
       </c>
       <c r="K34" t="n">
-        <v>52.71</v>
+        <v>54.12</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>219.73</v>
+        <v>221.14</v>
       </c>
     </row>
   </sheetData>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -28302,13 +28302,13 @@
         <v>10</v>
       </c>
       <c r="D1269" t="n">
-        <v>103.4</v>
+        <v>103.57</v>
       </c>
       <c r="E1269" t="n">
-        <v>156.98</v>
+        <v>157.42</v>
       </c>
       <c r="F1269" t="n">
-        <v>266.93</v>
+        <v>266.48</v>
       </c>
     </row>
     <row r="1270">
@@ -42237,12 +42237,12 @@
         <v>129.81</v>
       </c>
       <c r="K23" t="n">
-        <v>103.4</v>
+        <v>103.57</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>345.22</v>
+        <v>345.39</v>
       </c>
     </row>
   </sheetData>
@@ -43271,12 +43271,12 @@
         <v>14.19</v>
       </c>
       <c r="K23" t="n">
-        <v>156.98</v>
+        <v>157.42</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>320.41</v>
+        <v>320.85</v>
       </c>
     </row>
   </sheetData>
@@ -44237,7 +44237,7 @@
         <v>325.6</v>
       </c>
       <c r="K23" t="n">
-        <v>266.93</v>
+        <v>266.48</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>

--- a/water_data.xlsx
+++ b/water_data.xlsx
@@ -8330,13 +8330,13 @@
         <v>10</v>
       </c>
       <c r="D359" t="n">
-        <v>69.015</v>
+        <v>70.136</v>
       </c>
       <c r="E359" t="n">
-        <v>76.747</v>
+        <v>78.31999999999999</v>
       </c>
       <c r="F359" t="n">
-        <v>74.191</v>
+        <v>73.739</v>
       </c>
     </row>
     <row r="360">
@@ -13905,10 +13905,10 @@
         <v>17.48</v>
       </c>
       <c r="E613" t="n">
-        <v>22.734</v>
+        <v>22.782</v>
       </c>
       <c r="F613" t="n">
-        <v>40.732</v>
+        <v>40.521</v>
       </c>
     </row>
     <row r="614">
@@ -22570,13 +22570,13 @@
         <v>10</v>
       </c>
       <c r="D1007" t="n">
-        <v>74.23</v>
+        <v>75.56999999999999</v>
       </c>
       <c r="E1007" t="n">
-        <v>54.12</v>
+        <v>55.7</v>
       </c>
       <c r="F1007" t="n">
-        <v>178.07</v>
+        <v>177.84</v>
       </c>
     </row>
     <row r="1008">
@@ -36114,13 +36114,13 @@
         <v>10</v>
       </c>
       <c r="D1663" t="n">
-        <v>160.725</v>
+        <v>163.186</v>
       </c>
       <c r="E1663" t="n">
-        <v>153.601</v>
+        <v>156.802</v>
       </c>
       <c r="F1663" t="n">
-        <v>292.993</v>
+        <v>292.1</v>
       </c>
     </row>
   </sheetData>
@@ -37548,7 +37548,7 @@
         <v>148.64</v>
       </c>
       <c r="K34" t="n">
-        <v>178.07</v>
+        <v>177.84</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
@@ -38791,12 +38791,12 @@
         <v>140.368</v>
       </c>
       <c r="K34" t="n">
-        <v>160.725</v>
+        <v>163.186</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>484.13</v>
+        <v>486.591</v>
       </c>
     </row>
   </sheetData>
@@ -40045,12 +40045,12 @@
         <v>42.813</v>
       </c>
       <c r="K34" t="n">
-        <v>153.601</v>
+        <v>156.802</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>511.679</v>
+        <v>514.88</v>
       </c>
     </row>
   </sheetData>
@@ -41190,7 +41190,7 @@
         <v>285.545</v>
       </c>
       <c r="K34" t="n">
-        <v>292.993</v>
+        <v>292.1</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
@@ -45636,12 +45636,12 @@
         <v>37.966</v>
       </c>
       <c r="K31" t="n">
-        <v>69.015</v>
+        <v>70.136</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>150.109</v>
+        <v>151.23</v>
       </c>
     </row>
   </sheetData>
@@ -47038,12 +47038,12 @@
         <v>10.832</v>
       </c>
       <c r="K31" t="n">
-        <v>76.747</v>
+        <v>78.31999999999999</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>146.677</v>
+        <v>148.25</v>
       </c>
     </row>
   </sheetData>
@@ -48348,7 +48348,7 @@
         <v>85.508</v>
       </c>
       <c r="K31" t="n">
-        <v>74.191</v>
+        <v>73.739</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
@@ -50405,12 +50405,12 @@
         <v>15.561</v>
       </c>
       <c r="K23" t="n">
-        <v>22.734</v>
+        <v>22.782</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>143.862</v>
+        <v>143.91</v>
       </c>
     </row>
   </sheetData>
@@ -51363,7 +51363,7 @@
         <v>51.397</v>
       </c>
       <c r="K23" t="n">
-        <v>40.732</v>
+        <v>40.521</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
@@ -52894,12 +52894,12 @@
         <v>67.5</v>
       </c>
       <c r="K34" t="n">
-        <v>74.23</v>
+        <v>75.56999999999999</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>205.18</v>
+        <v>206.52</v>
       </c>
     </row>
   </sheetData>
@@ -54428,12 +54428,12 @@
         <v>16.42</v>
       </c>
       <c r="K34" t="n">
-        <v>54.12</v>
+        <v>55.7</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>221.14</v>
+        <v>222.72</v>
       </c>
     </row>
   </sheetData>
